--- a/derivatives/parametric_volatility_example.xlsx
+++ b/derivatives/parametric_volatility_example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ABak\latex\derivatives\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD171E2E-CFA8-4289-84E7-9CEF21320168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F298AA-46AB-43C9-AE32-734861E478A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11250" yWindow="4020" windowWidth="27150" windowHeight="16860" xr2:uid="{31829330-7045-44DE-930E-36EDCF213539}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{31829330-7045-44DE-930E-36EDCF213539}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -419,13 +419,13 @@
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -574,7 +574,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{246295EA-9751-4925-8C3C-BE49E772790E}" type="CELLRANGE">
+                    <a:fld id="{4089C621-F2B6-4714-BDEE-3A96B74716C4}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -607,7 +607,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7E8FE36F-5B1E-4011-A5F0-3B69460B5013}" type="CELLRANGE">
+                    <a:fld id="{543626FD-1142-4271-BC10-4CE05356B63D}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -641,7 +641,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{74F094C4-89C5-439F-8EC2-5A440982D898}" type="CELLRANGE">
+                    <a:fld id="{B7172EDE-1E16-4683-B49F-FF784DBE257B}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -675,7 +675,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BC31E99C-F624-490A-AAF9-2A3EBC19CF73}" type="CELLRANGE">
+                    <a:fld id="{39B4CD43-2E99-49CC-8E12-9261384D6E95}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -709,7 +709,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9CC3AE1D-D861-43E5-A58A-0B6E3CDFD259}" type="CELLRANGE">
+                    <a:fld id="{C5CABA82-D83A-47B2-AAC3-FA35BF9B7F70}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -811,19 +811,19 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>8.0499999999999988E-2</c:v>
+                  <c:v>8.7499999999999994E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.6249999999999998E-2</c:v>
+                  <c:v>7.6000000000000012E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.5499999999999998E-2</c:v>
+                  <c:v>6.9000000000000006E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.9750000000000001E-2</c:v>
+                  <c:v>6.8000000000000005E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.7499999999999994E-2</c:v>
+                  <c:v>7.2500000000000009E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1006,6 +1006,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1013,7 +1014,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1241,19 +1241,19 @@
                   <c:v>1.2400000000000002</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="#,##0.0000">
-                  <c:v>1.0323369799876165</c:v>
+                  <c:v>1.0949090068168106</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="#,##0.0000">
-                  <c:v>1.0600347861818515</c:v>
+                  <c:v>1.1293039487620771</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="#,##0.0000">
-                  <c:v>1.0879017903763666</c:v>
+                  <c:v>1.1587614138335498</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="#,##0.0000">
-                  <c:v>1.1177534735320678</c:v>
+                  <c:v>1.1857247812154261</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="#,##0.0000">
-                  <c:v>1.1510707999322727</c:v>
+                  <c:v>1.2140828375149078</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1265,79 +1265,79 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="30"/>
                 <c:pt idx="0">
-                  <c:v>9.0559463187796729E-2</c:v>
+                  <c:v>0.16690163787807857</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.6802897678449176E-2</c:v>
+                  <c:v>0.15526370930971153</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.3615816921207703E-2</c:v>
+                  <c:v>0.14446197909298242</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.0981939103500614E-2</c:v>
+                  <c:v>0.13447312555479016</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.8885553782162637E-2</c:v>
+                  <c:v>0.1252746377517584</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.7311497171383275E-2</c:v>
+                  <c:v>0.11684478058710904</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.6245128709093835E-2</c:v>
+                  <c:v>0.10916256172609889</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.5672308824755355E-2</c:v>
+                  <c:v>0.10220770020190049</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>7.5579377836803907E-2</c:v>
+                  <c:v>9.5960596611223428E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.595313591289736E-2</c:v>
+                  <c:v>9.04023048058189E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7.6780824030620323E-2</c:v>
+                  <c:v>8.5514504992336121E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7.8050105880476228E-2</c:v>
+                  <c:v>8.1279478158845161E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7.9749050656852713E-2</c:v>
+                  <c:v>7.7680081751746344E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>8.1866116686218071E-2</c:v>
+                  <c:v>7.4699726531794922E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>8.4390135845114941E-2</c:v>
+                  <c:v>7.2322354542605466E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>8.7310298723581356E-2</c:v>
+                  <c:v>7.0532418129298391E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>9.0616140492473851E-2</c:v>
+                  <c:v>6.9314859948939017E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>9.4297527435806633E-2</c:v>
+                  <c:v>6.8655093918120372E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>9.8344644111669544E-2</c:v>
+                  <c:v>6.8538987046476971E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.10274798110756644</c:v>
+                  <c:v>6.8952842108113269E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.10749832335813374</c:v>
+                  <c:v>6.9883381105899187E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.11258673899516657</c:v>
+                  <c:v>7.1317729486351511E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.11800456870171631</c:v>
+                  <c:v>7.3243401065392191E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.12374341554373314</c:v>
+                  <c:v>7.5648283627673327E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.12979513525431449</c:v>
+                  <c:v>7.8520625164394758E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2095,7 +2095,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9ED0BC87-D627-44CF-B5E9-2446EF04E29D}" type="CELLRANGE">
+                    <a:fld id="{F3A3EBCF-BE74-416D-8A5F-7625CA727FF5}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2129,7 +2129,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9BDFC68E-5AEE-4213-A48D-EF5FEA24BDEA}" type="CELLRANGE">
+                    <a:fld id="{1206951D-D29A-4F30-A1D0-2EC0DE8BC11E}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2163,7 +2163,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{90F75C42-FBA6-4180-89D3-FF61F32ED92A}" type="CELLRANGE">
+                    <a:fld id="{59C08CD4-2129-435D-8FA3-84640F64E1C1}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2197,7 +2197,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{73D8FF39-9B83-43D5-AC4B-4FA5259C2AA1}" type="CELLRANGE">
+                    <a:fld id="{1DFF76FD-6FE2-43B9-89E2-57D5CF338281}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2231,7 +2231,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{98A65526-4DE9-4F37-87E2-DBE13A170284}" type="CELLRANGE">
+                    <a:fld id="{C61BF8C6-52D3-4287-900E-0D8A84835041}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2384,19 +2384,19 @@
                   <c:v>1.2400000000000002</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="#,##0.0000">
-                  <c:v>1.0323369799876165</c:v>
+                  <c:v>1.0949090068168106</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="#,##0.0000">
-                  <c:v>1.0600347861818515</c:v>
+                  <c:v>1.1293039487620771</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="#,##0.0000">
-                  <c:v>1.0879017903763666</c:v>
+                  <c:v>1.1587614138335498</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="#,##0.0000">
-                  <c:v>1.1177534735320678</c:v>
+                  <c:v>1.1857247812154261</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="#,##0.0000">
-                  <c:v>1.1510707999322727</c:v>
+                  <c:v>1.2140828375149078</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2408,19 +2408,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="30"/>
                 <c:pt idx="25" formatCode="0.00%">
-                  <c:v>8.0499999999999988E-2</c:v>
+                  <c:v>8.7499999999999994E-2</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="0.00%">
-                  <c:v>7.6249999999999998E-2</c:v>
+                  <c:v>7.6000000000000012E-2</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="0.00%">
-                  <c:v>7.5499999999999998E-2</c:v>
+                  <c:v>6.9000000000000006E-2</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="0.00%">
-                  <c:v>7.9750000000000001E-2</c:v>
+                  <c:v>6.8000000000000005E-2</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="0.00%">
-                  <c:v>8.7499999999999994E-2</c:v>
+                  <c:v>7.2500000000000009E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2470,8 +2470,8 @@
         <c:axId val="713266048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="1.2"/>
-          <c:min val="1"/>
+          <c:max val="1.25"/>
+          <c:min val="1.05"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -2636,6 +2636,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2643,7 +2644,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3676,454 +3676,454 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="51">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="101">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="102">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="103">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="104">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="105">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="106">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="107">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="108">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="109">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="110">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="111">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="112">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="113">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="114">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="65">
+                <c:pt idx="115">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="116">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="67">
+                <c:pt idx="117">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="68">
+                <c:pt idx="118">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="69">
+                <c:pt idx="119">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="70">
+                <c:pt idx="120">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="121">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="72">
+                <c:pt idx="122">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="123">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="124">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="125">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="76">
+                <c:pt idx="126">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="77">
+                <c:pt idx="127">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="78">
+                <c:pt idx="128">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="79">
+                <c:pt idx="129">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="80">
+                <c:pt idx="130">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="81">
+                <c:pt idx="131">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="82">
+                <c:pt idx="132">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="83">
+                <c:pt idx="133">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="84">
+                <c:pt idx="134">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="85">
+                <c:pt idx="135">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="86">
+                <c:pt idx="136">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="87">
+                <c:pt idx="137">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="88">
+                <c:pt idx="138">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="89">
+                <c:pt idx="139">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="90">
+                <c:pt idx="140">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="91">
+                <c:pt idx="141">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="92">
+                <c:pt idx="142">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="93">
+                <c:pt idx="143">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="94">
+                <c:pt idx="144">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="95">
+                <c:pt idx="145">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="96">
+                <c:pt idx="146">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="97">
+                <c:pt idx="147">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="98">
+                <c:pt idx="148">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="99">
+                <c:pt idx="149">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="100">
+                <c:pt idx="150">
                   <c:v>1000000</c:v>
                 </c:pt>
-                <c:pt idx="101">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="123">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="124">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="125">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>0</c:v>
-                </c:pt>
                 <c:pt idx="151">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="152">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="153">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="154">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="155">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="156">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="157">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="158">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="159">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="160">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="161">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="162">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="163">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="164">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="165">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="166">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="167">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="168">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="169">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="170">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="171">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="172">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="173">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="174">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="175">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="176">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="177">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="178">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="179">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="180">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="181">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="182">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="183">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="184">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="185">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="186">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="187">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="188">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="189">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="190">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="191">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="192">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="193">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="194">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="195">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="196">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="197">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="198">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="199">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="200">
-                  <c:v>0</c:v>
+                  <c:v>1000000</c:v>
                 </c:pt>
                 <c:pt idx="201">
                   <c:v>0</c:v>
@@ -4270,7 +4270,7 @@
         <c:axId val="1923050944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="1.1500000000000001"/>
+          <c:max val="1.3"/>
           <c:min val="1"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -4402,6 +4402,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4409,7 +4410,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4552,187 +4552,187 @@
                 <c:formatCode>0.0000</c:formatCode>
                 <c:ptCount val="61"/>
                 <c:pt idx="0">
-                  <c:v>0.9</c:v>
+                  <c:v>1.05</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.90500000000000003</c:v>
+                  <c:v>1.0549999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.91</c:v>
+                  <c:v>1.0599999999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.91500000000000004</c:v>
+                  <c:v>1.0649999999999997</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.92</c:v>
+                  <c:v>1.0699999999999996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.92500000000000004</c:v>
+                  <c:v>1.0749999999999995</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.93</c:v>
+                  <c:v>1.0799999999999994</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.93500000000000005</c:v>
+                  <c:v>1.0849999999999993</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.94000000000000006</c:v>
+                  <c:v>1.0899999999999992</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.94500000000000006</c:v>
+                  <c:v>1.0949999999999991</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.95000000000000007</c:v>
+                  <c:v>1.099999999999999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.95500000000000007</c:v>
+                  <c:v>1.1049999999999989</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.96000000000000008</c:v>
+                  <c:v>1.1099999999999988</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.96500000000000008</c:v>
+                  <c:v>1.1149999999999987</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.97000000000000008</c:v>
+                  <c:v>1.1199999999999986</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.97500000000000009</c:v>
+                  <c:v>1.1249999999999984</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.98000000000000009</c:v>
+                  <c:v>1.1299999999999983</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.9850000000000001</c:v>
+                  <c:v>1.1349999999999982</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.9900000000000001</c:v>
+                  <c:v>1.1399999999999981</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.99500000000000011</c:v>
+                  <c:v>1.144999999999998</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1</c:v>
+                  <c:v>1.1499999999999979</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.0049999999999999</c:v>
+                  <c:v>1.1549999999999978</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.0099999999999998</c:v>
+                  <c:v>1.1599999999999977</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.0149999999999997</c:v>
+                  <c:v>1.1649999999999976</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.0199999999999996</c:v>
+                  <c:v>1.1699999999999975</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.0249999999999995</c:v>
+                  <c:v>1.1749999999999974</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.0299999999999994</c:v>
+                  <c:v>1.1799999999999973</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.0349999999999993</c:v>
+                  <c:v>1.1849999999999972</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.0399999999999991</c:v>
+                  <c:v>1.1899999999999971</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.044999999999999</c:v>
+                  <c:v>1.194999999999997</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.0499999999999989</c:v>
+                  <c:v>1.1999999999999968</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.0549999999999988</c:v>
+                  <c:v>1.2049999999999967</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1.0599999999999987</c:v>
+                  <c:v>1.2099999999999966</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1.0649999999999986</c:v>
+                  <c:v>1.2149999999999965</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1.0699999999999985</c:v>
+                  <c:v>1.2199999999999964</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1.0749999999999984</c:v>
+                  <c:v>1.2249999999999963</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1.0799999999999983</c:v>
+                  <c:v>1.2299999999999962</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1.0849999999999982</c:v>
+                  <c:v>1.2349999999999961</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1.0899999999999981</c:v>
+                  <c:v>1.239999999999996</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1.094999999999998</c:v>
+                  <c:v>1.2449999999999959</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1.0999999999999979</c:v>
+                  <c:v>1.2499999999999958</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1.1049999999999978</c:v>
+                  <c:v>1.2549999999999957</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1.1099999999999977</c:v>
+                  <c:v>1.2599999999999956</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1.1149999999999975</c:v>
+                  <c:v>1.2649999999999955</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1.1199999999999974</c:v>
+                  <c:v>1.2699999999999954</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1.1249999999999973</c:v>
+                  <c:v>1.2749999999999952</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>1.1299999999999972</c:v>
+                  <c:v>1.2799999999999951</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>1.1349999999999971</c:v>
+                  <c:v>1.284999999999995</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>1.139999999999997</c:v>
+                  <c:v>1.2899999999999949</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>1.1449999999999969</c:v>
+                  <c:v>1.2949999999999948</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>1.1499999999999968</c:v>
+                  <c:v>1.2999999999999947</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>1.1549999999999967</c:v>
+                  <c:v>1.3049999999999946</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>1.1599999999999966</c:v>
+                  <c:v>1.3099999999999945</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>1.1649999999999965</c:v>
+                  <c:v>1.3149999999999944</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>1.1699999999999964</c:v>
+                  <c:v>1.3199999999999943</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>1.1749999999999963</c:v>
+                  <c:v>1.3249999999999942</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>1.1799999999999962</c:v>
+                  <c:v>1.3299999999999941</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>1.1849999999999961</c:v>
+                  <c:v>1.334999999999994</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>1.1899999999999959</c:v>
+                  <c:v>1.3399999999999939</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>1.1949999999999958</c:v>
+                  <c:v>1.3449999999999938</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>1.1999999999999957</c:v>
+                  <c:v>1.3499999999999936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4744,187 +4744,187 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="61"/>
                 <c:pt idx="0">
-                  <c:v>4.953837050595477E-4</c:v>
+                  <c:v>2.4938748870468714E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.6818858155224432E-4</c:v>
+                  <c:v>2.8298925283318467E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.4694397915282923E-4</c:v>
+                  <c:v>3.2578882362376826E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.3207896769450875E-4</c:v>
+                  <c:v>3.7986616345095582E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.2420892364859199E-4</c:v>
+                  <c:v>4.4774694091237605E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.2410165619029039E-4</c:v>
+                  <c:v>5.3248158061173561E-3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.3289758777102089E-4</c:v>
+                  <c:v>6.3765030888964661E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.5201942362720451E-4</c:v>
+                  <c:v>7.6738221547341988E-3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.8343185194247039E-4</c:v>
+                  <c:v>9.2627508242058149E-3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.2963589819195569E-4</c:v>
+                  <c:v>1.1191997218901097E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.9409799497551184E-4</c:v>
+                  <c:v>1.3509888227413967E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>6.8113142324800269E-4</c:v>
+                  <c:v>1.625879677596169E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7.9661895624891569E-4</c:v>
+                  <c:v>1.9467618083084063E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>9.4808060737076221E-4</c:v>
+                  <c:v>2.3141874420853591E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.1453059435974876E-3</c:v>
+                  <c:v>2.7252266912264268E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.4009525250086793E-3</c:v>
+                  <c:v>3.1723109594901024E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.7311274073166765E-3</c:v>
+                  <c:v>3.6422910723394736E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2.1563977142368845E-3</c:v>
+                  <c:v>4.1160633322242193E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2.7024060139590827E-3</c:v>
+                  <c:v>4.5691021235013056E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3.4006663566011398E-3</c:v>
+                  <c:v>4.9730902441290817E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4.2892361072373189E-3</c:v>
+                  <c:v>5.2987518032086407E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>5.4125860958171811E-3</c:v>
+                  <c:v>5.5194969205516725E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>6.8209513667600707E-3</c:v>
+                  <c:v>5.6153192734264605E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>8.5681632471662859E-3</c:v>
+                  <c:v>5.5761041337521793E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.0707821592252422E-2</c:v>
+                  <c:v>5.4034613699812335E-2</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.3287434594734682E-2</c:v>
+                  <c:v>5.1106811567953325E-2</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.6339905136033159E-2</c:v>
+                  <c:v>4.7206879312548612E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.9873481519125671E-2</c:v>
+                  <c:v>4.2625703315813446E-2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2.3860308078788004E-2</c:v>
+                  <c:v>3.767448743609584E-2</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2.822632510354646E-2</c:v>
+                  <c:v>3.2646094300185204E-2</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>3.2844239994331254E-2</c:v>
+                  <c:v>2.7786060382891199E-2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>3.7532990927185005E-2</c:v>
+                  <c:v>2.3276465085906032E-2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>4.2065678999521329E-2</c:v>
+                  <c:v>1.923243096283872E-2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>4.6187058471483758E-2</c:v>
+                  <c:v>1.5708650932677416E-2</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>4.963921320806966E-2</c:v>
+                  <c:v>1.2711403426322834E-2</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>5.2191964180730924E-2</c:v>
+                  <c:v>1.0212772237174933E-2</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>5.3672362372751185E-2</c:v>
+                  <c:v>8.1640338261330676E-3</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>5.3987406897782954E-2</c:v>
+                  <c:v>6.5065441866526234E-3</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>5.313553390919732E-2</c:v>
+                  <c:v>5.1797902893949109E-3</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>5.1204228487722776E-2</c:v>
+                  <c:v>4.1264442226062051E-3</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>4.8355117287569166E-2</c:v>
+                  <c:v>3.2952672905274508E-3</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>4.4800132578061938E-2</c:v>
+                  <c:v>2.6422775394441145E-3</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>4.0773777960015467E-2</c:v>
+                  <c:v>2.1308158077043065E-3</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>3.6506963574391031E-2</c:v>
+                  <c:v>1.7309924473176092E-3</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>3.2206076245202664E-2</c:v>
+                  <c:v>1.4188558295624332E-3</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2.8039517413500314E-2</c:v>
+                  <c:v>1.1754408392872305E-3</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>2.4131864117962032E-2</c:v>
+                  <c:v>9.8585766497873237E-4</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>2.056427971634614E-2</c:v>
+                  <c:v>8.3850217692721808E-4</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>1.7379657077834031E-2</c:v>
+                  <c:v>7.2436546801846191E-4</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>1.4589907124538951E-2</c:v>
+                  <c:v>6.364676106075188E-4</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>1.2184171849135719E-2</c:v>
+                  <c:v>5.6940021196347874E-4</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>1.0136388787791859E-2</c:v>
+                  <c:v>5.1899020741327545E-4</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>8.4117884641714408E-3</c:v>
+                  <c:v>4.8198415176698345E-4</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>6.9717934071688329E-3</c:v>
+                  <c:v>4.5587494751960362E-4</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>5.7776080822269822E-3</c:v>
+                  <c:v>4.386946720488506E-4</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>4.7924739779361273E-3</c:v>
+                  <c:v>4.2891094741429991E-4</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>3.9829790453027271E-3</c:v>
+                  <c:v>4.2531376181173926E-4</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>3.319674838488182E-3</c:v>
+                  <c:v>4.2694617837378188E-4</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>2.7771746080766232E-3</c:v>
+                  <c:v>4.3305177547374468E-4</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>2.3339744043599123E-3</c:v>
+                  <c:v>4.4302392661889128E-4</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>1.972113632288676E-3</c:v>
+                  <c:v>4.5636252630062475E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4951,8 +4951,8 @@
         <c:axId val="551620431"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="1.2"/>
-          <c:min val="0.95000000000000007"/>
+          <c:max val="1.25"/>
+          <c:min val="1.05"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -5084,6 +5084,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5091,7 +5092,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7814,12 +7814,12 @@
         <v>53</v>
       </c>
       <c r="B1" s="25">
-        <v>1.0820000000000001</v>
-      </c>
-      <c r="E1" s="33" t="s">
+        <v>1.1539999999999999</v>
+      </c>
+      <c r="E1" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="34"/>
+      <c r="F1" s="35"/>
       <c r="S1" t="s">
         <v>41</v>
       </c>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="T2" s="3">
         <f>D19</f>
-        <v>8.0499999999999988E-2</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="U2" t="str">
         <f>C19</f>
@@ -7860,20 +7860,20 @@
         <v>51</v>
       </c>
       <c r="B3" s="20">
-        <v>4.2999999999999997E-2</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="22">
-        <v>1.05</v>
+      <c r="F3" s="28">
+        <v>1.1000000000000001</v>
       </c>
       <c r="S3">
         <v>25</v>
       </c>
       <c r="T3" s="3">
         <f>D20</f>
-        <v>7.6249999999999998E-2</v>
+        <v>7.6000000000000012E-2</v>
       </c>
       <c r="U3" t="str">
         <f>C20</f>
@@ -7885,20 +7885,20 @@
         <v>52</v>
       </c>
       <c r="B4" s="20">
-        <v>2.3E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>49</v>
       </c>
       <c r="F4" s="28">
-        <v>1.1000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="S4">
         <v>50</v>
       </c>
       <c r="T4" s="3">
         <f>D21</f>
-        <v>7.5499999999999998E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="U4" t="str">
         <f>C21</f>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="B5" s="26">
         <f>B1 * EXP((B3 - B4)*B2)</f>
-        <v>1.0874235475698719</v>
+        <v>1.1583356242145937</v>
       </c>
       <c r="E5" t="s">
         <v>60</v>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="T5" s="3">
         <f>D22</f>
-        <v>7.9750000000000001E-2</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="U5" t="str">
         <f>C22</f>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="T6" s="3">
         <f>D23</f>
-        <v>8.7499999999999994E-2</v>
+        <v>7.2500000000000009E-2</v>
       </c>
       <c r="U6" t="str">
         <f>C23</f>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="B8" s="24">
         <f>F42</f>
-        <v>472976.78051225375</v>
+        <v>789772.99953014147</v>
       </c>
       <c r="C8" s="12"/>
     </row>
@@ -7981,11 +7981,11 @@
       </c>
       <c r="B9" s="19">
         <f>F71</f>
-        <v>467983.33807939343</v>
+        <v>783974.49553293432</v>
       </c>
       <c r="C9" s="19">
         <f>(B9 - B$8) * 0.01 / $F$12</f>
-        <v>-49934.4243286032</v>
+        <v>-57985.039972071536</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
@@ -8054,11 +8054,11 @@
       </c>
       <c r="B10" s="19">
         <f>F100</f>
-        <v>473417.97914599738</v>
+        <v>790091.59042804188</v>
       </c>
       <c r="C10" s="19">
         <f>(B10 - B$8) * 0.01 / $F$12</f>
-        <v>4411.9863374362467</v>
+        <v>3185.9089790040161</v>
       </c>
       <c r="S10">
         <v>0.01</v>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="U10" s="3">
         <f t="shared" ref="U10:U34" si="0">$E$29 + $E$30 * LN(T10 / $B$5) + $E$31 * (LN(T10 / $B$5))^2</f>
-        <v>9.0559463187796729E-2</v>
+        <v>0.16690163787807857</v>
       </c>
       <c r="X10">
         <v>1E-3</v>
@@ -8085,47 +8085,47 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="AC10" s="29">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="AD10" s="29">
         <f>AC10-$AC$7</f>
-        <v>0.89999000000000007</v>
+        <v>1.04999</v>
       </c>
       <c r="AE10" s="29">
         <f>AC10+$AC$7</f>
-        <v>0.90000999999999998</v>
+        <v>1.0500100000000001</v>
       </c>
       <c r="AF10" s="30">
         <f>$E$29 + LN(AC10/$B$5) * $E$30 + (LN(AC10/$B$5))^2 * $E$31</f>
-        <v>0.16349421343004095</v>
+        <v>0.11684478058710904</v>
       </c>
       <c r="AG10" s="30">
         <f t="shared" ref="AG10:AH10" si="1">$E$29 + LN(AD10/$B$5) * $E$30 + (LN(AD10/$B$5))^2 * $E$31</f>
-        <v>0.16350510039895991</v>
+        <v>0.11685283356049236</v>
       </c>
       <c r="AH10" s="30">
         <f t="shared" si="1"/>
-        <v>0.16348332725596426</v>
+        <v>0.11683672836130474</v>
       </c>
       <c r="AI10" s="31">
         <f>$B$1 * EXP(-$B$4*$B$2) * _xlfn.NORM.DIST((LN($B$1/AC10) + ($B$3-$B$4+AF10^2/2)*$B$2)/(AF10*SQRT($B$2)), 0, 1, TRUE) - AC10*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST((LN($B$1/AC10) + ($B$3-$B$4-AF10^2/2)*$B$2)/(AF10*SQRT($B$2)), 0, 1, TRUE)</f>
-        <v>0.18570041144741578</v>
+        <v>0.10858819559657473</v>
       </c>
       <c r="AJ10" s="31">
         <f t="shared" ref="AJ10:AK10" si="2">$B$1 * EXP(-$B$4*$B$2) * _xlfn.NORM.DIST((LN($B$1/AD10) + ($B$3-$B$4+AG10^2/2)*$B$2)/(AG10*SQRT($B$2)), 0, 1, TRUE) - AD10*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST((LN($B$1/AD10) + ($B$3-$B$4-AG10^2/2)*$B$2)/(AG10*SQRT($B$2)), 0, 1, TRUE)</f>
-        <v>0.18571033665203029</v>
+        <v>0.10859804467952072</v>
       </c>
       <c r="AK10" s="31">
         <f t="shared" si="2"/>
-        <v>0.18569048625254303</v>
+        <v>0.10857834656301468</v>
       </c>
       <c r="AL10" s="5">
         <f>(AJ10+AK10-AI10*2)/$AC$7^2</f>
-        <v>9.7417629518758972E-2</v>
+        <v>0.4938593978209837</v>
       </c>
       <c r="AM10" s="3">
         <f>AL10/SUM($AL$10:$AL$70)</f>
-        <v>4.953837050595477E-4</v>
+        <v>2.4938748870468714E-3</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -8134,11 +8134,11 @@
       </c>
       <c r="B11" s="19">
         <f>F129</f>
-        <v>468455.70258081355</v>
+        <v>784619.10942768096</v>
       </c>
       <c r="C11" s="19">
         <f>(B11 - B$8) * 0.01 / $F$12</f>
-        <v>-45210.779314402025</v>
+        <v>-51538.901024605148</v>
       </c>
       <c r="T11" s="5">
         <f t="shared" ref="T11:T34" si="3">T10+$S$10</f>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="U11" s="3">
         <f t="shared" si="0"/>
-        <v>8.6802897678449176E-2</v>
+        <v>0.15526370930971153</v>
       </c>
       <c r="Y11" s="23">
         <f t="shared" ref="Y11:Y74" si="4">Y10+$X$10</f>
@@ -8158,47 +8158,47 @@
       </c>
       <c r="AC11" s="29">
         <f>AC10+$AB$10</f>
-        <v>0.90500000000000003</v>
+        <v>1.0549999999999999</v>
       </c>
       <c r="AD11" s="29">
         <f t="shared" ref="AD11:AD70" si="6">AC11-$AC$7</f>
-        <v>0.90499000000000007</v>
+        <v>1.0549899999999999</v>
       </c>
       <c r="AE11" s="29">
         <f t="shared" ref="AE11:AE50" si="7">AC11+$AC$7</f>
-        <v>0.90500999999999998</v>
+        <v>1.05501</v>
       </c>
       <c r="AF11" s="30">
         <f t="shared" ref="AF11:AF50" si="8">$E$29 + LN(AC11/$B$5) * $E$30 + (LN(AC11/$B$5))^2 * $E$31</f>
-        <v>0.15814976159973676</v>
+        <v>0.1129115002449651</v>
       </c>
       <c r="AG11" s="30">
         <f t="shared" ref="AG11:AG50" si="9">$E$29 + LN(AD11/$B$5) * $E$30 + (LN(AD11/$B$5))^2 * $E$31</f>
-        <v>0.15816025426432267</v>
+        <v>0.11291918198760528</v>
       </c>
       <c r="AH11" s="30">
         <f t="shared" ref="AH11:AH50" si="10">$E$29 + LN(AE11/$B$5) * $E$30 + (LN(AE11/$B$5))^2 * $E$31</f>
-        <v>0.15813926971754239</v>
+        <v>0.11290381923967768</v>
       </c>
       <c r="AI11" s="31">
         <f t="shared" ref="AI11:AI50" si="11">$B$1 * EXP(-$B$4*$B$2) * _xlfn.NORM.DIST((LN($B$1/AC11) + ($B$3-$B$4+AF11^2/2)*$B$2)/(AF11*SQRT($B$2)), 0, 1, TRUE) - AC11*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST((LN($B$1/AC11) + ($B$3-$B$4-AF11^2/2)*$B$2)/(AF11*SQRT($B$2)), 0, 1, TRUE)</f>
-        <v>0.18073900583529257</v>
+        <v>0.10367009998656451</v>
       </c>
       <c r="AJ11" s="31">
         <f t="shared" ref="AJ11:AJ50" si="12">$B$1 * EXP(-$B$4*$B$2) * _xlfn.NORM.DIST((LN($B$1/AD11) + ($B$3-$B$4+AG11^2/2)*$B$2)/(AG11*SQRT($B$2)), 0, 1, TRUE) - AD11*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST((LN($B$1/AD11) + ($B$3-$B$4-AG11^2/2)*$B$2)/(AG11*SQRT($B$2)), 0, 1, TRUE)</f>
-        <v>0.1807489263071943</v>
+        <v>0.10367992278472038</v>
       </c>
       <c r="AK11" s="31">
         <f t="shared" ref="AK11:AK50" si="13">$B$1 * EXP(-$B$4*$B$2) * _xlfn.NORM.DIST((LN($B$1/AE11) + ($B$3-$B$4+AH11^2/2)*$B$2)/(AH11*SQRT($B$2)), 0, 1, TRUE) - AE11*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST((LN($B$1/AE11) + ($B$3-$B$4-AH11^2/2)*$B$2)/(AH11*SQRT($B$2)), 0, 1, TRUE)</f>
-        <v>0.1807290853725978</v>
+        <v>0.10366027724444871</v>
       </c>
       <c r="AL11" s="5">
         <f t="shared" ref="AL11:AL70" si="14">(AJ11+AK11-AI11*2)/$AC$7^2</f>
-        <v>9.2069685209139593E-2</v>
+        <v>0.5604006148018924</v>
       </c>
       <c r="AM11" s="3">
         <f t="shared" ref="AM11:AM70" si="15">AL11/SUM($AL$10:$AL$70)</f>
-        <v>4.6818858155224432E-4</v>
+        <v>2.8298925283318467E-3</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -8207,11 +8207,11 @@
       </c>
       <c r="B12" s="19">
         <f>O100</f>
-        <v>473751.64914485143</v>
+        <v>790123.17731798696</v>
       </c>
       <c r="C12" s="19">
         <f>(B12 - B$8) * 0.01 / $F$12</f>
-        <v>7748.6863259767415</v>
+        <v>3501.7778784548864</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -8225,7 +8225,7 @@
       </c>
       <c r="U12" s="3">
         <f t="shared" si="0"/>
-        <v>8.3615816921207703E-2</v>
+        <v>0.14446197909298242</v>
       </c>
       <c r="Y12" s="23">
         <f t="shared" si="4"/>
@@ -8237,47 +8237,47 @@
       </c>
       <c r="AC12" s="29">
         <f t="shared" ref="AC12:AC70" si="16">AC11+$AB$10</f>
-        <v>0.91</v>
+        <v>1.0599999999999998</v>
       </c>
       <c r="AD12" s="29">
         <f t="shared" si="6"/>
-        <v>0.90999000000000008</v>
+        <v>1.0599899999999998</v>
       </c>
       <c r="AE12" s="29">
         <f t="shared" si="7"/>
-        <v>0.91000999999999999</v>
+        <v>1.0600099999999999</v>
       </c>
       <c r="AF12" s="30">
         <f t="shared" si="8"/>
-        <v>0.15300091274523836</v>
+        <v>0.10916256172609898</v>
       </c>
       <c r="AG12" s="30">
         <f t="shared" si="9"/>
-        <v>0.15301101726950753</v>
+        <v>0.10916987730754898</v>
       </c>
       <c r="AH12" s="30">
         <f t="shared" si="10"/>
-        <v>0.15299080899115491</v>
+        <v>0.10915524687194955</v>
       </c>
       <c r="AI12" s="31">
         <f t="shared" si="11"/>
-        <v>0.17577990438016033</v>
+        <v>9.8766052257546311E-2</v>
       </c>
       <c r="AJ12" s="31">
         <f t="shared" si="12"/>
-        <v>0.17578982035790536</v>
+        <v>9.8775845004851481E-2</v>
       </c>
       <c r="AK12" s="31">
         <f t="shared" si="13"/>
-        <v>0.1757699884112045</v>
+        <v>9.8756259574756755E-2</v>
       </c>
       <c r="AL12" s="5">
         <f t="shared" si="14"/>
-        <v>8.7891915967475129E-2</v>
+        <v>0.64515615072480148</v>
       </c>
       <c r="AM12" s="3">
         <f t="shared" si="15"/>
-        <v>4.4694397915282923E-4</v>
+        <v>3.2578882362376826E-3</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -8286,11 +8286,11 @@
       </c>
       <c r="B13" s="19">
         <f>O129</f>
-        <v>476191.95435165241</v>
+        <v>793286.9863444512</v>
       </c>
       <c r="C13" s="19">
         <f>(B13 - B$8) * 0.01 / $F$12</f>
-        <v>32151.738393986598</v>
+        <v>35139.868143097265</v>
       </c>
       <c r="E13" t="s">
         <v>50</v>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="U13" s="3">
         <f t="shared" si="0"/>
-        <v>8.0981939103500614E-2</v>
+        <v>0.13447312555479016</v>
       </c>
       <c r="Y13" s="23">
         <f t="shared" si="4"/>
@@ -8316,47 +8316,47 @@
       </c>
       <c r="AC13" s="29">
         <f t="shared" si="16"/>
-        <v>0.91500000000000004</v>
+        <v>1.0649999999999997</v>
       </c>
       <c r="AD13" s="29">
         <f t="shared" si="6"/>
-        <v>0.91499000000000008</v>
+        <v>1.0649899999999997</v>
       </c>
       <c r="AE13" s="29">
         <f t="shared" si="7"/>
-        <v>0.91500999999999999</v>
+        <v>1.0650099999999998</v>
       </c>
       <c r="AF13" s="30">
         <f t="shared" si="8"/>
-        <v>0.14804461529537108</v>
+        <v>0.10559545189492538</v>
       </c>
       <c r="AG13" s="30">
         <f t="shared" si="9"/>
-        <v>0.14805433772233378</v>
+        <v>0.10560240629865306</v>
       </c>
       <c r="AH13" s="30">
         <f t="shared" si="10"/>
-        <v>0.14803489362662731</v>
+        <v>0.10558849820861636</v>
       </c>
       <c r="AI13" s="31">
         <f t="shared" si="11"/>
-        <v>0.17082300280733542</v>
+        <v>9.3878179863807198E-2</v>
       </c>
       <c r="AJ13" s="31">
         <f t="shared" si="12"/>
-        <v>0.17083291446888804</v>
+        <v>9.38879377842462E-2</v>
       </c>
       <c r="AK13" s="31">
         <f t="shared" si="13"/>
-        <v>0.17081309115427967</v>
+        <v>9.386842201859269E-2</v>
       </c>
       <c r="AL13" s="5">
         <f t="shared" si="14"/>
-        <v>8.4968698743637092E-2</v>
+        <v>0.7522449330110702</v>
       </c>
       <c r="AM13" s="3">
         <f t="shared" si="15"/>
-        <v>4.3207896769450875E-4</v>
+        <v>3.7986616345095582E-3</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="U14" s="3">
         <f t="shared" si="0"/>
-        <v>7.8885553782162637E-2</v>
+        <v>0.1252746377517584</v>
       </c>
       <c r="Y14" s="23">
         <f t="shared" si="4"/>
@@ -8378,47 +8378,47 @@
       </c>
       <c r="AC14" s="29">
         <f t="shared" si="16"/>
-        <v>0.92</v>
+        <v>1.0699999999999996</v>
       </c>
       <c r="AD14" s="29">
         <f t="shared" si="6"/>
-        <v>0.91999000000000009</v>
+        <v>1.0699899999999996</v>
       </c>
       <c r="AE14" s="29">
         <f t="shared" si="7"/>
-        <v>0.92000999999999999</v>
+        <v>1.0700099999999997</v>
       </c>
       <c r="AF14" s="30">
         <f t="shared" si="8"/>
-        <v>0.14327787743809378</v>
+        <v>0.10220770020190074</v>
       </c>
       <c r="AG14" s="30">
         <f t="shared" si="9"/>
-        <v>0.14328722369270921</v>
+        <v>0.10221429832710345</v>
       </c>
       <c r="AH14" s="30">
         <f t="shared" si="10"/>
-        <v>0.14326853192996375</v>
+        <v>0.10220110278440156</v>
       </c>
       <c r="AI14" s="31">
         <f t="shared" si="11"/>
-        <v>0.16586822831690873</v>
+        <v>8.9009170401493476E-2</v>
       </c>
       <c r="AJ14" s="31">
         <f t="shared" si="12"/>
-        <v>0.16587813577466703</v>
+        <v>8.9018887481422726E-2</v>
       </c>
       <c r="AK14" s="31">
         <f t="shared" si="13"/>
-        <v>0.16585832086749253</v>
+        <v>8.8999453410231077E-2</v>
       </c>
       <c r="AL14" s="5">
         <f t="shared" si="14"/>
-        <v>8.3421047847309623E-2</v>
+        <v>0.88666851638663491</v>
       </c>
       <c r="AM14" s="3">
         <f t="shared" si="15"/>
-        <v>4.2420892364859199E-4</v>
+        <v>4.4774694091237605E-3</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="U15" s="3">
         <f t="shared" si="0"/>
-        <v>7.7311497171383275E-2</v>
+        <v>0.11684478058710904</v>
       </c>
       <c r="Y15" s="23">
         <f t="shared" si="4"/>
@@ -8450,47 +8450,47 @@
       </c>
       <c r="AC15" s="29">
         <f t="shared" si="16"/>
-        <v>0.92500000000000004</v>
+        <v>1.0749999999999995</v>
       </c>
       <c r="AD15" s="29">
         <f t="shared" si="6"/>
-        <v>0.92499000000000009</v>
+        <v>1.0749899999999994</v>
       </c>
       <c r="AE15" s="29">
         <f t="shared" si="7"/>
-        <v>0.92501</v>
+        <v>1.0750099999999996</v>
       </c>
       <c r="AF15" s="30">
         <f t="shared" si="8"/>
-        <v>0.13869776566484873</v>
+        <v>9.8996877787895399E-2</v>
       </c>
       <c r="AG15" s="30">
         <f t="shared" si="9"/>
-        <v>0.1387067415568933</v>
+        <v>9.9003124451268298E-2</v>
       </c>
       <c r="AH15" s="30">
         <f t="shared" si="10"/>
-        <v>0.1386887905077836</v>
+        <v>9.8990631822674133E-2</v>
       </c>
       <c r="AI15" s="31">
         <f t="shared" si="11"/>
-        <v>0.1609155425152613</v>
+        <v>8.4162397166306913E-2</v>
       </c>
       <c r="AJ15" s="31">
         <f t="shared" si="12"/>
-        <v>0.16092544580922497</v>
+        <v>8.4172065879051683E-2</v>
       </c>
       <c r="AK15" s="31">
         <f t="shared" si="13"/>
-        <v>0.16090563922963763</v>
+        <v>8.4152728559008905E-2</v>
       </c>
       <c r="AL15" s="5">
         <f t="shared" si="14"/>
-        <v>8.3399953609841745E-2</v>
+        <v>1.054467624328481</v>
       </c>
       <c r="AM15" s="3">
         <f t="shared" si="15"/>
-        <v>4.2410165619029039E-4</v>
+        <v>5.3248158061173561E-3</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="U16" s="3">
         <f t="shared" si="0"/>
-        <v>7.6245128709093835E-2</v>
+        <v>0.10916256172609889</v>
       </c>
       <c r="Y16" s="23">
         <f t="shared" si="4"/>
@@ -8512,70 +8512,70 @@
       </c>
       <c r="AC16" s="29">
         <f t="shared" si="16"/>
-        <v>0.93</v>
+        <v>1.0799999999999994</v>
       </c>
       <c r="AD16" s="29">
         <f t="shared" si="6"/>
-        <v>0.92999000000000009</v>
+        <v>1.0799899999999993</v>
       </c>
       <c r="AE16" s="29">
         <f t="shared" si="7"/>
-        <v>0.93001</v>
+        <v>1.0800099999999995</v>
       </c>
       <c r="AF16" s="30">
         <f t="shared" si="8"/>
-        <v>0.134301403357591</v>
+        <v>9.5960596611223803E-2</v>
       </c>
       <c r="AG16" s="30">
         <f t="shared" si="9"/>
-        <v>0.13431001458444242</v>
+        <v>9.5966496548683666E-2</v>
       </c>
       <c r="AH16" s="30">
         <f t="shared" si="10"/>
-        <v>0.13429279285443502</v>
+        <v>9.5954697362523572E-2</v>
       </c>
       <c r="AI16" s="31">
         <f t="shared" si="11"/>
-        <v>0.15596494541257755</v>
+        <v>7.9342069852179731E-2</v>
       </c>
       <c r="AJ16" s="31">
         <f t="shared" si="12"/>
-        <v>0.15597484450108712</v>
+        <v>7.9351680830139881E-2</v>
       </c>
       <c r="AK16" s="31">
         <f t="shared" si="13"/>
-        <v>0.15595504633258095</v>
+        <v>7.9332459000492794E-2</v>
       </c>
       <c r="AL16" s="5">
         <f t="shared" si="14"/>
-        <v>8.5129681082207739E-2</v>
+        <v>1.2627321410718648</v>
       </c>
       <c r="AM16" s="3">
         <f t="shared" si="15"/>
-        <v>4.3289758777102089E-4</v>
+        <v>6.3765030888964661E-3</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A17" s="35" t="s">
+      <c r="A17" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35" t="s">
+      <c r="B17" s="33"/>
+      <c r="C17" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35" t="s">
+      <c r="D17" s="33"/>
+      <c r="E17" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="35"/>
-      <c r="G17" s="35"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
       <c r="T17" s="5">
         <f t="shared" si="3"/>
         <v>1.07</v>
       </c>
       <c r="U17" s="3">
         <f t="shared" si="0"/>
-        <v>7.5672308824755355E-2</v>
+        <v>0.10220770020190049</v>
       </c>
       <c r="Y17" s="23">
         <f t="shared" si="4"/>
@@ -8587,47 +8587,47 @@
       </c>
       <c r="AC17" s="29">
         <f t="shared" si="16"/>
-        <v>0.93500000000000005</v>
+        <v>1.0849999999999993</v>
       </c>
       <c r="AD17" s="29">
         <f t="shared" si="6"/>
-        <v>0.9349900000000001</v>
+        <v>1.0849899999999992</v>
       </c>
       <c r="AE17" s="29">
         <f t="shared" si="7"/>
-        <v>0.93501000000000001</v>
+        <v>1.0850099999999994</v>
       </c>
       <c r="AF17" s="30">
         <f t="shared" si="8"/>
-        <v>0.13008596941702988</v>
+        <v>9.3096508596664615E-2</v>
       </c>
       <c r="AG17" s="30">
         <f t="shared" si="9"/>
-        <v>0.13009422156637085</v>
+        <v>9.3102066465030275E-2</v>
       </c>
       <c r="AH17" s="30">
         <f t="shared" si="10"/>
-        <v>0.13007771798031709</v>
+        <v>9.3090951407823072E-2</v>
       </c>
       <c r="AI17" s="31">
         <f t="shared" si="11"/>
-        <v>0.15101648081336261</v>
+        <v>7.4553412109876427E-2</v>
       </c>
       <c r="AJ17" s="31">
         <f t="shared" si="12"/>
-        <v>0.15102637556066412</v>
+        <v>7.4562953762360218E-2</v>
       </c>
       <c r="AK17" s="31">
         <f t="shared" si="13"/>
-        <v>0.1510065860749501</v>
+        <v>7.4543870609356522E-2</v>
       </c>
       <c r="AL17" s="5">
         <f t="shared" si="14"/>
-        <v>8.8890006466613145E-2</v>
+        <v>1.5196388591931507</v>
       </c>
       <c r="AM17" s="3">
         <f t="shared" si="15"/>
-        <v>4.5201942362720451E-4</v>
+        <v>7.6738221547341988E-3</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="U18" s="3">
         <f t="shared" si="0"/>
-        <v>7.5579377836803907E-2</v>
+        <v>9.5960596611223428E-2</v>
       </c>
       <c r="Y18" s="23">
         <f t="shared" si="4"/>
@@ -8670,47 +8670,47 @@
       </c>
       <c r="AC18" s="29">
         <f t="shared" si="16"/>
-        <v>0.94000000000000006</v>
+        <v>1.0899999999999992</v>
       </c>
       <c r="AD18" s="29">
         <f t="shared" si="6"/>
-        <v>0.9399900000000001</v>
+        <v>1.0899899999999991</v>
       </c>
       <c r="AE18" s="29">
         <f t="shared" si="7"/>
-        <v>0.94001000000000001</v>
+        <v>1.0900099999999993</v>
       </c>
       <c r="AF18" s="30">
         <f t="shared" si="8"/>
-        <v>0.12604869693067658</v>
+        <v>9.0402304805819303E-2</v>
       </c>
       <c r="AG18" s="30">
         <f t="shared" si="9"/>
-        <v>0.1260565954831197</v>
+        <v>9.0407525184450055E-2</v>
       </c>
       <c r="AH18" s="30">
         <f t="shared" si="10"/>
-        <v>0.12604079908000598</v>
+        <v>9.0397085097630558E-2</v>
       </c>
       <c r="AI18" s="31">
         <f t="shared" si="11"/>
-        <v>0.14607024352456122</v>
+        <v>6.9802865619030707E-2</v>
       </c>
       <c r="AJ18" s="31">
         <f t="shared" si="12"/>
-        <v>0.14608013368423445</v>
+        <v>6.9812323699457335E-2</v>
       </c>
       <c r="AK18" s="31">
         <f t="shared" si="13"/>
-        <v>0.14606035337439471</v>
+        <v>6.9793407722033352E-2</v>
       </c>
       <c r="AL18" s="5">
         <f t="shared" si="14"/>
-        <v>9.5067287375627516E-2</v>
+        <v>1.8342927177172894</v>
       </c>
       <c r="AM18" s="3">
         <f t="shared" si="15"/>
-        <v>4.8343185194247039E-4</v>
+        <v>9.2627508242058149E-3</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -8718,25 +8718,25 @@
         <v>4</v>
       </c>
       <c r="B19" s="20">
-        <v>7.5499999999999998E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D19" s="13">
         <f>B19 + B23 - B21/2</f>
-        <v>8.0499999999999988E-2</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="E19" s="14">
         <v>0.9</v>
       </c>
       <c r="F19" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(E19 * EXP($B$4*$B$2), 0, 1) * D19 * SQRT($B$2) - ($B$3 - $B$4 + D19^2/2)*$B$2)</f>
-        <v>1.0323369799876165</v>
+        <v>1.0949090068168106</v>
       </c>
       <c r="G19" s="16">
         <f t="shared" ref="G19:G21" si="17">EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(1/(D19*SQRT($B$2)) * (LN($B$1 / F19) + ($B$3 - $B$4 + D19^2/2)*$B$2), 0, 1, 1)</f>
-        <v>0.9</v>
+        <v>0.90000000000000024</v>
       </c>
       <c r="T19" s="5">
         <f t="shared" si="3"/>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="U19" s="3">
         <f t="shared" si="0"/>
-        <v>7.595313591289736E-2</v>
+        <v>9.04023048058189E-2</v>
       </c>
       <c r="Y19" s="23">
         <f t="shared" si="4"/>
@@ -8756,47 +8756,47 @@
       </c>
       <c r="AC19" s="29">
         <f t="shared" si="16"/>
-        <v>0.94500000000000006</v>
+        <v>1.0949999999999991</v>
       </c>
       <c r="AD19" s="29">
         <f t="shared" si="6"/>
-        <v>0.94499000000000011</v>
+        <v>1.094989999999999</v>
       </c>
       <c r="AE19" s="29">
         <f t="shared" si="7"/>
-        <v>0.94501000000000002</v>
+        <v>1.0950099999999992</v>
       </c>
       <c r="AF19" s="30">
         <f t="shared" si="8"/>
-        <v>0.12218687187934571</v>
+        <v>8.7875714628185456E-2</v>
       </c>
       <c r="AG19" s="30">
         <f t="shared" si="9"/>
-        <v>0.12219442221098296</v>
+        <v>8.788060202057868E-2</v>
       </c>
       <c r="AH19" s="30">
         <f t="shared" si="10"/>
-        <v>0.12217932223883189</v>
+        <v>8.7870827897302134E-2</v>
       </c>
       <c r="AI19" s="31">
         <f t="shared" si="11"/>
-        <v>0.14112638893324314</v>
+        <v>6.5098316813156698E-2</v>
       </c>
       <c r="AJ19" s="31">
         <f t="shared" si="12"/>
-        <v>0.14113627412623542</v>
+        <v>6.5107673948037403E-2</v>
       </c>
       <c r="AK19" s="31">
         <f t="shared" si="13"/>
-        <v>0.1411165037506662</v>
+        <v>6.5088959899909926E-2</v>
       </c>
       <c r="AL19" s="5">
         <f t="shared" si="14"/>
-        <v>0.1041533526091598</v>
+        <v>2.2163393342822242</v>
       </c>
       <c r="AM19" s="3">
         <f t="shared" si="15"/>
-        <v>5.2963589819195569E-4</v>
+        <v>1.1191997218901097E-2</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -8804,25 +8804,25 @@
         <v>6</v>
       </c>
       <c r="B20" s="20">
-        <v>3.5000000000000001E-3</v>
+        <v>-8.0000000000000002E-3</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>18</v>
       </c>
       <c r="D20" s="13">
         <f>B19+B22 - B20/2</f>
-        <v>7.6249999999999998E-2</v>
+        <v>7.6000000000000012E-2</v>
       </c>
       <c r="E20" s="14">
         <v>0.75</v>
       </c>
       <c r="F20" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(E20 * EXP($B$4*$B$2), 0, 1) * D20 * SQRT($B$2) - ($B$3 - $B$4 + D20^2/2)*$B$2)</f>
-        <v>1.0600347861818515</v>
+        <v>1.1293039487620771</v>
       </c>
       <c r="G20" s="16">
         <f t="shared" si="17"/>
-        <v>0.75000000000000078</v>
+        <v>0.75000000000000044</v>
       </c>
       <c r="T20" s="5">
         <f t="shared" si="3"/>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="U20" s="3">
         <f t="shared" si="0"/>
-        <v>7.6780824030620323E-2</v>
+        <v>8.5514504992336121E-2</v>
       </c>
       <c r="Y20" s="23">
         <f t="shared" si="4"/>
@@ -8842,47 +8842,47 @@
       </c>
       <c r="AC20" s="29">
         <f t="shared" si="16"/>
-        <v>0.95000000000000007</v>
+        <v>1.099999999999999</v>
       </c>
       <c r="AD20" s="29">
         <f t="shared" si="6"/>
-        <v>0.94999000000000011</v>
+        <v>1.0999899999999989</v>
       </c>
       <c r="AE20" s="29">
         <f t="shared" si="7"/>
-        <v>0.95001000000000002</v>
+        <v>1.100009999999999</v>
       </c>
       <c r="AF20" s="30">
         <f t="shared" si="8"/>
-        <v>0.11849783188080916</v>
+        <v>8.5514504992336648E-2</v>
       </c>
       <c r="AG20" s="30">
         <f t="shared" si="9"/>
-        <v>0.11850503926568834</v>
+        <v>8.5519063827685676E-2</v>
       </c>
       <c r="AH20" s="30">
         <f t="shared" si="10"/>
-        <v>0.11849062517660591</v>
+        <v>8.550994680971255E-2</v>
       </c>
       <c r="AI20" s="31">
         <f t="shared" si="11"/>
-        <v>0.13618514567090811</v>
+        <v>6.0449337004196191E-2</v>
       </c>
       <c r="AJ20" s="31">
         <f t="shared" si="12"/>
-        <v>0.13619502535655059</v>
+        <v>6.0458572209214245E-2</v>
       </c>
       <c r="AK20" s="31">
         <f t="shared" si="13"/>
-        <v>0.13617526599694862</v>
+        <v>6.044010206671302E-2</v>
       </c>
       <c r="AL20" s="5">
         <f t="shared" si="14"/>
-        <v>0.11682987910432983</v>
+        <v>2.6753488313602243</v>
       </c>
       <c r="AM20" s="3">
         <f t="shared" si="15"/>
-        <v>5.9409799497551184E-4</v>
+        <v>1.3509888227413967E-2</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -8890,25 +8890,25 @@
         <v>8</v>
       </c>
       <c r="B21" s="20">
-        <v>7.0000000000000001E-3</v>
+        <v>-1.4999999999999999E-2</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>4</v>
       </c>
       <c r="D21" s="13">
         <f>B19</f>
-        <v>7.5499999999999998E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="E21" s="14">
         <v>0.5</v>
       </c>
       <c r="F21" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(E21 * EXP($B$4*$B$2), 0, 1) * D21 * SQRT($B$2) - ($B$3 - $B$4 + D21^2/2)*$B$2)</f>
-        <v>1.0879017903763666</v>
+        <v>1.1587614138335498</v>
       </c>
       <c r="G21" s="16">
         <f t="shared" si="17"/>
-        <v>0.49999999999999944</v>
+        <v>0.50000000000000022</v>
       </c>
       <c r="T21" s="5">
         <f t="shared" si="3"/>
@@ -8916,7 +8916,7 @@
       </c>
       <c r="U21" s="3">
         <f t="shared" si="0"/>
-        <v>7.8050105880476228E-2</v>
+        <v>8.1279478158845161E-2</v>
       </c>
       <c r="Y21" s="23">
         <f t="shared" si="4"/>
@@ -8928,47 +8928,47 @@
       </c>
       <c r="AC21" s="29">
         <f t="shared" si="16"/>
-        <v>0.95500000000000007</v>
+        <v>1.1049999999999989</v>
       </c>
       <c r="AD21" s="29">
         <f t="shared" si="6"/>
-        <v>0.95499000000000012</v>
+        <v>1.1049899999999988</v>
       </c>
       <c r="AE21" s="29">
         <f t="shared" si="7"/>
-        <v>0.95501000000000003</v>
+        <v>1.1050099999999989</v>
       </c>
       <c r="AF21" s="30">
         <f t="shared" si="8"/>
-        <v>0.11497896496935535</v>
+        <v>8.3316479596625886E-2</v>
       </c>
       <c r="AG21" s="30">
         <f t="shared" si="9"/>
-        <v>0.11498583458188599</v>
+        <v>8.332071423133966E-2</v>
       </c>
       <c r="AH21" s="30">
         <f t="shared" si="10"/>
-        <v>0.1149720960272501</v>
+        <v>8.3312245605996163E-2</v>
       </c>
       <c r="AI21" s="31">
         <f t="shared" si="11"/>
-        <v>0.13124683229345424</v>
+        <v>5.58674190748496E-2</v>
       </c>
       <c r="AJ21" s="31">
         <f t="shared" si="12"/>
-        <v>0.13125670573134662</v>
+        <v>5.5876507300746669E-2</v>
       </c>
       <c r="AK21" s="31">
         <f t="shared" si="13"/>
-        <v>0.13123695886895637</v>
+        <v>5.5858331170923758E-2</v>
       </c>
       <c r="AL21" s="5">
         <f t="shared" si="14"/>
-        <v>0.13394507725195123</v>
+        <v>3.2197122745714064</v>
       </c>
       <c r="AM21" s="3">
         <f t="shared" si="15"/>
-        <v>6.8113142324800269E-4</v>
+        <v>1.625879677596169E-2</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -8976,25 +8976,25 @@
         <v>7</v>
       </c>
       <c r="B22" s="20">
-        <v>2.5000000000000001E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>19</v>
       </c>
       <c r="D22" s="13">
         <f>B19 + B22 + B20/2</f>
-        <v>7.9750000000000001E-2</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="E22" s="14">
         <v>0.25</v>
       </c>
       <c r="F22" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(E22 * EXP($B$4*$B$2), 0, 1) * D22 * SQRT($B$2) - ($B$3 - $B$4 + D22^2/2)*$B$2)</f>
-        <v>1.1177534735320678</v>
+        <v>1.1857247812154261</v>
       </c>
       <c r="G22" s="16">
         <f>EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(1/(D22*SQRT($B$2)) * (LN($B$1 / F22) + ($B$3 - $B$4 + D22^2/2)*$B$2), 0, 1, 1)</f>
-        <v>0.24999999999999961</v>
+        <v>0.25000000000000094</v>
       </c>
       <c r="T22" s="5">
         <f t="shared" si="3"/>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="U22" s="3">
         <f t="shared" si="0"/>
-        <v>7.9749050656852713E-2</v>
+        <v>7.7680081751746344E-2</v>
       </c>
       <c r="Y22" s="23">
         <f t="shared" si="4"/>
@@ -9014,47 +9014,47 @@
       </c>
       <c r="AC22" s="29">
         <f t="shared" si="16"/>
-        <v>0.96000000000000008</v>
+        <v>1.1099999999999988</v>
       </c>
       <c r="AD22" s="29">
         <f t="shared" si="6"/>
-        <v>0.95999000000000012</v>
+        <v>1.1099899999999987</v>
       </c>
       <c r="AE22" s="29">
         <f t="shared" si="7"/>
-        <v>0.96001000000000003</v>
+        <v>1.1100099999999988</v>
       </c>
       <c r="AF22" s="30">
         <f t="shared" si="8"/>
-        <v>0.11162770841005135</v>
+        <v>8.1279478158845717E-2</v>
       </c>
       <c r="AG22" s="30">
         <f t="shared" si="9"/>
-        <v>0.11163424532734229</v>
+        <v>8.1283392878030741E-2</v>
       </c>
       <c r="AH22" s="30">
         <f t="shared" si="10"/>
-        <v>0.11162117215312753</v>
+        <v>8.1275564075245027E-2</v>
       </c>
       <c r="AI22" s="31">
         <f t="shared" si="11"/>
-        <v>0.12631187917427145</v>
+        <v>5.1366184184738484E-2</v>
       </c>
       <c r="AJ22" s="31">
         <f t="shared" si="12"/>
-        <v>0.12632174537434049</v>
+        <v>5.1375095956986305E-2</v>
       </c>
       <c r="AK22" s="31">
         <f t="shared" si="13"/>
-        <v>0.12630201298986798</v>
+        <v>5.1357272798005837E-2</v>
       </c>
       <c r="AL22" s="5">
         <f t="shared" si="14"/>
-        <v>0.15665579944368344</v>
+        <v>3.8551517533846886</v>
       </c>
       <c r="AM22" s="3">
         <f t="shared" si="15"/>
-        <v>7.9661895624891569E-4</v>
+        <v>1.9467618083084063E-2</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -9062,25 +9062,25 @@
         <v>9</v>
       </c>
       <c r="B23" s="20">
-        <v>8.5000000000000006E-3</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>20</v>
       </c>
       <c r="D23" s="13">
         <f>B19 + B23 + B21/2</f>
-        <v>8.7499999999999994E-2</v>
+        <v>7.2500000000000009E-2</v>
       </c>
       <c r="E23" s="14">
         <v>0.1</v>
       </c>
       <c r="F23" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(E23 * EXP($B$4*$B$2), 0, 1) * D23 * SQRT($B$2) - ($B$3 - $B$4 + D23^2/2)*$B$2)</f>
-        <v>1.1510707999322727</v>
+        <v>1.2140828375149078</v>
       </c>
       <c r="G23" s="16">
         <f>EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(1/(D23*SQRT($B$2)) * (LN($B$1 / F23) + ($B$3 - $B$4 + D23^2/2)*$B$2), 0, 1, 1)</f>
-        <v>9.9999999999999784E-2</v>
+        <v>9.9999999999999215E-2</v>
       </c>
       <c r="S23" s="9"/>
       <c r="T23" s="5">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="U23" s="3">
         <f t="shared" si="0"/>
-        <v>8.1866116686218071E-2</v>
+        <v>7.4699726531794922E-2</v>
       </c>
       <c r="V23" s="9"/>
       <c r="W23" s="9"/>
@@ -9103,47 +9103,47 @@
       </c>
       <c r="AC23" s="29">
         <f t="shared" si="16"/>
-        <v>0.96500000000000008</v>
+        <v>1.1149999999999987</v>
       </c>
       <c r="AD23" s="29">
         <f t="shared" si="6"/>
-        <v>0.96499000000000013</v>
+        <v>1.1149899999999986</v>
       </c>
       <c r="AE23" s="29">
         <f t="shared" si="7"/>
-        <v>0.96501000000000003</v>
+        <v>1.1150099999999987</v>
       </c>
       <c r="AF23" s="30">
         <f t="shared" si="8"/>
-        <v>0.10844154754655211</v>
+        <v>7.9401375684298225E-2</v>
       </c>
       <c r="AG23" s="30">
         <f t="shared" si="9"/>
-        <v>0.10844775675068316</v>
+        <v>7.9404974703204484E-2</v>
       </c>
       <c r="AH23" s="30">
         <f t="shared" si="10"/>
-        <v>0.10843533899291775</v>
+        <v>7.9397777292614852E-2</v>
       </c>
       <c r="AI23" s="31">
         <f t="shared" si="11"/>
-        <v>0.12138085714146374</v>
+        <v>4.696152077333593E-2</v>
       </c>
       <c r="AJ23" s="31">
         <f t="shared" si="12"/>
-        <v>0.12139071479874519</v>
+        <v>4.6970222012392981E-2</v>
       </c>
       <c r="AK23" s="31">
         <f t="shared" si="13"/>
-        <v>0.12137099950282637</v>
+        <v>4.6952819992554962E-2</v>
       </c>
       <c r="AL23" s="5">
         <f t="shared" si="14"/>
-        <v>0.18644086274832714</v>
+        <v>4.5827608374793263</v>
       </c>
       <c r="AM23" s="3">
         <f t="shared" si="15"/>
-        <v>9.4808060737076221E-4</v>
+        <v>2.3141874420853591E-2</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -9159,7 +9159,7 @@
       </c>
       <c r="U24" s="3">
         <f t="shared" si="0"/>
-        <v>8.4390135845114941E-2</v>
+        <v>7.2322354542605466E-2</v>
       </c>
       <c r="Y24" s="23">
         <f t="shared" si="4"/>
@@ -9171,47 +9171,47 @@
       </c>
       <c r="AC24" s="29">
         <f t="shared" si="16"/>
-        <v>0.97000000000000008</v>
+        <v>1.1199999999999986</v>
       </c>
       <c r="AD24" s="29">
         <f t="shared" si="6"/>
-        <v>0.96999000000000013</v>
+        <v>1.1199899999999985</v>
       </c>
       <c r="AE24" s="29">
         <f t="shared" si="7"/>
-        <v>0.97001000000000004</v>
+        <v>1.1200099999999986</v>
       </c>
       <c r="AF24" s="30">
         <f t="shared" si="8"/>
-        <v>0.10541801468134732</v>
+        <v>7.7680081751746843E-2</v>
       </c>
       <c r="AG24" s="30">
         <f t="shared" si="9"/>
-        <v>0.10542390106157713</v>
+        <v>7.7683369217178402E-2</v>
       </c>
       <c r="AH24" s="30">
         <f t="shared" si="10"/>
-        <v>0.10541212894192725</v>
+        <v>7.7676794905312235E-2</v>
       </c>
       <c r="AI24" s="31">
         <f t="shared" si="11"/>
-        <v>0.11645451479359858</v>
+        <v>4.2671607253569332E-2</v>
       </c>
       <c r="AJ24" s="31">
         <f t="shared" si="12"/>
-        <v>0.11646436220343059</v>
+        <v>4.2680059382265823E-2</v>
       </c>
       <c r="AK24" s="31">
         <f t="shared" si="13"/>
-        <v>0.11644466740628912</v>
+        <v>4.2663155664546593E-2</v>
       </c>
       <c r="AL24" s="5">
         <f t="shared" si="14"/>
-        <v>0.22522539389058235</v>
+        <v>5.3967375013286292</v>
       </c>
       <c r="AM24" s="3">
         <f t="shared" si="15"/>
-        <v>1.1453059435974876E-3</v>
+        <v>2.7252266912264268E-2</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="U25" s="3">
         <f t="shared" si="0"/>
-        <v>8.7310298723581356E-2</v>
+        <v>7.0532418129298391E-2</v>
       </c>
       <c r="Y25" s="23">
         <f t="shared" si="4"/>
@@ -9242,47 +9242,47 @@
       </c>
       <c r="AC25" s="29">
         <f t="shared" si="16"/>
-        <v>0.97500000000000009</v>
+        <v>1.1249999999999984</v>
       </c>
       <c r="AD25" s="29">
         <f t="shared" si="6"/>
-        <v>0.97499000000000013</v>
+        <v>1.1249899999999984</v>
       </c>
       <c r="AE25" s="29">
         <f t="shared" si="7"/>
-        <v>0.97501000000000004</v>
+        <v>1.1250099999999985</v>
       </c>
       <c r="AF25" s="30">
         <f t="shared" si="8"/>
-        <v>0.10255468798737583</v>
+        <v>7.6113539816737463E-2</v>
       </c>
       <c r="AG25" s="30">
         <f t="shared" si="9"/>
-        <v>0.10256025634228799</v>
+        <v>7.6116519808428776E-2</v>
       </c>
       <c r="AH25" s="30">
         <f t="shared" si="10"/>
-        <v>0.10254912026376567</v>
+        <v>7.6110560435949895E-2</v>
       </c>
       <c r="AI25" s="31">
         <f t="shared" si="11"/>
-        <v>0.11153382689783764</v>
+        <v>3.8516762151635797E-2</v>
       </c>
       <c r="AJ25" s="31">
         <f t="shared" si="12"/>
-        <v>0.11154366184615239</v>
+        <v>3.8524922605656098E-2</v>
       </c>
       <c r="AK25" s="31">
         <f t="shared" si="13"/>
-        <v>0.11152399197707275</v>
+        <v>3.850860232582487E-2</v>
       </c>
       <c r="AL25" s="5">
         <f t="shared" si="14"/>
-        <v>0.27549851289165866</v>
+        <v>6.2820937341001573</v>
       </c>
       <c r="AM25" s="3">
         <f t="shared" si="15"/>
-        <v>1.4009525250086793E-3</v>
+        <v>3.1723109594901024E-2</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="U26" s="3">
         <f t="shared" si="0"/>
-        <v>9.0616140492473851E-2</v>
+        <v>6.9314859948939017E-2</v>
       </c>
       <c r="Y26" s="23">
         <f t="shared" si="4"/>
@@ -9313,47 +9313,47 @@
       </c>
       <c r="AC26" s="29">
         <f t="shared" si="16"/>
-        <v>0.98000000000000009</v>
+        <v>1.1299999999999983</v>
       </c>
       <c r="AD26" s="29">
         <f t="shared" si="6"/>
-        <v>0.97999000000000014</v>
+        <v>1.1299899999999983</v>
       </c>
       <c r="AE26" s="29">
         <f t="shared" si="7"/>
-        <v>0.98001000000000005</v>
+        <v>1.1300099999999984</v>
       </c>
       <c r="AF26" s="30">
         <f t="shared" si="8"/>
-        <v>9.9849190449978725E-2</v>
+        <v>7.4699726531795407E-2</v>
       </c>
       <c r="AG26" s="30">
         <f t="shared" si="9"/>
-        <v>9.9854445489568372E-2</v>
+        <v>7.4702403063754474E-2</v>
       </c>
       <c r="AH26" s="30">
         <f t="shared" si="10"/>
-        <v>9.9843936032358555E-2</v>
+        <v>7.4697050602777038E-2</v>
       </c>
       <c r="AI26" s="31">
         <f t="shared" si="11"/>
-        <v>0.1066200567894634</v>
+        <v>3.4519065216681244E-2</v>
       </c>
       <c r="AJ26" s="31">
         <f t="shared" si="12"/>
-        <v>0.1066298764118131</v>
+        <v>3.4526888464055383E-2</v>
       </c>
       <c r="AK26" s="31">
         <f t="shared" si="13"/>
-        <v>0.10661023720115648</v>
+        <v>3.4511242690586141E-2</v>
       </c>
       <c r="AL26" s="5">
         <f t="shared" si="14"/>
-        <v>0.34042768604081169</v>
+        <v>7.2127903649743521</v>
       </c>
       <c r="AM26" s="3">
         <f t="shared" si="15"/>
-        <v>1.7311274073166765E-3</v>
+        <v>3.6422910723394736E-2</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="U27" s="3">
         <f t="shared" si="0"/>
-        <v>9.4297527435806633E-2</v>
+        <v>6.8655093918120372E-2</v>
       </c>
       <c r="Y27" s="23">
         <f t="shared" si="4"/>
@@ -9381,54 +9381,54 @@
       </c>
       <c r="AC27" s="29">
         <f t="shared" si="16"/>
-        <v>0.9850000000000001</v>
+        <v>1.1349999999999982</v>
       </c>
       <c r="AD27" s="29">
         <f t="shared" si="6"/>
-        <v>0.98499000000000014</v>
+        <v>1.1349899999999982</v>
       </c>
       <c r="AE27" s="29">
         <f t="shared" si="7"/>
-        <v>0.98501000000000005</v>
+        <v>1.1350099999999983</v>
       </c>
       <c r="AF27" s="30">
         <f t="shared" si="8"/>
-        <v>9.7299188838202544E-2</v>
+        <v>7.3436651083018736E-2</v>
       </c>
       <c r="AG27" s="30">
         <f t="shared" si="9"/>
-        <v>9.7304135185904889E-2</v>
+        <v>7.343902810483785E-2</v>
       </c>
       <c r="AH27" s="30">
         <f t="shared" si="10"/>
-        <v>9.729424310330817E-2</v>
+        <v>7.3434274656304838E-2</v>
       </c>
       <c r="AI27" s="31">
         <f t="shared" si="11"/>
-        <v>0.10171483620419064</v>
+        <v>3.0701704841953226E-2</v>
       </c>
       <c r="AJ27" s="31">
         <f t="shared" si="12"/>
-        <v>0.10172463680617949</v>
+        <v>3.0709143979019027E-2</v>
       </c>
       <c r="AK27" s="31">
         <f t="shared" si="13"/>
-        <v>0.10170503564460753</v>
+        <v>3.0694266519987079E-2</v>
       </c>
       <c r="AL27" s="5">
         <f t="shared" si="14"/>
-        <v>0.42405745581675086</v>
+        <v>8.1509965443871106</v>
       </c>
       <c r="AM27" s="3">
         <f t="shared" si="15"/>
-        <v>2.1563977142368845E-3</v>
+        <v>4.1160633322242193E-2</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="35"/>
+      <c r="B28" s="33"/>
       <c r="D28" t="s">
         <v>56</v>
       </c>
@@ -9441,7 +9441,7 @@
       </c>
       <c r="U28" s="3">
         <f t="shared" si="0"/>
-        <v>9.8344644111669544E-2</v>
+        <v>6.8538987046476971E-2</v>
       </c>
       <c r="Y28" s="23">
         <f t="shared" si="4"/>
@@ -9453,47 +9453,47 @@
       </c>
       <c r="AC28" s="29">
         <f t="shared" si="16"/>
-        <v>0.9900000000000001</v>
+        <v>1.1399999999999981</v>
       </c>
       <c r="AD28" s="29">
         <f t="shared" si="6"/>
-        <v>0.98999000000000015</v>
+        <v>1.1399899999999981</v>
       </c>
       <c r="AE28" s="29">
         <f t="shared" si="7"/>
-        <v>0.99001000000000006</v>
+        <v>1.1400099999999982</v>
       </c>
       <c r="AF28" s="30">
         <f t="shared" si="8"/>
-        <v>9.4902392704498378E-2</v>
+        <v>7.2322354542605896E-2</v>
       </c>
       <c r="AG28" s="30">
         <f t="shared" si="9"/>
-        <v>9.4907034899161774E-2</v>
+        <v>7.2324435940740908E-2</v>
       </c>
       <c r="AH28" s="30">
         <f t="shared" si="10"/>
-        <v>9.4897751113648718E-2</v>
+        <v>7.2320273731865614E-2</v>
       </c>
       <c r="AI28" s="31">
         <f t="shared" si="11"/>
-        <v>9.6820266391547394E-2</v>
+        <v>2.7088034657307358E-2</v>
       </c>
       <c r="AJ28" s="31">
         <f t="shared" si="12"/>
-        <v>9.6830043222685847E-2</v>
+        <v>2.7095043576798261E-2</v>
       </c>
       <c r="AK28" s="31">
         <f t="shared" si="13"/>
-        <v>9.6810489613551987E-2</v>
+        <v>2.7081026642630901E-2</v>
       </c>
       <c r="AL28" s="5">
         <f t="shared" si="14"/>
-        <v>0.53143045519732357</v>
+        <v>9.0481444559031825</v>
       </c>
       <c r="AM28" s="3">
         <f t="shared" si="15"/>
-        <v>2.7024060139590827E-3</v>
+        <v>4.5691021235013056E-2</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="E29" s="16">
         <f>INDEX(LINEST(D19:D23, A30:B34, 1, 0), 3)</f>
-        <v>7.5812924652568087E-2</v>
+        <v>6.9478426720588835E-2</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="3"/>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="U29" s="3">
         <f t="shared" si="0"/>
-        <v>0.10274798110756644</v>
+        <v>6.8952842108113269E-2</v>
       </c>
       <c r="Y29" s="23">
         <f t="shared" si="4"/>
@@ -9531,64 +9531,64 @@
       </c>
       <c r="AC29" s="29">
         <f t="shared" si="16"/>
-        <v>0.99500000000000011</v>
+        <v>1.144999999999998</v>
       </c>
       <c r="AD29" s="29">
         <f t="shared" si="6"/>
-        <v>0.99499000000000015</v>
+        <v>1.144989999999998</v>
       </c>
       <c r="AE29" s="29">
         <f t="shared" si="7"/>
-        <v>0.99501000000000006</v>
+        <v>1.1450099999999981</v>
       </c>
       <c r="AF29" s="30">
         <f t="shared" si="8"/>
-        <v>9.2656553411899836E-2</v>
+        <v>7.1354909236868796E-2</v>
       </c>
       <c r="AG29" s="30">
         <f t="shared" si="9"/>
-        <v>9.2660895909704541E-2</v>
+        <v>7.1356698835887994E-2</v>
       </c>
       <c r="AH29" s="30">
         <f t="shared" si="10"/>
-        <v>9.2652211509078097E-2</v>
+        <v>7.1353120217656371E-2</v>
       </c>
       <c r="AI29" s="31">
         <f t="shared" si="11"/>
-        <v>9.1939044522222679E-2</v>
+        <v>2.3700365900843789E-2</v>
       </c>
       <c r="AJ29" s="31">
         <f t="shared" si="12"/>
-        <v>9.1948791495296112E-2</v>
+        <v>2.3706901926154544E-2</v>
       </c>
       <c r="AK29" s="31">
         <f t="shared" si="13"/>
-        <v>9.1929297616023642E-2</v>
+        <v>2.3693830860348819E-2</v>
       </c>
       <c r="AL29" s="5">
         <f t="shared" si="14"/>
-        <v>0.66874394910598756</v>
+        <v>9.8481578447717748</v>
       </c>
       <c r="AM29" s="3">
         <f t="shared" si="15"/>
-        <v>3.4006663566011398E-3</v>
+        <v>4.9730902441290817E-2</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A30" s="16">
         <f>LN(F19 / $B$5)</f>
-        <v>-5.1986035668809515E-2</v>
+        <v>-5.631290706777313E-2</v>
       </c>
       <c r="B30" s="16">
         <f>A30^2</f>
-        <v>2.7025479045587352E-3</v>
+        <v>3.171143502423653E-3</v>
       </c>
       <c r="D30" s="12" t="s">
         <v>26</v>
       </c>
       <c r="E30" s="16">
         <f>INDEX(LINEST(D19:D23, A30:B34, 1, 0), 2)</f>
-        <v>5.2789239141018386E-2</v>
+        <v>-0.11922747537162547</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="3"/>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="U30" s="3">
         <f t="shared" si="0"/>
-        <v>0.10749832335813374</v>
+        <v>6.9883381105899187E-2</v>
       </c>
       <c r="Y30" s="23">
         <f t="shared" si="4"/>
@@ -9611,64 +9611,64 @@
       </c>
       <c r="AC30" s="29">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>1.1499999999999979</v>
       </c>
       <c r="AD30" s="29">
         <f t="shared" si="6"/>
-        <v>0.99999000000000005</v>
+        <v>1.1499899999999978</v>
       </c>
       <c r="AE30" s="29">
         <f t="shared" si="7"/>
-        <v>1.0000100000000001</v>
+        <v>1.150009999999998</v>
       </c>
       <c r="AF30" s="30">
         <f t="shared" si="8"/>
-        <v>9.0559463187796729E-2</v>
+        <v>7.053241812929871E-2</v>
       </c>
       <c r="AG30" s="30">
         <f t="shared" si="9"/>
-        <v>9.0563510364121358E-2</v>
+        <v>7.0533919693101951E-2</v>
       </c>
       <c r="AH30" s="30">
         <f t="shared" si="10"/>
-        <v>9.0555416597784003E-2</v>
+        <v>7.0530917137834465E-2</v>
       </c>
       <c r="AI30" s="31">
         <f t="shared" si="11"/>
-        <v>8.707461907333347E-2</v>
+        <v>2.055857745259726E-2</v>
       </c>
       <c r="AJ30" s="31">
         <f t="shared" si="12"/>
-        <v>8.7084328422732504E-2</v>
+        <v>2.0564604216478544E-2</v>
       </c>
       <c r="AK30" s="31">
         <f t="shared" si="13"/>
-        <v>8.7064909808282631E-2</v>
+        <v>2.0552551738022173E-2</v>
       </c>
       <c r="AL30" s="5">
         <f t="shared" si="14"/>
-        <v>0.84348195095174094</v>
+        <v>10.493061974869986</v>
       </c>
       <c r="AM30" s="3">
         <f t="shared" si="15"/>
-        <v>4.2892361072373189E-3</v>
+        <v>5.2987518032086407E-2</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A31" s="16">
         <f>LN(F20 / $B$5)</f>
-        <v>-2.5509455686094796E-2</v>
+        <v>-2.5382699698755316E-2</v>
       </c>
       <c r="B31" s="16">
         <f>A31^2</f>
-        <v>6.5073232940083409E-4</v>
+        <v>6.442814439971932E-4</v>
       </c>
       <c r="D31" s="12" t="s">
         <v>27</v>
       </c>
       <c r="E31" s="16">
         <f>INDEX(LINEST(D19:D23, A30:B34, 1, 0), 1)</f>
-        <v>2.7292155617304821</v>
+        <v>3.6982679829872933</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="3"/>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="U31" s="3">
         <f t="shared" si="0"/>
-        <v>0.11258673899516657</v>
+        <v>7.1317729486351511E-2</v>
       </c>
       <c r="Y31" s="23">
         <f t="shared" si="4"/>
@@ -9691,57 +9691,57 @@
       </c>
       <c r="AC31" s="29">
         <f t="shared" si="16"/>
-        <v>1.0049999999999999</v>
+        <v>1.1549999999999978</v>
       </c>
       <c r="AD31" s="29">
         <f t="shared" si="6"/>
-        <v>1.0049899999999998</v>
+        <v>1.1549899999999977</v>
       </c>
       <c r="AE31" s="29">
         <f t="shared" si="7"/>
-        <v>1.00501</v>
+        <v>1.1550099999999979</v>
       </c>
       <c r="AF31" s="30">
         <f t="shared" si="8"/>
-        <v>8.8608954203452994E-2</v>
+        <v>6.9853014218264814E-2</v>
       </c>
       <c r="AG31" s="30">
         <f t="shared" si="9"/>
-        <v>8.8612710354690385E-2</v>
+        <v>6.9854231451273729E-2</v>
       </c>
       <c r="AH31" s="30">
         <f t="shared" si="10"/>
-        <v>8.8605198630012719E-2</v>
+        <v>6.9851797550244843E-2</v>
       </c>
       <c r="AI31" s="31">
         <f t="shared" si="11"/>
-        <v>8.2231376713361004E-2</v>
+        <v>1.767868135609485E-2</v>
       </c>
       <c r="AJ31" s="31">
         <f t="shared" si="12"/>
-        <v>8.2241038589248472E-2</v>
+        <v>1.7684171599355203E-2</v>
       </c>
       <c r="AK31" s="31">
         <f t="shared" si="13"/>
-        <v>8.2221714943912505E-2</v>
+        <v>1.7673192205854615E-2</v>
       </c>
       <c r="AL31" s="5">
         <f t="shared" si="14"/>
-        <v>1.064389687499556</v>
+        <v>10.930201188585896</v>
       </c>
       <c r="AM31" s="3">
         <f t="shared" si="15"/>
-        <v>5.4125860958171811E-3</v>
+        <v>5.5194969205516725E-2</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A32" s="16">
         <f>LN(F21 / $B$5)</f>
-        <v>4.3969773703030133E-4</v>
+        <v>3.6751988954891534E-4</v>
       </c>
       <c r="B32" s="16">
         <f>A32^2</f>
-        <v>1.9333409994956802E-7</v>
+        <v>1.3507086921404693E-7</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="3"/>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="U32" s="3">
         <f t="shared" si="0"/>
-        <v>0.11800456870171631</v>
+        <v>7.3243401065392191E-2</v>
       </c>
       <c r="Y32" s="23">
         <f t="shared" si="4"/>
@@ -9767,57 +9767,57 @@
       </c>
       <c r="AC32" s="29">
         <f t="shared" si="16"/>
-        <v>1.0099999999999998</v>
+        <v>1.1599999999999977</v>
       </c>
       <c r="AD32" s="29">
         <f t="shared" si="6"/>
-        <v>1.0099899999999997</v>
+        <v>1.1599899999999976</v>
       </c>
       <c r="AE32" s="29">
         <f t="shared" si="7"/>
-        <v>1.0100099999999999</v>
+        <v>1.1600099999999978</v>
       </c>
       <c r="AF32" s="30">
         <f t="shared" si="8"/>
-        <v>8.6802897678449259E-2</v>
+        <v>6.9314859948939267E-2</v>
       </c>
       <c r="AG32" s="30">
         <f t="shared" si="9"/>
-        <v>8.6806367023773132E-2</v>
+        <v>6.9315796497259552E-2</v>
       </c>
       <c r="AH32" s="30">
         <f t="shared" si="10"/>
-        <v>8.6799428902560372E-2</v>
+        <v>6.9313923958373366E-2</v>
       </c>
       <c r="AI32" s="31">
         <f t="shared" si="11"/>
-        <v>7.7414860781437222E-2</v>
+        <v>1.5071522738987375E-2</v>
       </c>
       <c r="AJ32" s="31">
         <f t="shared" si="12"/>
-        <v>7.7424462783069137E-2</v>
+        <v>1.5076460648506429E-2</v>
       </c>
       <c r="AK32" s="31">
         <f t="shared" si="13"/>
-        <v>7.7405258913939901E-2</v>
+        <v>1.5066585941464039E-2</v>
       </c>
       <c r="AL32" s="5">
         <f t="shared" si="14"/>
-        <v>1.3413459232225475</v>
+        <v>11.119957177285754</v>
       </c>
       <c r="AM32" s="3">
         <f t="shared" si="15"/>
-        <v>6.8209513667600707E-3</v>
+        <v>5.6153192734264605E-2</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A33" s="16">
         <f>LN(F22 / $B$5)</f>
-        <v>2.7509663313720598E-2</v>
+        <v>2.3370049249623742E-2</v>
       </c>
       <c r="B33" s="16">
         <f>A33^2</f>
-        <v>7.5678157563426496E-4</v>
+        <v>5.4615920192983922E-4</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="10"/>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="U33" s="3">
         <f t="shared" si="0"/>
-        <v>0.12374341554373314</v>
+        <v>7.5648283627673327E-2</v>
       </c>
       <c r="Y33" s="23">
         <f t="shared" si="4"/>
@@ -9842,57 +9842,57 @@
       </c>
       <c r="AC33" s="29">
         <f t="shared" si="16"/>
-        <v>1.0149999999999997</v>
+        <v>1.1649999999999976</v>
       </c>
       <c r="AD33" s="29">
         <f t="shared" si="6"/>
-        <v>1.0149899999999996</v>
+        <v>1.1649899999999975</v>
       </c>
       <c r="AE33" s="29">
         <f t="shared" si="7"/>
-        <v>1.0150099999999997</v>
+        <v>1.1650099999999977</v>
       </c>
       <c r="AF33" s="30">
         <f t="shared" si="8"/>
-        <v>8.5139203009260672E-2</v>
+        <v>6.8916146639055736E-2</v>
       </c>
       <c r="AG33" s="30">
         <f t="shared" si="9"/>
-        <v>8.5142389692345014E-2</v>
+        <v>6.8916806091612062E-2</v>
       </c>
       <c r="AH33" s="30">
         <f t="shared" si="10"/>
-        <v>8.5136016887398469E-2</v>
+        <v>6.8915487737132519E-2</v>
       </c>
       <c r="AI33" s="31">
         <f t="shared" si="11"/>
-        <v>7.2632017287097561E-2</v>
+        <v>1.2741803465693535E-2</v>
       </c>
       <c r="AJ33" s="31">
         <f t="shared" si="12"/>
-        <v>7.2641543948980258E-2</v>
+        <v>1.2746186188986652E-2</v>
       </c>
       <c r="AK33" s="31">
         <f t="shared" si="13"/>
-        <v>7.2622490793708527E-2</v>
+        <v>1.2737421846630403E-2</v>
       </c>
       <c r="AL33" s="5">
         <f t="shared" si="14"/>
-        <v>1.6849366346605164</v>
+        <v>11.042299852270785</v>
       </c>
       <c r="AM33" s="3">
         <f t="shared" si="15"/>
-        <v>8.5681632471662859E-3</v>
+        <v>5.5761041337521793E-2</v>
       </c>
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A34" s="16">
         <f>LN(F23 / $B$5)</f>
-        <v>5.6881459093779917E-2</v>
+        <v>4.7004757408746337E-2</v>
       </c>
       <c r="B34" s="16">
         <f>A34^2</f>
-        <v>3.2355003886373581E-3</v>
+        <v>2.2094472190550937E-3</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="10"/>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="U34" s="3">
         <f t="shared" si="0"/>
-        <v>0.12979513525431449</v>
+        <v>7.8520625164394758E-2</v>
       </c>
       <c r="Y34" s="23">
         <f t="shared" si="4"/>
@@ -9917,58 +9917,58 @@
       </c>
       <c r="AC34" s="29">
         <f t="shared" si="16"/>
-        <v>1.0199999999999996</v>
+        <v>1.1699999999999975</v>
       </c>
       <c r="AD34" s="29">
         <f t="shared" si="6"/>
-        <v>1.0199899999999995</v>
+        <v>1.1699899999999974</v>
       </c>
       <c r="AE34" s="29">
         <f t="shared" si="7"/>
-        <v>1.0200099999999996</v>
+        <v>1.1700099999999976</v>
       </c>
       <c r="AF34" s="30">
         <f t="shared" si="8"/>
-        <v>8.3615816921207814E-2</v>
+        <v>6.8655093918120469E-2</v>
       </c>
       <c r="AG34" s="30">
         <f t="shared" si="9"/>
-        <v>8.3618725011900125E-2</v>
+        <v>6.8655479807764846E-2</v>
       </c>
       <c r="AH34" s="30">
         <f t="shared" si="10"/>
-        <v>8.3612909383670816E-2</v>
+        <v>6.8654708572098933E-2</v>
       </c>
       <c r="AI34" s="31">
         <f t="shared" si="11"/>
-        <v>6.7891458037179109E-2</v>
+        <v>1.0687588749335064E-2</v>
       </c>
       <c r="AJ34" s="31">
         <f t="shared" si="12"/>
-        <v>6.790089029670654E-2</v>
+        <v>1.0691426824779082E-2</v>
       </c>
       <c r="AK34" s="31">
         <f t="shared" si="13"/>
-        <v>6.7882025988221906E-2</v>
+        <v>1.0683751743932768E-2</v>
       </c>
       <c r="AL34" s="5">
         <f t="shared" si="14"/>
-        <v>2.1057022792092535</v>
+        <v>10.700417218956202</v>
       </c>
       <c r="AM34" s="3">
         <f t="shared" si="15"/>
-        <v>1.0707821592252422E-2</v>
+        <v>5.4034613699812335E-2</v>
       </c>
     </row>
     <row r="35" spans="1:39" x14ac:dyDescent="0.25">
       <c r="T35" s="6">
         <f>F19</f>
-        <v>1.0323369799876165</v>
+        <v>1.0949090068168106</v>
       </c>
       <c r="U35" s="3"/>
       <c r="V35" s="3">
         <f>D19</f>
-        <v>8.0499999999999988E-2</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="W35" t="str">
         <f>C19</f>
@@ -9985,47 +9985,47 @@
       </c>
       <c r="AC35" s="29">
         <f t="shared" si="16"/>
-        <v>1.0249999999999995</v>
+        <v>1.1749999999999974</v>
       </c>
       <c r="AD35" s="29">
         <f t="shared" si="6"/>
-        <v>1.0249899999999994</v>
+        <v>1.1749899999999973</v>
       </c>
       <c r="AE35" s="29">
         <f t="shared" si="7"/>
-        <v>1.0250099999999995</v>
+        <v>1.1750099999999974</v>
       </c>
       <c r="AF35" s="30">
         <f t="shared" si="8"/>
-        <v>8.2230722643048343E-2</v>
+        <v>6.8529949179706895E-2</v>
       </c>
       <c r="AG35" s="30">
         <f t="shared" si="9"/>
-        <v>8.2233356138998334E-2</v>
+        <v>6.8530064984301323E-2</v>
       </c>
       <c r="AH35" s="30">
         <f t="shared" si="10"/>
-        <v>8.222808969232967E-2</v>
+        <v>6.8529833911833996E-2</v>
       </c>
       <c r="AI35" s="31">
         <f t="shared" si="11"/>
-        <v>6.3203721881698871E-2</v>
+        <v>8.9003868347954929E-3</v>
       </c>
       <c r="AJ35" s="31">
         <f t="shared" si="12"/>
-        <v>6.3213036576282633E-2</v>
+        <v>8.9037034461268982E-3</v>
       </c>
       <c r="AK35" s="31">
         <f t="shared" si="13"/>
-        <v>6.3194407448413648E-2</v>
+        <v>8.8970712355268544E-3</v>
       </c>
       <c r="AL35" s="5">
         <f t="shared" si="14"/>
-        <v>2.61298538362098</v>
+        <v>10.120627669252256</v>
       </c>
       <c r="AM35" s="3">
         <f t="shared" si="15"/>
-        <v>1.3287434594734682E-2</v>
+        <v>5.1106811567953325E-2</v>
       </c>
     </row>
     <row r="36" spans="1:39" x14ac:dyDescent="0.25">
@@ -10047,11 +10047,11 @@
       </c>
       <c r="T36" s="6">
         <f>F20</f>
-        <v>1.0600347861818515</v>
+        <v>1.1293039487620771</v>
       </c>
       <c r="V36" s="3">
         <f>D20</f>
-        <v>7.6249999999999998E-2</v>
+        <v>7.6000000000000012E-2</v>
       </c>
       <c r="W36" t="str">
         <f>C20</f>
@@ -10067,47 +10067,47 @@
       </c>
       <c r="AC36" s="29">
         <f t="shared" si="16"/>
-        <v>1.0299999999999994</v>
+        <v>1.1799999999999973</v>
       </c>
       <c r="AD36" s="29">
         <f t="shared" si="6"/>
-        <v>1.0299899999999993</v>
+        <v>1.1799899999999972</v>
       </c>
       <c r="AE36" s="29">
         <f t="shared" si="7"/>
-        <v>1.0300099999999994</v>
+        <v>1.1800099999999973</v>
       </c>
       <c r="AF36" s="30">
         <f t="shared" si="8"/>
-        <v>8.0981939103500794E-2</v>
+        <v>6.8538987046476929E-2</v>
       </c>
       <c r="AG36" s="30">
         <f t="shared" si="9"/>
-        <v>8.0984301931745786E-2</v>
+        <v>6.8538836189950825E-2</v>
       </c>
       <c r="AH36" s="30">
         <f t="shared" si="10"/>
-        <v>8.0979576812702708E-2</v>
+        <v>6.8539138432930052E-2</v>
       </c>
       <c r="AI36" s="31">
         <f t="shared" si="11"/>
-        <v>5.8581504561305286E-2</v>
+        <v>7.3657982259942578E-3</v>
       </c>
       <c r="AJ36" s="31">
         <f t="shared" si="12"/>
-        <v>5.8590674025256306E-2</v>
+        <v>7.3686273865460894E-3</v>
       </c>
       <c r="AK36" s="31">
         <f t="shared" si="13"/>
-        <v>5.8572335418679899E-2</v>
+        <v>7.3629700002752485E-3</v>
       </c>
       <c r="AL36" s="5">
         <f t="shared" si="14"/>
-        <v>3.2132563276832111</v>
+        <v>9.3483282226358693</v>
       </c>
       <c r="AM36" s="3">
         <f t="shared" si="15"/>
-        <v>1.6339905136033159E-2</v>
+        <v>4.7206879312548612E-2</v>
       </c>
     </row>
     <row r="37" spans="1:39" x14ac:dyDescent="0.25">
@@ -10116,31 +10116,31 @@
       </c>
       <c r="B37" s="17">
         <f>$F$3</f>
-        <v>1.05</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="C37" s="13">
         <f>E29 + E30*LN(B37/$B$5) + E31*LN(B37/$B$5)^2</f>
-        <v>7.7311497171383275E-2</v>
+        <v>8.5514504992336121E-2</v>
       </c>
       <c r="D37" s="18">
         <f>1 / (C37 * SQRT($B$2)) * (LN($B$1/B37) + ($B$3-$B$4 + C37^2/2)*$B$2)</f>
-        <v>0.92529962587395009</v>
+        <v>1.2299218619532732</v>
       </c>
       <c r="E37" s="18">
         <f>1 / (C37 * SQRT($B$2)) * (LN($B$1/B37) + ($B$3-$B$4 - C37^2/2)*$B$2)</f>
-        <v>0.88664387728825833</v>
+        <v>1.1871646094571053</v>
       </c>
       <c r="F37" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(D37,0,1,1) - B37*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(E37, 0, 1, 1)) * $F$2</f>
-        <v>41082.215173197656</v>
+        <v>60449.337004194858</v>
       </c>
       <c r="T37" s="6">
         <f>F21</f>
-        <v>1.0879017903763666</v>
+        <v>1.1587614138335498</v>
       </c>
       <c r="V37" s="3">
         <f>D21</f>
-        <v>7.5499999999999998E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="W37" t="str">
         <f>C21</f>
@@ -10156,47 +10156,47 @@
       </c>
       <c r="AC37" s="29">
         <f t="shared" si="16"/>
-        <v>1.0349999999999993</v>
+        <v>1.1849999999999972</v>
       </c>
       <c r="AD37" s="29">
         <f t="shared" si="6"/>
-        <v>1.0349899999999992</v>
+        <v>1.1849899999999971</v>
       </c>
       <c r="AE37" s="29">
         <f t="shared" si="7"/>
-        <v>1.0350099999999993</v>
+        <v>1.1850099999999972</v>
       </c>
       <c r="AF37" s="30">
         <f t="shared" si="8"/>
-        <v>7.9867520149019516E-2</v>
+        <v>6.868050884758263E-2</v>
       </c>
       <c r="AG37" s="30">
         <f t="shared" si="9"/>
-        <v>7.9869616167528371E-2</v>
+        <v>6.8680094700965921E-2</v>
       </c>
       <c r="AH37" s="30">
         <f t="shared" si="10"/>
-        <v>7.9865424660309853E-2</v>
+        <v>6.8680923517436598E-2</v>
       </c>
       <c r="AI37" s="31">
         <f t="shared" si="11"/>
-        <v>5.4039816496052939E-2</v>
+        <v>6.0646363273878512E-3</v>
       </c>
       <c r="AJ37" s="31">
         <f t="shared" si="12"/>
-        <v>5.4048808349022037E-2</v>
+        <v>6.0670202726724742E-3</v>
       </c>
       <c r="AK37" s="31">
         <f t="shared" si="13"/>
-        <v>5.4030825033897556E-2</v>
+        <v>6.0622532262155082E-3</v>
       </c>
       <c r="AL37" s="5">
         <f t="shared" si="14"/>
-        <v>3.9081371472349242</v>
+        <v>8.4411228007397181</v>
       </c>
       <c r="AM37" s="3">
         <f t="shared" si="15"/>
-        <v>1.9873481519125671E-2</v>
+        <v>4.2625703315813446E-2</v>
       </c>
     </row>
     <row r="38" spans="1:39" x14ac:dyDescent="0.25">
@@ -10205,31 +10205,31 @@
       </c>
       <c r="B38" s="17">
         <f>$F$3 + $F$13</f>
-        <v>1.0501</v>
+        <v>1.1001000000000001</v>
       </c>
       <c r="C38" s="13">
         <f>E29 + E30*LN(B38/$B$5) + E31*LN(B38/$B$5)^2</f>
-        <v>7.729834440216761E-2</v>
+        <v>8.5468952535843468E-2</v>
       </c>
       <c r="D38" s="18">
         <f>1 / (C38 * SQRT($B$2)) * (LN($B$1/B38) + ($B$3-$B$4 + C38^2/2)*$B$2)</f>
-        <v>0.92298644236921945</v>
+        <v>1.2284273878654557</v>
       </c>
       <c r="E38" s="18">
         <f>1 / (C38 * SQRT($B$2)) * (LN($B$1/B38) + ($B$3-$B$4 - C38^2/2)*$B$2)</f>
-        <v>0.88433727016813568</v>
+        <v>1.1856929115975339</v>
       </c>
       <c r="F38" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(D38,0,1,1) - B38*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(E38, 0, 1, 1)) * $F$2</f>
-        <v>41000.036551845034</v>
+        <v>60356.999684977542</v>
       </c>
       <c r="T38" s="6">
         <f>F22</f>
-        <v>1.1177534735320678</v>
+        <v>1.1857247812154261</v>
       </c>
       <c r="V38" s="3">
         <f>D22</f>
-        <v>7.9750000000000001E-2</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="W38" t="str">
         <f>C22</f>
@@ -10245,47 +10245,47 @@
       </c>
       <c r="AC38" s="29">
         <f t="shared" si="16"/>
-        <v>1.0399999999999991</v>
+        <v>1.1899999999999971</v>
       </c>
       <c r="AD38" s="29">
         <f t="shared" si="6"/>
-        <v>1.0399899999999991</v>
+        <v>1.189989999999997</v>
       </c>
       <c r="AE38" s="29">
         <f t="shared" si="7"/>
-        <v>1.0400099999999992</v>
+        <v>1.1900099999999971</v>
       </c>
       <c r="AF38" s="30">
         <f t="shared" si="8"/>
-        <v>7.8885553782162832E-2</v>
+        <v>6.8952842108113033E-2</v>
       </c>
       <c r="AG38" s="30">
         <f t="shared" si="9"/>
-        <v>7.8887386781338859E-2</v>
+        <v>6.8952167990545515E-2</v>
       </c>
       <c r="AH38" s="30">
         <f t="shared" si="10"/>
-        <v>7.8883721305271923E-2</v>
+        <v>6.8953516742330898E-2</v>
       </c>
       <c r="AI38" s="31">
         <f t="shared" si="11"/>
-        <v>4.9596018428284538E-2</v>
+        <v>4.9743502373476023E-3</v>
       </c>
       <c r="AJ38" s="31">
         <f t="shared" si="12"/>
-        <v>4.9604795662091195E-2</v>
+        <v>4.9763364104272179E-3</v>
       </c>
       <c r="AK38" s="31">
         <f t="shared" si="13"/>
-        <v>4.9587241663692883E-2</v>
+        <v>4.9723648103318641E-3</v>
       </c>
       <c r="AL38" s="5">
         <f t="shared" si="14"/>
-        <v>4.6921500018726183</v>
+        <v>7.4606387734377213</v>
       </c>
       <c r="AM38" s="3">
         <f t="shared" si="15"/>
-        <v>2.3860308078788004E-2</v>
+        <v>3.767448743609584E-2</v>
       </c>
     </row>
     <row r="39" spans="1:39" x14ac:dyDescent="0.25">
@@ -10294,31 +10294,31 @@
       </c>
       <c r="B39" s="17">
         <f>$F$4</f>
-        <v>1.1000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="C39" s="13">
         <f>E29 + E30*LN(B39/$B$5) + E31*LN(B39/$B$5)^2</f>
-        <v>7.6780824030620323E-2</v>
+        <v>6.9883381105899145E-2</v>
       </c>
       <c r="D39" s="18">
         <f>1 / (C39 * SQRT($B$2)) * (LN($B$1/B39) + ($B$3-$B$4 + C39^2/2)*$B$2)</f>
-        <v>-0.28033269109981163</v>
+        <v>-0.99385368278256703</v>
       </c>
       <c r="E39" s="18">
         <f>1 / (C39 * SQRT($B$2)) * (LN($B$1/B39) + ($B$3-$B$4 - C39^2/2)*$B$2)</f>
-        <v>-0.31872310311512181</v>
+        <v>-1.0287953733355164</v>
       </c>
       <c r="F39" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(D39,0,1,1) - B39*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(E39, 0, 1, 1)) * $F$2</f>
-        <v>11087.419338093152</v>
+        <v>3328.4408944939114</v>
       </c>
       <c r="T39" s="6">
         <f>F23</f>
-        <v>1.1510707999322727</v>
+        <v>1.2140828375149078</v>
       </c>
       <c r="V39" s="3">
         <f>D23</f>
-        <v>8.7499999999999994E-2</v>
+        <v>7.2500000000000009E-2</v>
       </c>
       <c r="W39" t="str">
         <f>C23</f>
@@ -10334,47 +10334,47 @@
       </c>
       <c r="AC39" s="29">
         <f t="shared" si="16"/>
-        <v>1.044999999999999</v>
+        <v>1.194999999999997</v>
       </c>
       <c r="AD39" s="29">
         <f t="shared" si="6"/>
-        <v>1.044989999999999</v>
+        <v>1.1949899999999969</v>
       </c>
       <c r="AE39" s="29">
         <f t="shared" si="7"/>
-        <v>1.0450099999999991</v>
+        <v>1.195009999999997</v>
       </c>
       <c r="AF39" s="30">
         <f t="shared" si="8"/>
-        <v>7.8034161419919659E-2</v>
+        <v>6.9354340050261587E-2</v>
       </c>
       <c r="AG39" s="30">
         <f t="shared" si="9"/>
-        <v>7.8035735124064531E-2</v>
+        <v>6.9353409229978957E-2</v>
       </c>
       <c r="AH39" s="30">
         <f t="shared" si="10"/>
-        <v>7.8032588230676589E-2</v>
+        <v>6.9355271380708447E-2</v>
       </c>
       <c r="AI39" s="31">
         <f t="shared" si="11"/>
-        <v>4.5269680515053312E-2</v>
+        <v>4.0705492711990421E-3</v>
       </c>
       <c r="AJ39" s="31">
         <f t="shared" si="12"/>
-        <v>4.5278201986665545E-2</v>
+        <v>4.0721873031790423E-3</v>
       </c>
       <c r="AK39" s="31">
         <f t="shared" si="13"/>
-        <v>4.5261159598514178E-2</v>
+        <v>4.0689118857061835E-3</v>
       </c>
       <c r="AL39" s="5">
         <f t="shared" si="14"/>
-        <v>5.5507309859592615</v>
+        <v>6.4648714159787337</v>
       </c>
       <c r="AM39" s="3">
         <f t="shared" si="15"/>
-        <v>2.822632510354646E-2</v>
+        <v>3.2646094300185204E-2</v>
       </c>
     </row>
     <row r="40" spans="1:39" x14ac:dyDescent="0.25">
@@ -10383,23 +10383,23 @@
       </c>
       <c r="B40" s="17">
         <f>$F$4+$F$13</f>
-        <v>1.1001000000000001</v>
+        <v>1.2000999999999999</v>
       </c>
       <c r="C40" s="13">
         <f>E29 + E30*LN(B40/$B$5) + E31*LN(B40/$B$5)^2</f>
-        <v>7.6791351173436911E-2</v>
+        <v>6.9895251858567098E-2</v>
       </c>
       <c r="D40" s="18">
         <f>1 / (C40 * SQRT($B$2)) * (LN($B$1/B40) + ($B$3-$B$4 + C40^2/2)*$B$2)</f>
-        <v>-0.28265658101447988</v>
+        <v>-0.9960633766866539</v>
       </c>
       <c r="E40" s="18">
         <f>1 / (C40 * SQRT($B$2)) * (LN($B$1/B40) + ($B$3-$B$4 - C40^2/2)*$B$2)</f>
-        <v>-0.32105225660119835</v>
+        <v>-1.0310110026159376</v>
       </c>
       <c r="F40" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(D40,0,1,1) - B40*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(E40, 0, 1, 1)) * $F$2</f>
-        <v>11052.538394791756</v>
+        <v>3315.0808752296089</v>
       </c>
       <c r="Y40" s="23">
         <f t="shared" si="4"/>
@@ -10411,47 +10411,47 @@
       </c>
       <c r="AC40" s="29">
         <f t="shared" si="16"/>
-        <v>1.0499999999999989</v>
+        <v>1.1999999999999968</v>
       </c>
       <c r="AD40" s="29">
         <f t="shared" si="6"/>
-        <v>1.0499899999999989</v>
+        <v>1.1999899999999968</v>
       </c>
       <c r="AE40" s="29">
         <f t="shared" si="7"/>
-        <v>1.050009999999999</v>
+        <v>1.2000099999999969</v>
       </c>
       <c r="AF40" s="30">
         <f t="shared" si="8"/>
-        <v>7.7311497171383414E-2</v>
+        <v>6.9883381105898784E-2</v>
       </c>
       <c r="AG40" s="30">
         <f t="shared" si="9"/>
-        <v>7.7312815240122928E-2</v>
+        <v>6.9882196801196478E-2</v>
       </c>
       <c r="AH40" s="30">
         <f t="shared" si="10"/>
-        <v>7.7310179610290311E-2</v>
+        <v>6.9884565914378124E-2</v>
       </c>
       <c r="AI40" s="31">
         <f t="shared" si="11"/>
-        <v>4.1082215173198544E-2</v>
+        <v>3.3284408944943833E-3</v>
       </c>
       <c r="AJ40" s="31">
         <f t="shared" si="12"/>
-        <v>4.1090436590743185E-2</v>
+        <v>3.3297799196890521E-3</v>
       </c>
       <c r="AK40" s="31">
         <f t="shared" si="13"/>
-        <v>4.1073994401538694E-2</v>
+        <v>3.3271024195441201E-3</v>
       </c>
       <c r="AL40" s="5">
         <f t="shared" si="14"/>
-        <v>6.4588479009586299</v>
+        <v>5.5024440559492396</v>
       </c>
       <c r="AM40" s="3">
         <f t="shared" si="15"/>
-        <v>3.2844239994331254E-2</v>
+        <v>2.7786060382891199E-2</v>
       </c>
     </row>
     <row r="41" spans="1:39" x14ac:dyDescent="0.25">
@@ -10465,47 +10465,47 @@
       </c>
       <c r="AC41" s="29">
         <f t="shared" si="16"/>
-        <v>1.0549999999999988</v>
+        <v>1.2049999999999967</v>
       </c>
       <c r="AD41" s="29">
         <f t="shared" si="6"/>
-        <v>1.0549899999999988</v>
+        <v>1.2049899999999967</v>
       </c>
       <c r="AE41" s="29">
         <f t="shared" si="7"/>
-        <v>1.0550099999999989</v>
+        <v>1.2050099999999968</v>
       </c>
       <c r="AF41" s="30">
         <f t="shared" si="8"/>
-        <v>7.6715747134181861E-2</v>
+        <v>7.0538368440245511E-2</v>
       </c>
       <c r="AG41" s="30">
         <f t="shared" si="9"/>
-        <v>7.6716813163854716E-2</v>
+        <v>7.0536933820420394E-2</v>
       </c>
       <c r="AH41" s="30">
         <f t="shared" si="10"/>
-        <v>7.6714681605025231E-2</v>
+        <v>7.053980355755754E-2</v>
       </c>
       <c r="AI41" s="31">
         <f t="shared" si="11"/>
-        <v>3.7056251039602972E-2</v>
+        <v>2.7240396159067537E-3</v>
       </c>
       <c r="AJ41" s="31">
         <f t="shared" si="12"/>
-        <v>3.7064126480535142E-2</v>
+        <v>2.7251261465702226E-3</v>
       </c>
       <c r="AK41" s="31">
         <f t="shared" si="13"/>
-        <v>3.704837633676028E-2</v>
+        <v>2.7229535461846532E-3</v>
       </c>
       <c r="AL41" s="5">
         <f t="shared" si="14"/>
-        <v>7.3808947842479702</v>
+        <v>4.6094136840757463</v>
       </c>
       <c r="AM41" s="3">
         <f t="shared" si="15"/>
-        <v>3.7532990927185005E-2</v>
+        <v>2.3276465085906032E-2</v>
       </c>
     </row>
     <row r="42" spans="1:39" x14ac:dyDescent="0.25">
@@ -10514,21 +10514,21 @@
       </c>
       <c r="B42" s="19">
         <f>(F37 - F38) / $F$13</f>
-        <v>821786.21352621121</v>
+        <v>923373.1921731669</v>
       </c>
       <c r="C42" s="12" t="s">
         <v>30</v>
       </c>
       <c r="D42" s="19">
         <f>(F39 - F40) / $F$13</f>
-        <v>348809.43301395746</v>
+        <v>133600.19264302537</v>
       </c>
       <c r="E42" s="12" t="s">
         <v>0</v>
       </c>
       <c r="F42" s="19">
         <f>B42-D42</f>
-        <v>472976.78051225375</v>
+        <v>789772.99953014147</v>
       </c>
       <c r="Y42" s="23">
         <f t="shared" si="4"/>
@@ -10540,47 +10540,47 @@
       </c>
       <c r="AC42" s="29">
         <f t="shared" si="16"/>
-        <v>1.0599999999999987</v>
+        <v>1.2099999999999966</v>
       </c>
       <c r="AD42" s="29">
         <f t="shared" si="6"/>
-        <v>1.0599899999999987</v>
+        <v>1.2099899999999966</v>
       </c>
       <c r="AE42" s="29">
         <f t="shared" si="7"/>
-        <v>1.0600099999999988</v>
+        <v>1.2100099999999967</v>
       </c>
       <c r="AF42" s="30">
         <f t="shared" si="8"/>
-        <v>7.6245128709093932E-2</v>
+        <v>7.1317729486350914E-2</v>
       </c>
       <c r="AG42" s="30">
         <f t="shared" si="9"/>
-        <v>7.6245946234104772E-2</v>
+        <v>7.1316047672621743E-2</v>
       </c>
       <c r="AH42" s="30">
         <f t="shared" si="10"/>
-        <v>7.62443116775917E-2</v>
+        <v>7.131941179137212E-2</v>
       </c>
       <c r="AI42" s="31">
         <f t="shared" si="11"/>
-        <v>3.3214745999395556E-2</v>
+        <v>2.235066975501826E-3</v>
       </c>
       <c r="AJ42" s="31">
         <f t="shared" si="12"/>
-        <v>3.3222229926199276E-2</v>
+        <v>2.235943431424553E-3</v>
       </c>
       <c r="AK42" s="31">
         <f t="shared" si="13"/>
-        <v>3.3207262899817014E-2</v>
+        <v>2.2341909004368887E-3</v>
       </c>
       <c r="AL42" s="5">
         <f t="shared" si="14"/>
-        <v>8.2722517724675964</v>
+        <v>3.8085778975016633</v>
       </c>
       <c r="AM42" s="3">
         <f t="shared" si="15"/>
-        <v>4.2065678999521329E-2</v>
+        <v>1.923243096283872E-2</v>
       </c>
     </row>
     <row r="43" spans="1:39" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -10594,47 +10594,47 @@
       </c>
       <c r="AC43" s="29">
         <f t="shared" si="16"/>
-        <v>1.0649999999999986</v>
+        <v>1.2149999999999965</v>
       </c>
       <c r="AD43" s="29">
         <f t="shared" si="6"/>
-        <v>1.0649899999999985</v>
+        <v>1.2149899999999965</v>
       </c>
       <c r="AE43" s="29">
         <f t="shared" si="7"/>
-        <v>1.0650099999999987</v>
+        <v>1.2150099999999966</v>
       </c>
       <c r="AF43" s="30">
         <f t="shared" si="8"/>
-        <v>7.5897889932302925E-2</v>
+        <v>7.2219915490088424E-2</v>
       </c>
       <c r="AG43" s="30">
         <f t="shared" si="9"/>
-        <v>7.589846242644048E-2</v>
+        <v>7.2217989556495568E-2</v>
       </c>
       <c r="AH43" s="30">
         <f t="shared" si="10"/>
-        <v>7.5897317924786253E-2</v>
+        <v>7.2221841908871931E-2</v>
       </c>
       <c r="AI43" s="31">
         <f t="shared" si="11"/>
-        <v>2.9579878866687004E-2</v>
+        <v>1.8415244393034103E-3</v>
       </c>
       <c r="AJ43" s="31">
         <f t="shared" si="12"/>
-        <v>2.9586928515057065E-2</v>
+        <v>1.8422283147559726E-3</v>
       </c>
       <c r="AK43" s="31">
         <f t="shared" si="13"/>
-        <v>2.95728301265894E-2</v>
+        <v>1.8408208749275956E-3</v>
       </c>
       <c r="AL43" s="5">
         <f t="shared" si="14"/>
-        <v>9.0827245724511823</v>
+        <v>3.1107674769437206</v>
       </c>
       <c r="AM43" s="3">
         <f t="shared" si="15"/>
-        <v>4.6187058471483758E-2</v>
+        <v>1.5708650932677416E-2</v>
       </c>
     </row>
     <row r="44" spans="1:39" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -10667,47 +10667,47 @@
       </c>
       <c r="AC44" s="29">
         <f t="shared" si="16"/>
-        <v>1.0699999999999985</v>
+        <v>1.2199999999999964</v>
       </c>
       <c r="AD44" s="29">
         <f t="shared" si="6"/>
-        <v>1.0699899999999984</v>
+        <v>1.2199899999999964</v>
       </c>
       <c r="AE44" s="29">
         <f t="shared" si="7"/>
-        <v>1.0700099999999986</v>
+        <v>1.2200099999999965</v>
       </c>
       <c r="AF44" s="30">
         <f t="shared" si="8"/>
-        <v>7.567230882475541E-2</v>
+        <v>7.3243401065391359E-2</v>
       </c>
       <c r="AG44" s="30">
         <f t="shared" si="9"/>
-        <v>7.5672639702477146E-2</v>
+        <v>7.3241234039676223E-2</v>
       </c>
       <c r="AH44" s="30">
         <f t="shared" si="10"/>
-        <v>7.5671978426884251E-2</v>
+        <v>7.3245568570287439E-2</v>
       </c>
       <c r="AI44" s="31">
         <f t="shared" si="11"/>
-        <v>2.6171805104466039E-2</v>
+        <v>1.5259690418087946E-3</v>
       </c>
       <c r="AJ44" s="31">
         <f t="shared" si="12"/>
-        <v>2.6178383029695107E-2</v>
+        <v>1.5265326147688302E-3</v>
       </c>
       <c r="AK44" s="31">
         <f t="shared" si="13"/>
-        <v>2.6165228155396347E-2</v>
+        <v>1.5254057205713323E-3</v>
       </c>
       <c r="AL44" s="5">
         <f t="shared" si="14"/>
-        <v>9.7615937555417513</v>
+        <v>2.5172257334116206</v>
       </c>
       <c r="AM44" s="3">
         <f t="shared" si="15"/>
-        <v>4.963921320806966E-2</v>
+        <v>1.2711403426322834E-2</v>
       </c>
     </row>
     <row r="45" spans="1:39" x14ac:dyDescent="0.25">
@@ -10721,63 +10721,63 @@
       </c>
       <c r="AC45" s="29">
         <f t="shared" si="16"/>
-        <v>1.0749999999999984</v>
+        <v>1.2249999999999963</v>
       </c>
       <c r="AD45" s="29">
         <f t="shared" si="6"/>
-        <v>1.0749899999999983</v>
+        <v>1.2249899999999962</v>
       </c>
       <c r="AE45" s="29">
         <f t="shared" si="7"/>
-        <v>1.0750099999999985</v>
+        <v>1.2250099999999964</v>
       </c>
       <c r="AF45" s="30">
         <f t="shared" si="8"/>
-        <v>7.5566692758113299E-2</v>
+        <v>7.438668375945913E-2</v>
       </c>
       <c r="AG45" s="30">
         <f t="shared" si="9"/>
-        <v>7.5566785375797252E-2</v>
+        <v>7.4384278623924077E-2</v>
       </c>
       <c r="AH45" s="30">
         <f t="shared" si="10"/>
-        <v>7.5566600613624565E-2</v>
+        <v>7.4389089368255515E-2</v>
       </c>
       <c r="AI45" s="31">
         <f t="shared" si="11"/>
-        <v>2.3007401520101944E-2</v>
+        <v>1.273550419006092E-3</v>
       </c>
       <c r="AJ45" s="31">
         <f t="shared" si="12"/>
-        <v>2.3013478022296252E-2</v>
+        <v>1.2740008695223126E-3</v>
       </c>
       <c r="AK45" s="31">
         <f t="shared" si="13"/>
-        <v>2.3001326044267079E-2</v>
+        <v>1.2731001707323164E-3</v>
       </c>
       <c r="AL45" s="5">
         <f t="shared" si="14"/>
-        <v>10.263594418802311</v>
+        <v>2.0224244501321205</v>
       </c>
       <c r="AM45" s="3">
         <f t="shared" si="15"/>
-        <v>5.2191964180730924E-2</v>
+        <v>1.0212772237174933E-2</v>
       </c>
     </row>
     <row r="46" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A46" s="35" t="s">
+      <c r="A46" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="B46" s="35"/>
-      <c r="C46" s="35" t="s">
+      <c r="B46" s="33"/>
+      <c r="C46" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="D46" s="35"/>
-      <c r="E46" s="35" t="s">
+      <c r="D46" s="33"/>
+      <c r="E46" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="F46" s="35"/>
-      <c r="G46" s="35"/>
+      <c r="F46" s="33"/>
+      <c r="G46" s="33"/>
       <c r="Y46" s="23">
         <f t="shared" si="4"/>
         <v>1.035999999999996</v>
@@ -10788,47 +10788,47 @@
       </c>
       <c r="AC46" s="29">
         <f t="shared" si="16"/>
-        <v>1.0799999999999983</v>
+        <v>1.2299999999999962</v>
       </c>
       <c r="AD46" s="29">
         <f t="shared" si="6"/>
-        <v>1.0799899999999982</v>
+        <v>1.2299899999999961</v>
       </c>
       <c r="AE46" s="29">
         <f t="shared" si="7"/>
-        <v>1.0800099999999984</v>
+        <v>1.2300099999999963</v>
       </c>
       <c r="AF46" s="30">
         <f t="shared" si="8"/>
-        <v>7.5579377836803893E-2</v>
+        <v>7.5648283627672244E-2</v>
       </c>
       <c r="AG46" s="30">
         <f t="shared" si="9"/>
-        <v>7.5579235493968791E-2</v>
+        <v>7.5645643320021133E-2</v>
       </c>
       <c r="AH46" s="30">
         <f t="shared" si="10"/>
-        <v>7.5579520646291323E-2</v>
+        <v>7.5650924402753408E-2</v>
       </c>
       <c r="AI46" s="31">
         <f t="shared" si="11"/>
-        <v>2.0099146810528601E-2</v>
+        <v>1.0718782102620977E-3</v>
       </c>
       <c r="AJ46" s="31">
         <f t="shared" si="12"/>
-        <v>2.0104701939504865E-2</v>
+        <v>1.0722380098489998E-3</v>
       </c>
       <c r="AK46" s="31">
         <f t="shared" si="13"/>
-        <v>2.0093592737023935E-2</v>
+        <v>1.0715185723466913E-3</v>
       </c>
       <c r="AL46" s="5">
         <f t="shared" si="14"/>
-        <v>10.554715990096495</v>
+        <v>1.6167149563539593</v>
       </c>
       <c r="AM46" s="3">
         <f t="shared" si="15"/>
-        <v>5.3672362372751185E-2</v>
+        <v>8.1640338261330676E-3</v>
       </c>
     </row>
     <row r="47" spans="1:39" x14ac:dyDescent="0.25">
@@ -10867,47 +10867,47 @@
       </c>
       <c r="AC47" s="29">
         <f t="shared" si="16"/>
-        <v>1.0849999999999982</v>
+        <v>1.2349999999999961</v>
       </c>
       <c r="AD47" s="29">
         <f t="shared" si="6"/>
-        <v>1.0849899999999981</v>
+        <v>1.234989999999996</v>
       </c>
       <c r="AE47" s="29">
         <f t="shared" si="7"/>
-        <v>1.0850099999999983</v>
+        <v>1.2350099999999962</v>
       </c>
       <c r="AF47" s="30">
         <f t="shared" si="8"/>
-        <v>7.5708728295689823E-2</v>
+        <v>7.7026742817962748E-2</v>
       </c>
       <c r="AG47" s="30">
         <f t="shared" si="9"/>
-        <v>7.5708354236184522E-2</v>
+        <v>7.702387023212301E-2</v>
       </c>
       <c r="AH47" s="30">
         <f t="shared" si="10"/>
-        <v>7.570910281541475E-2</v>
+        <v>7.702961586548801E-2</v>
       </c>
       <c r="AI47" s="31">
         <f t="shared" si="11"/>
-        <v>1.7454280626757246E-2</v>
+        <v>9.1078530627055482E-4</v>
       </c>
       <c r="AJ47" s="31">
         <f t="shared" si="12"/>
-        <v>1.7459305504743283E-2</v>
+        <v>9.1107275714263913E-4</v>
       </c>
       <c r="AK47" s="31">
         <f t="shared" si="13"/>
-        <v>1.7449256810438185E-2</v>
+        <v>9.1049798424687467E-4</v>
       </c>
       <c r="AL47" s="5">
         <f t="shared" si="14"/>
-        <v>10.616669765539653</v>
+        <v>1.2884840416838015</v>
       </c>
       <c r="AM47" s="3">
         <f t="shared" si="15"/>
-        <v>5.3987406897782954E-2</v>
+        <v>6.5065441866526234E-3</v>
       </c>
     </row>
     <row r="48" spans="1:39" x14ac:dyDescent="0.25">
@@ -10916,25 +10916,25 @@
       </c>
       <c r="B48" s="13">
         <f>$B$19+$F$12</f>
-        <v>7.6499999999999999E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="C48" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D48" s="13">
         <f>B48 + B52 - B50/2</f>
-        <v>8.1499999999999989E-2</v>
+        <v>8.8499999999999995E-2</v>
       </c>
       <c r="E48" s="14">
         <v>0.9</v>
       </c>
       <c r="F48" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(E48 * EXP($B$4*$B$2), 0, 1) * D48 * SQRT($B$2) - ($B$3 - $B$4 + D48^2/2)*$B$2)</f>
-        <v>1.0316810332656901</v>
+        <v>1.0942166809761167</v>
       </c>
       <c r="G48" s="16">
         <f t="shared" ref="G48:G50" si="18">EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(1/(D48*SQRT($B$2)) * (LN($B$1 / F48) + ($B$3 - $B$4 + D48^2/2)*$B$2), 0, 1, 1)</f>
-        <v>0.90000000000000058</v>
+        <v>0.90000000000000036</v>
       </c>
       <c r="W48" s="9"/>
       <c r="X48" s="9"/>
@@ -10948,47 +10948,47 @@
       </c>
       <c r="AC48" s="29">
         <f t="shared" si="16"/>
-        <v>1.0899999999999981</v>
+        <v>1.239999999999996</v>
       </c>
       <c r="AD48" s="29">
         <f t="shared" si="6"/>
-        <v>1.089989999999998</v>
+        <v>1.2399899999999959</v>
       </c>
       <c r="AE48" s="29">
         <f t="shared" si="7"/>
-        <v>1.0900099999999981</v>
+        <v>1.2400099999999961</v>
       </c>
       <c r="AF48" s="30">
         <f t="shared" si="8"/>
-        <v>7.5953135912897221E-2</v>
+        <v>7.8520625164393468E-2</v>
       </c>
       <c r="AG48" s="30">
         <f t="shared" si="9"/>
-        <v>7.5952533326060223E-2</v>
+        <v>7.8517523151319851E-2</v>
       </c>
       <c r="AH48" s="30">
         <f t="shared" si="10"/>
-        <v>7.5953738953629057E-2</v>
+        <v>7.8523727633493245E-2</v>
       </c>
       <c r="AI48" s="31">
         <f t="shared" si="11"/>
-        <v>1.5074351268041464E-2</v>
+        <v>7.8204090160352568E-4</v>
       </c>
       <c r="AJ48" s="31">
         <f t="shared" si="12"/>
-        <v>1.507884855923225E-2</v>
+        <v>7.8227073196606572E-4</v>
       </c>
       <c r="AK48" s="31">
         <f t="shared" si="13"/>
-        <v>1.5069855021765499E-2</v>
+        <v>7.8181117381582316E-4</v>
       </c>
       <c r="AL48" s="5">
         <f t="shared" si="14"/>
-        <v>10.449148213353963</v>
+        <v>1.0257483751274774</v>
       </c>
       <c r="AM48" s="3">
         <f t="shared" si="15"/>
-        <v>5.313553390919732E-2</v>
+        <v>5.1797902893949109E-3</v>
       </c>
     </row>
     <row r="49" spans="1:39" x14ac:dyDescent="0.25">
@@ -10997,21 +10997,21 @@
       </c>
       <c r="B49" s="20">
         <f>$B$20</f>
-        <v>3.5000000000000001E-3</v>
+        <v>-8.0000000000000002E-3</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>18</v>
       </c>
       <c r="D49" s="13">
         <f>B48+B51 - B49/2</f>
-        <v>7.7249999999999999E-2</v>
+        <v>7.7000000000000013E-2</v>
       </c>
       <c r="E49" s="14">
         <v>0.75</v>
       </c>
       <c r="F49" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(E49 * EXP($B$4*$B$2), 0, 1) * D49 * SQRT($B$2) - ($B$3 - $B$4 + D49^2/2)*$B$2)</f>
-        <v>1.0596904431927263</v>
+        <v>1.1289377095147208</v>
       </c>
       <c r="G49" s="16">
         <f t="shared" si="18"/>
@@ -11029,47 +11029,47 @@
       </c>
       <c r="AC49" s="29">
         <f t="shared" si="16"/>
-        <v>1.094999999999998</v>
+        <v>1.2449999999999959</v>
       </c>
       <c r="AD49" s="29">
         <f t="shared" si="6"/>
-        <v>1.0949899999999979</v>
+        <v>1.2449899999999958</v>
       </c>
       <c r="AE49" s="29">
         <f t="shared" si="7"/>
-        <v>1.095009999999998</v>
+        <v>1.245009999999996</v>
       </c>
       <c r="AF49" s="30">
         <f t="shared" si="8"/>
-        <v>7.6311019437355909E-2</v>
+        <v>8.0128515789708366E-2</v>
       </c>
       <c r="AG49" s="30">
         <f t="shared" si="9"/>
-        <v>7.6310191459145804E-2</v>
+        <v>8.0125187158169062E-2</v>
       </c>
       <c r="AH49" s="30">
         <f t="shared" si="10"/>
-        <v>7.6311847863241661E-2</v>
+        <v>8.0131844871698013E-2</v>
       </c>
       <c r="AI49" s="31">
         <f t="shared" si="11"/>
-        <v>1.2955206875898406E-2</v>
+        <v>6.790528811737237E-4</v>
       </c>
       <c r="AJ49" s="31">
         <f t="shared" si="12"/>
-        <v>1.2959190357659411E-2</v>
+        <v>6.79236831918964E-4</v>
       </c>
       <c r="AK49" s="31">
         <f t="shared" si="13"/>
-        <v>1.2951224401072936E-2</v>
+        <v>6.7886901214402051E-4</v>
       </c>
       <c r="AL49" s="5">
         <f t="shared" si="14"/>
-        <v>10.069355349529017</v>
+        <v>0.81715537114668269</v>
       </c>
       <c r="AM49" s="3">
         <f t="shared" si="15"/>
-        <v>5.1204228487722776E-2</v>
+        <v>4.1264442226062051E-3</v>
       </c>
     </row>
     <row r="50" spans="1:39" x14ac:dyDescent="0.25">
@@ -11078,25 +11078,25 @@
       </c>
       <c r="B50" s="20">
         <f>$B$21</f>
-        <v>7.0000000000000001E-3</v>
+        <v>-1.4999999999999999E-2</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>4</v>
       </c>
       <c r="D50" s="13">
         <f>B48</f>
-        <v>7.6499999999999999E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="E50" s="14">
         <v>0.5</v>
       </c>
       <c r="F50" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(E50 * EXP($B$4*$B$2), 0, 1) * D50 * SQRT($B$2) - ($B$3 - $B$4 + D50^2/2)*$B$2)</f>
-        <v>1.0879185293005196</v>
+        <v>1.1587777251087923</v>
       </c>
       <c r="G50" s="16">
         <f t="shared" si="18"/>
-        <v>0.50000000000000111</v>
+        <v>0.50000000000000155</v>
       </c>
       <c r="N50" s="6"/>
       <c r="P50" s="3"/>
@@ -11110,47 +11110,47 @@
       </c>
       <c r="AC50" s="29">
         <f t="shared" si="16"/>
-        <v>1.0999999999999979</v>
+        <v>1.2499999999999958</v>
       </c>
       <c r="AD50" s="29">
         <f t="shared" si="6"/>
-        <v>1.0999899999999978</v>
+        <v>1.2499899999999957</v>
       </c>
       <c r="AE50" s="29">
         <f t="shared" si="7"/>
-        <v>1.1000099999999979</v>
+        <v>1.2500099999999958</v>
       </c>
       <c r="AF50" s="30">
         <f t="shared" si="8"/>
-        <v>7.6780824030620087E-2</v>
+        <v>8.1849020716621465E-2</v>
       </c>
       <c r="AG50" s="30">
         <f t="shared" si="9"/>
-        <v>7.6779773744718033E-2</v>
+        <v>8.1845468233966989E-2</v>
       </c>
       <c r="AH50" s="30">
         <f t="shared" si="10"/>
-        <v>7.6781874758082097E-2</v>
+        <v>8.1852573644232582E-2</v>
       </c>
       <c r="AI50" s="31">
         <f t="shared" si="11"/>
-        <v>1.1087419338093929E-2</v>
+        <v>5.9658524641912486E-4</v>
       </c>
       <c r="AJ50" s="31">
         <f t="shared" si="12"/>
-        <v>1.1090912660311147E-2</v>
+        <v>5.9673261013903217E-4</v>
       </c>
       <c r="AK50" s="31">
         <f t="shared" si="13"/>
-        <v>1.108392696678423E-2</v>
+        <v>5.9643794795504607E-4</v>
       </c>
       <c r="AL50" s="5">
         <f t="shared" si="14"/>
-        <v>9.5090751939252964</v>
+        <v>0.65255828518573356</v>
       </c>
       <c r="AM50" s="3">
         <f t="shared" si="15"/>
-        <v>4.8355117287569166E-2</v>
+        <v>3.2952672905274508E-3</v>
       </c>
     </row>
     <row r="51" spans="1:39" x14ac:dyDescent="0.25">
@@ -11159,25 +11159,25 @@
       </c>
       <c r="B51" s="20">
         <f>$B$22</f>
-        <v>2.5000000000000001E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>19</v>
       </c>
       <c r="D51" s="13">
         <f>B48 + B51 + B49/2</f>
-        <v>8.0750000000000002E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="E51" s="14">
         <v>0.25</v>
       </c>
       <c r="F51" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(E51 * EXP($B$4*$B$2), 0, 1) * D51 * SQRT($B$2) - ($B$3 - $B$4 + D51^2/2)*$B$2)</f>
-        <v>1.1181503939843658</v>
+        <v>1.1861425882511798</v>
       </c>
       <c r="G51" s="16">
         <f>EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(1/(D51*SQRT($B$2)) * (LN($B$1 / F51) + ($B$3 - $B$4 + D51^2/2)*$B$2), 0, 1, 1)</f>
-        <v>0.25000000000000039</v>
+        <v>0.25000000000000011</v>
       </c>
       <c r="N51" s="6"/>
       <c r="P51" s="3"/>
@@ -11191,47 +11191,47 @@
       </c>
       <c r="AC51" s="29">
         <f t="shared" si="16"/>
-        <v>1.1049999999999978</v>
+        <v>1.2549999999999957</v>
       </c>
       <c r="AD51" s="29">
         <f t="shared" si="6"/>
-        <v>1.1049899999999977</v>
+        <v>1.2549899999999956</v>
       </c>
       <c r="AE51" s="29">
         <f t="shared" ref="AE51:AE70" si="19">AC51+$AC$7</f>
-        <v>1.1050099999999978</v>
+        <v>1.2550099999999957</v>
       </c>
       <c r="AF51" s="30">
         <f t="shared" ref="AF51:AF70" si="20">$E$29 + LN(AC51/$B$5) * $E$30 + (LN(AC51/$B$5))^2 * $E$31</f>
-        <v>7.7361020722553506E-2</v>
+        <v>8.3680766487620684E-2</v>
       </c>
       <c r="AG51" s="30">
         <f t="shared" ref="AG51:AG70" si="21">$E$29 + LN(AD51/$B$5) * $E$30 + (LN(AD51/$B$5))^2 * $E$31</f>
-        <v>7.7359751161438228E-2</v>
+        <v>8.3676992880535886E-2</v>
       </c>
       <c r="AH51" s="30">
         <f t="shared" ref="AH51:AH70" si="22">$E$29 + LN(AE51/$B$5) * $E$30 + (LN(AE51/$B$5))^2 * $E$31</f>
-        <v>7.7362290719214369E-2</v>
+        <v>8.3684540534249022E-2</v>
       </c>
       <c r="AI51" s="31">
         <f t="shared" ref="AI51:AI70" si="23">$B$1 * EXP(-$B$4*$B$2) * _xlfn.NORM.DIST((LN($B$1/AC51) + ($B$3-$B$4+AF51^2/2)*$B$2)/(AF51*SQRT($B$2)), 0, 1, TRUE) - AC51*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST((LN($B$1/AC51) + ($B$3-$B$4-AF51^2/2)*$B$2)/(AF51*SQRT($B$2)), 0, 1, TRUE)</f>
-        <v>9.4570690612001407E-3</v>
+        <v>5.3050493114146363E-4</v>
       </c>
       <c r="AJ51" s="31">
         <f t="shared" ref="AJ51:AJ70" si="24">$B$1 * EXP(-$B$4*$B$2) * _xlfn.NORM.DIST((LN($B$1/AD51) + ($B$3-$B$4+AG51^2/2)*$B$2)/(AG51*SQRT($B$2)), 0, 1, TRUE) - AD51*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST((LN($B$1/AD51) + ($B$3-$B$4-AG51^2/2)*$B$2)/(AG51*SQRT($B$2)), 0, 1, TRUE)</f>
-        <v>9.4601038883503907E-3</v>
+        <v>5.3062302406550049E-4</v>
       </c>
       <c r="AK51" s="31">
         <f t="shared" ref="AK51:AK70" si="25">$B$1 * EXP(-$B$4*$B$2) * _xlfn.NORM.DIST((LN($B$1/AE51) + ($B$3-$B$4+AH51^2/2)*$B$2)/(AH51*SQRT($B$2)), 0, 1, TRUE) - AE51*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST((LN($B$1/AE51) + ($B$3-$B$4-AH51^2/2)*$B$2)/(AH51*SQRT($B$2)), 0, 1, TRUE)</f>
-        <v>9.4540351150483315E-3</v>
+        <v>5.3038689054216853E-4</v>
       </c>
       <c r="AL51" s="5">
         <f t="shared" si="14"/>
-        <v>8.8099844086642047</v>
+        <v>0.52324741761644578</v>
       </c>
       <c r="AM51" s="3">
         <f t="shared" si="15"/>
-        <v>4.4800132578061938E-2</v>
+        <v>2.6422775394441145E-3</v>
       </c>
     </row>
     <row r="52" spans="1:39" x14ac:dyDescent="0.25">
@@ -11240,25 +11240,25 @@
       </c>
       <c r="B52" s="20">
         <f>$B$23</f>
-        <v>8.5000000000000006E-3</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="C52" s="12" t="s">
         <v>20</v>
       </c>
       <c r="D52" s="13">
         <f>B48 + B52 + B50/2</f>
-        <v>8.8499999999999995E-2</v>
+        <v>7.350000000000001E-2</v>
       </c>
       <c r="E52" s="14">
         <v>0.1</v>
       </c>
       <c r="F52" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(E52 * EXP($B$4*$B$2), 0, 1) * D52 * SQRT($B$2) - ($B$3 - $B$4 + D52^2/2)*$B$2)</f>
-        <v>1.1518320662656254</v>
+        <v>1.2148813946749826</v>
       </c>
       <c r="G52" s="16">
         <f>EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(1/(D52*SQRT($B$2)) * (LN($B$1 / F52) + ($B$3 - $B$4 + D52^2/2)*$B$2), 0, 1, 1)</f>
-        <v>9.9999999999999936E-2</v>
+        <v>9.9999999999999756E-2</v>
       </c>
       <c r="N52" s="6"/>
       <c r="P52" s="3"/>
@@ -11272,47 +11272,47 @@
       </c>
       <c r="AC52" s="29">
         <f t="shared" si="16"/>
-        <v>1.1099999999999977</v>
+        <v>1.2599999999999956</v>
       </c>
       <c r="AD52" s="29">
         <f t="shared" si="6"/>
-        <v>1.1099899999999976</v>
+        <v>1.2599899999999955</v>
       </c>
       <c r="AE52" s="29">
         <f t="shared" si="19"/>
-        <v>1.1100099999999977</v>
+        <v>1.2600099999999956</v>
       </c>
       <c r="AF52" s="30">
         <f t="shared" si="20"/>
-        <v>7.8050105880475881E-2</v>
+        <v>8.5622399793066795E-2</v>
       </c>
       <c r="AG52" s="30">
         <f t="shared" si="21"/>
-        <v>7.8048620026472268E-2</v>
+        <v>8.5618407748306508E-2</v>
       </c>
       <c r="AH52" s="30">
         <f t="shared" si="22"/>
-        <v>7.8051592164110006E-2</v>
+        <v>8.5626392272036625E-2</v>
       </c>
       <c r="AI52" s="31">
         <f t="shared" si="23"/>
-        <v>8.0467753469892211E-3</v>
+        <v>4.7756405157070927E-4</v>
       </c>
       <c r="AJ52" s="31">
         <f t="shared" si="24"/>
-        <v>8.0493891407479312E-3</v>
+        <v>4.776586126528648E-4</v>
       </c>
       <c r="AK52" s="31">
         <f t="shared" si="25"/>
-        <v>8.0441623550503438E-3</v>
+        <v>4.774695326848731E-4</v>
       </c>
       <c r="AL52" s="5">
         <f t="shared" si="14"/>
-        <v>8.0181983275195972</v>
+        <v>0.4219631935531431</v>
       </c>
       <c r="AM52" s="3">
         <f t="shared" si="15"/>
-        <v>4.0773777960015467E-2</v>
+        <v>2.1308158077043065E-3</v>
       </c>
     </row>
     <row r="53" spans="1:39" x14ac:dyDescent="0.25">
@@ -11334,47 +11334,47 @@
       </c>
       <c r="AC53" s="29">
         <f t="shared" si="16"/>
-        <v>1.1149999999999975</v>
+        <v>1.2649999999999955</v>
       </c>
       <c r="AD53" s="29">
         <f t="shared" si="6"/>
-        <v>1.1149899999999975</v>
+        <v>1.2649899999999954</v>
       </c>
       <c r="AE53" s="29">
         <f t="shared" si="19"/>
-        <v>1.1150099999999976</v>
+        <v>1.2650099999999955</v>
       </c>
       <c r="AF53" s="30">
         <f t="shared" si="20"/>
-        <v>7.8846600691381247E-2</v>
+        <v>8.76725871073777E-2</v>
       </c>
       <c r="AG53" s="30">
         <f t="shared" si="21"/>
-        <v>7.8844901477683055E-2</v>
+        <v>8.7668379272486482E-2</v>
       </c>
       <c r="AH53" s="30">
         <f t="shared" si="22"/>
-        <v>7.8848300328892104E-2</v>
+        <v>8.7676795371222221E-2</v>
       </c>
       <c r="AI53" s="31">
         <f t="shared" si="23"/>
-        <v>6.8368385605129811E-3</v>
+        <v>4.3521817777174981E-4</v>
       </c>
       <c r="AJ53" s="31">
         <f t="shared" si="24"/>
-        <v>6.8390722717742713E-3</v>
+        <v>4.3529369757418918E-4</v>
       </c>
       <c r="AK53" s="31">
         <f t="shared" si="25"/>
-        <v>6.8346055671642536E-3</v>
+        <v>4.3514269224797023E-4</v>
       </c>
       <c r="AL53" s="5">
         <f t="shared" si="14"/>
-        <v>7.1791256273101558</v>
+        <v>0.34278659771791448</v>
       </c>
       <c r="AM53" s="3">
         <f t="shared" si="15"/>
-        <v>3.6506963574391031E-2</v>
+        <v>1.7309924473176092E-3</v>
       </c>
     </row>
     <row r="54" spans="1:39" x14ac:dyDescent="0.25">
@@ -11399,47 +11399,47 @@
       </c>
       <c r="AC54" s="29">
         <f t="shared" si="16"/>
-        <v>1.1199999999999974</v>
+        <v>1.2699999999999954</v>
       </c>
       <c r="AD54" s="29">
         <f t="shared" si="6"/>
-        <v>1.1199899999999974</v>
+        <v>1.2699899999999953</v>
       </c>
       <c r="AE54" s="29">
         <f t="shared" si="19"/>
-        <v>1.1200099999999975</v>
+        <v>1.2700099999999954</v>
       </c>
       <c r="AF54" s="30">
         <f t="shared" si="20"/>
-        <v>7.9749050656852213E-2</v>
+        <v>8.9830014333091235E-2</v>
       </c>
       <c r="AG54" s="30">
         <f t="shared" si="21"/>
-        <v>7.9747140968519856E-2</v>
+        <v>8.9825593317107461E-2</v>
       </c>
       <c r="AH54" s="30">
         <f t="shared" si="22"/>
-        <v>7.9750960763274675E-2</v>
+        <v>8.9834435772848303E-2</v>
       </c>
       <c r="AI54" s="31">
         <f t="shared" si="23"/>
-        <v>5.8063667066265701E-3</v>
+        <v>4.014780382017441E-4</v>
       </c>
       <c r="AJ54" s="31">
         <f t="shared" si="24"/>
-        <v>5.808262611183862E-3</v>
+        <v>4.0153802472911101E-4</v>
       </c>
       <c r="AK54" s="31">
         <f t="shared" si="25"/>
-        <v>5.8044714354045235E-3</v>
+        <v>4.0141807977182864E-4</v>
       </c>
       <c r="AL54" s="5">
         <f t="shared" si="14"/>
-        <v>6.3333524535913446</v>
+        <v>0.28097451448827465</v>
       </c>
       <c r="AM54" s="3">
         <f t="shared" si="15"/>
-        <v>3.2206076245202664E-2</v>
+        <v>1.4188558295624332E-3</v>
       </c>
     </row>
     <row r="55" spans="1:39" x14ac:dyDescent="0.25">
@@ -11464,47 +11464,47 @@
       </c>
       <c r="AC55" s="29">
         <f t="shared" si="16"/>
-        <v>1.1249999999999973</v>
+        <v>1.2749999999999952</v>
       </c>
       <c r="AD55" s="29">
         <f t="shared" si="6"/>
-        <v>1.1249899999999973</v>
+        <v>1.2749899999999952</v>
       </c>
       <c r="AE55" s="29">
         <f t="shared" si="19"/>
-        <v>1.1250099999999974</v>
+        <v>1.2750099999999953</v>
       </c>
       <c r="AF55" s="30">
         <f t="shared" si="20"/>
-        <v>8.0756025100305467E-2</v>
+        <v>9.2093386452607617E-2</v>
       </c>
       <c r="AG55" s="30">
         <f t="shared" si="21"/>
-        <v>8.075390777523947E-2</v>
+        <v>9.208875482675255E-2</v>
       </c>
       <c r="AH55" s="30">
         <f t="shared" si="22"/>
-        <v>8.075814283783242E-2</v>
+        <v>9.2098018497131034E-2</v>
       </c>
       <c r="AI55" s="31">
         <f t="shared" si="23"/>
-        <v>4.9342845758775233E-3</v>
+        <v>3.7479053110854588E-4</v>
       </c>
       <c r="AJ55" s="31">
         <f t="shared" si="24"/>
-        <v>4.9358844236270516E-3</v>
+        <v>3.7483772158937445E-4</v>
       </c>
       <c r="AK55" s="31">
         <f t="shared" si="25"/>
-        <v>4.9326852795275045E-3</v>
+        <v>3.7474336390484753E-4</v>
       </c>
       <c r="AL55" s="5">
         <f t="shared" si="14"/>
-        <v>5.5139950938531959</v>
+        <v>0.23277130223320339</v>
       </c>
       <c r="AM55" s="3">
         <f t="shared" si="15"/>
-        <v>2.8039517413500314E-2</v>
+        <v>1.1754408392872305E-3</v>
       </c>
     </row>
     <row r="56" spans="1:39" x14ac:dyDescent="0.25">
@@ -11526,54 +11526,54 @@
       </c>
       <c r="AC56" s="29">
         <f t="shared" si="16"/>
-        <v>1.1299999999999972</v>
+        <v>1.2799999999999951</v>
       </c>
       <c r="AD56" s="29">
         <f t="shared" si="6"/>
-        <v>1.1299899999999972</v>
+        <v>1.2799899999999951</v>
       </c>
       <c r="AE56" s="29">
         <f t="shared" si="19"/>
-        <v>1.1300099999999973</v>
+        <v>1.2800099999999952</v>
       </c>
       <c r="AF56" s="30">
         <f t="shared" si="20"/>
-        <v>8.1866116686217391E-2</v>
+        <v>9.4461427187416985E-2</v>
       </c>
       <c r="AG56" s="30">
         <f t="shared" si="21"/>
-        <v>8.1863794516108104E-2</v>
+        <v>9.4456587485768823E-2</v>
       </c>
       <c r="AH56" s="30">
         <f t="shared" si="22"/>
-        <v>8.1868439263249909E-2</v>
+        <v>9.4466267302702078E-2</v>
       </c>
       <c r="AI56" s="31">
         <f t="shared" si="23"/>
-        <v>4.200159290225991E-3</v>
+        <v>3.5394444370252798E-4</v>
       </c>
       <c r="AJ56" s="31">
         <f t="shared" si="24"/>
-        <v>4.201502862566181E-3</v>
+        <v>3.5398097151341859E-4</v>
       </c>
       <c r="AK56" s="31">
         <f t="shared" si="25"/>
-        <v>4.1988161924409739E-3</v>
+        <v>3.539079354144721E-4</v>
       </c>
       <c r="AL56" s="5">
         <f t="shared" si="14"/>
-        <v>4.7455517293570884</v>
+        <v>0.19522834737717429</v>
       </c>
       <c r="AM56" s="3">
         <f t="shared" si="15"/>
-        <v>2.4131864117962032E-2</v>
+        <v>9.8585766497873237E-4</v>
       </c>
     </row>
     <row r="57" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A57" s="35" t="s">
+      <c r="A57" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="B57" s="35"/>
+      <c r="B57" s="33"/>
       <c r="D57" t="s">
         <v>56</v>
       </c>
@@ -11592,47 +11592,47 @@
       </c>
       <c r="AC57" s="29">
         <f t="shared" si="16"/>
-        <v>1.1349999999999971</v>
+        <v>1.284999999999995</v>
       </c>
       <c r="AD57" s="29">
         <f t="shared" si="6"/>
-        <v>1.1349899999999971</v>
+        <v>1.284989999999995</v>
       </c>
       <c r="AE57" s="29">
         <f t="shared" si="19"/>
-        <v>1.1350099999999972</v>
+        <v>1.2850099999999951</v>
       </c>
       <c r="AF57" s="30">
         <f t="shared" si="20"/>
-        <v>8.3077940950987819E-2</v>
+        <v>9.6932878664624716E-2</v>
       </c>
       <c r="AG57" s="30">
         <f t="shared" si="21"/>
-        <v>8.3075416682242456E-2</v>
+        <v>9.69278333847787E-2</v>
       </c>
       <c r="AH57" s="30">
         <f t="shared" si="22"/>
-        <v>8.3080465621208396E-2</v>
+        <v>9.6937924353148713E-2</v>
       </c>
       <c r="AI57" s="31">
         <f t="shared" si="23"/>
-        <v>3.5848128645590005E-3</v>
+        <v>3.3799643171340821E-4</v>
       </c>
       <c r="AJ57" s="31">
         <f t="shared" si="24"/>
-        <v>3.5859369649805239E-3</v>
+        <v>3.3802395693942333E-4</v>
       </c>
       <c r="AK57" s="31">
         <f t="shared" si="25"/>
-        <v>3.5836891685357974E-3</v>
+        <v>3.3796892309216273E-4</v>
       </c>
       <c r="AL57" s="5">
         <f t="shared" si="14"/>
-        <v>4.0439832038607895</v>
+        <v>0.16604769642603043</v>
       </c>
       <c r="AM57" s="3">
         <f t="shared" si="15"/>
-        <v>2.056427971634614E-2</v>
+        <v>8.3850217692721808E-4</v>
       </c>
     </row>
     <row r="58" spans="1:39" x14ac:dyDescent="0.25">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="E58" s="16">
         <f>INDEX(LINEST(D48:D52, A59:B63, 1, 0), 3)</f>
-        <v>7.6809680272726152E-2</v>
+        <v>7.0473961258901374E-2</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="3"/>
@@ -11664,64 +11664,64 @@
       </c>
       <c r="AC58" s="29">
         <f t="shared" si="16"/>
-        <v>1.139999999999997</v>
+        <v>1.2899999999999949</v>
       </c>
       <c r="AD58" s="29">
         <f t="shared" si="6"/>
-        <v>1.139989999999997</v>
+        <v>1.2899899999999949</v>
       </c>
       <c r="AE58" s="29">
         <f t="shared" si="19"/>
-        <v>1.1400099999999971</v>
+        <v>1.290009999999995</v>
       </c>
       <c r="AF58" s="30">
         <f t="shared" si="20"/>
-        <v>8.4390135845114081E-2</v>
+        <v>9.9506501090592142E-2</v>
       </c>
       <c r="AG58" s="30">
         <f t="shared" si="21"/>
-        <v>8.4387412179761132E-2</v>
+        <v>9.9501252694305625E-2</v>
       </c>
       <c r="AH58" s="30">
         <f t="shared" si="22"/>
-        <v>8.4392859906582032E-2</v>
+        <v>9.9511749890668494E-2</v>
       </c>
       <c r="AI58" s="31">
         <f t="shared" si="23"/>
-        <v>3.0707235386316367E-3</v>
+        <v>3.2621328073834804E-4</v>
       </c>
       <c r="AJ58" s="31">
         <f t="shared" si="24"/>
-        <v>3.0716613877672383E-3</v>
+        <v>3.2623309175497037E-4</v>
       </c>
       <c r="AK58" s="31">
         <f t="shared" si="25"/>
-        <v>3.0697860312684788E-3</v>
+        <v>3.2619348406625823E-4</v>
       </c>
       <c r="AL58" s="5">
         <f t="shared" si="14"/>
-        <v>3.4177244367938893</v>
+        <v>0.14344532506260774</v>
       </c>
       <c r="AM58" s="3">
         <f t="shared" si="15"/>
-        <v>1.7379657077834031E-2</v>
+        <v>7.2436546801846191E-4</v>
       </c>
     </row>
     <row r="59" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A59" s="16">
         <f>LN(F48 / $B$5)</f>
-        <v>-5.2621637431776239E-2</v>
+        <v>-5.6945420648547525E-2</v>
       </c>
       <c r="B59" s="16">
         <f>A59^2</f>
-        <v>2.7690367260013141E-3</v>
+        <v>3.2427809328400229E-3</v>
       </c>
       <c r="D59" s="12" t="s">
         <v>26</v>
       </c>
       <c r="E59" s="16">
         <f>INDEX(LINEST(D48:D52, A59:B63, 1, 0), 2)</f>
-        <v>5.2220455030935427E-2</v>
+        <v>-0.11814139885599927</v>
       </c>
       <c r="F59" s="6"/>
       <c r="G59" s="3"/>
@@ -11738,64 +11738,64 @@
       </c>
       <c r="AC59" s="29">
         <f t="shared" si="16"/>
-        <v>1.1449999999999969</v>
+        <v>1.2949999999999948</v>
       </c>
       <c r="AD59" s="29">
         <f t="shared" si="6"/>
-        <v>1.1449899999999968</v>
+        <v>1.2949899999999948</v>
       </c>
       <c r="AE59" s="29">
         <f t="shared" si="19"/>
-        <v>1.145009999999997</v>
+        <v>1.2950099999999949</v>
       </c>
       <c r="AF59" s="30">
         <f t="shared" si="20"/>
-        <v>8.5801361286355571E-2</v>
+        <v>0.10218107243151314</v>
       </c>
       <c r="AG59" s="30">
         <f t="shared" si="21"/>
-        <v>8.5798440882927873E-2</v>
+        <v>0.10217562334533849</v>
       </c>
       <c r="AH59" s="30">
         <f t="shared" si="22"/>
-        <v>8.5804282080624239E-2</v>
+        <v>0.10218652191665938</v>
       </c>
       <c r="AI59" s="31">
         <f t="shared" si="23"/>
-        <v>2.642239554987158E-3</v>
+        <v>3.1802706055063593E-4</v>
       </c>
       <c r="AJ59" s="31">
         <f t="shared" si="24"/>
-        <v>2.6430205275615459E-3</v>
+        <v>3.1804015279919204E-4</v>
       </c>
       <c r="AK59" s="31">
         <f t="shared" si="25"/>
-        <v>2.6414588693245422E-3</v>
+        <v>3.1801398090598038E-4</v>
       </c>
       <c r="AL59" s="5">
         <f t="shared" si="14"/>
-        <v>2.8691177211825898</v>
+        <v>0.1260390056212479</v>
       </c>
       <c r="AM59" s="3">
         <f t="shared" si="15"/>
-        <v>1.4589907124538951E-2</v>
+        <v>6.364676106075188E-4</v>
       </c>
     </row>
     <row r="60" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A60" s="16">
         <f>LN(F49 / $B$5)</f>
-        <v>-2.5834349674600837E-2</v>
+        <v>-2.5707057589528355E-2</v>
       </c>
       <c r="B60" s="16">
         <f>A60^2</f>
-        <v>6.6741362310954839E-4</v>
+        <v>6.6085280991132742E-4</v>
       </c>
       <c r="D60" s="12" t="s">
         <v>27</v>
       </c>
       <c r="E60" s="16">
         <f>INDEX(LINEST(D48:D52, A59:B63, 1, 0), 1)</f>
-        <v>2.6666889465631205</v>
+        <v>3.6128335465894481</v>
       </c>
       <c r="F60" s="6"/>
       <c r="G60" s="3"/>
@@ -11812,57 +11812,57 @@
       </c>
       <c r="AC60" s="29">
         <f t="shared" si="16"/>
-        <v>1.1499999999999968</v>
+        <v>1.2999999999999947</v>
       </c>
       <c r="AD60" s="29">
         <f t="shared" si="6"/>
-        <v>1.1499899999999967</v>
+        <v>1.2999899999999946</v>
       </c>
       <c r="AE60" s="29">
         <f t="shared" si="19"/>
-        <v>1.1500099999999969</v>
+        <v>1.3000099999999948</v>
       </c>
       <c r="AF60" s="30">
         <f t="shared" si="20"/>
-        <v>8.7310298723580301E-2</v>
+        <v>0.10495538810075672</v>
       </c>
       <c r="AG60" s="30">
         <f t="shared" si="21"/>
-        <v>8.7307184197976742E-2</v>
+        <v>0.10494974071665944</v>
       </c>
       <c r="AH60" s="30">
         <f t="shared" si="22"/>
-        <v>8.7313413634835177E-2</v>
+        <v>0.10496103587907596</v>
       </c>
       <c r="AI60" s="31">
         <f t="shared" si="23"/>
-        <v>2.2856411528379694E-3</v>
+        <v>3.1300038011328885E-4</v>
       </c>
       <c r="AJ60" s="31">
         <f t="shared" si="24"/>
-        <v>2.2862907788553377E-3</v>
+        <v>3.1300751708777594E-4</v>
       </c>
       <c r="AK60" s="31">
         <f t="shared" si="25"/>
-        <v>2.2849917664233832E-3</v>
+        <v>3.1299325441457373E-4</v>
       </c>
       <c r="AL60" s="5">
         <f t="shared" si="14"/>
-        <v>2.3960278205947811</v>
+        <v>0.11275771982788284</v>
       </c>
       <c r="AM60" s="3">
         <f t="shared" si="15"/>
-        <v>1.2184171849135719E-2</v>
+        <v>5.6940021196347874E-4</v>
       </c>
     </row>
     <row r="61" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A61" s="16">
         <f>LN(F50 / $B$5)</f>
-        <v>4.5508404811666253E-4</v>
+        <v>3.8159626475972114E-4</v>
       </c>
       <c r="B61" s="16">
         <f>A61^2</f>
-        <v>2.0710149085024881E-7</v>
+        <v>1.4561570927857119E-7</v>
       </c>
       <c r="F61" s="6"/>
       <c r="G61" s="3"/>
@@ -11875,61 +11875,61 @@
       </c>
       <c r="Z61" s="7">
         <f t="shared" si="5"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC61" s="29">
         <f t="shared" si="16"/>
-        <v>1.1549999999999967</v>
+        <v>1.3049999999999946</v>
       </c>
       <c r="AD61" s="29">
         <f t="shared" si="6"/>
-        <v>1.1549899999999966</v>
+        <v>1.3049899999999945</v>
       </c>
       <c r="AE61" s="29">
         <f t="shared" si="19"/>
-        <v>1.1550099999999968</v>
+        <v>1.3050099999999947</v>
       </c>
       <c r="AF61" s="30">
         <f t="shared" si="20"/>
-        <v>8.8915650710995484E-2</v>
+        <v>0.10782826065280654</v>
       </c>
       <c r="AG61" s="30">
         <f t="shared" si="21"/>
-        <v>8.8912344637322449E-2</v>
+        <v>0.10782241732877099</v>
       </c>
       <c r="AH61" s="30">
         <f t="shared" si="22"/>
-        <v>8.891895716521292E-2</v>
+        <v>0.10783410436638168</v>
       </c>
       <c r="AI61" s="31">
         <f t="shared" si="23"/>
-        <v>1.9890902562870322E-3</v>
+        <v>3.1079949559060377E-4</v>
       </c>
       <c r="AJ61" s="31">
         <f t="shared" si="24"/>
-        <v>1.9896304081987032E-3</v>
+        <v>3.1080125603707986E-4</v>
       </c>
       <c r="AK61" s="31">
         <f t="shared" si="25"/>
-        <v>1.9885503037083141E-3</v>
+        <v>3.1079774542163568E-4</v>
       </c>
       <c r="AL61" s="5">
         <f t="shared" si="14"/>
-        <v>1.9933295292151596</v>
+        <v>0.1027750801130267</v>
       </c>
       <c r="AM61" s="3">
         <f t="shared" si="15"/>
-        <v>1.0136388787791859E-2</v>
+        <v>5.1899020741327545E-4</v>
       </c>
     </row>
     <row r="62" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A62" s="16">
         <f>LN(F51 / $B$5)</f>
-        <v>2.7864705820005477E-2</v>
+        <v>2.3722351444471133E-2</v>
       </c>
       <c r="B62" s="16">
         <f>A62^2</f>
-        <v>7.7644183043544708E-4</v>
+        <v>5.6274995805500163E-4</v>
       </c>
       <c r="D62" s="3"/>
       <c r="E62" s="10"/>
@@ -11944,61 +11944,61 @@
       </c>
       <c r="Z62" s="7">
         <f t="shared" si="5"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC62" s="29">
         <f t="shared" si="16"/>
-        <v>1.1599999999999966</v>
+        <v>1.3099999999999945</v>
       </c>
       <c r="AD62" s="29">
         <f t="shared" si="6"/>
-        <v>1.1599899999999965</v>
+        <v>1.3099899999999944</v>
       </c>
       <c r="AE62" s="29">
         <f t="shared" si="19"/>
-        <v>1.1600099999999967</v>
+        <v>1.3100099999999946</v>
       </c>
       <c r="AF62" s="30">
         <f t="shared" si="20"/>
-        <v>9.0616140492472588E-2</v>
+        <v>0.11079851948363537</v>
       </c>
       <c r="AG62" s="30">
         <f t="shared" si="21"/>
-        <v>9.0612645403865433E-2</v>
+        <v>0.11079248254425783</v>
       </c>
       <c r="AH62" s="30">
         <f t="shared" si="22"/>
-        <v>9.0619635956598388E-2</v>
+        <v>0.11080455680793636</v>
       </c>
       <c r="AI62" s="31">
         <f t="shared" si="23"/>
-        <v>1.7425050742043424E-3</v>
+        <v>3.1117349182008605E-4</v>
       </c>
       <c r="AJ62" s="31">
         <f t="shared" si="24"/>
-        <v>1.7429542705625356E-3</v>
+        <v>3.111703062942707E-4</v>
       </c>
       <c r="AK62" s="31">
         <f t="shared" si="25"/>
-        <v>1.7420560432646892E-3</v>
+        <v>3.1117668689058242E-4</v>
       </c>
       <c r="AL62" s="5">
         <f t="shared" si="14"/>
-        <v>1.6541853997686926</v>
+        <v>9.5446810177701721E-2</v>
       </c>
       <c r="AM62" s="3">
         <f t="shared" si="15"/>
-        <v>8.4117884641714408E-3</v>
+        <v>4.8198415176698345E-4</v>
       </c>
     </row>
     <row r="63" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A63" s="16">
         <f>LN(F52 / $B$5)</f>
-        <v>5.7542595411994329E-2</v>
+        <v>4.7662286390246132E-2</v>
       </c>
       <c r="B63" s="16">
         <f>A63^2</f>
-        <v>3.311150286748471E-3</v>
+        <v>2.2716935439458415E-3</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="10"/>
@@ -12013,51 +12013,51 @@
       </c>
       <c r="Z63" s="7">
         <f t="shared" si="5"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC63" s="29">
         <f t="shared" si="16"/>
-        <v>1.1649999999999965</v>
+        <v>1.3149999999999944</v>
       </c>
       <c r="AD63" s="29">
         <f t="shared" si="6"/>
-        <v>1.1649899999999964</v>
+        <v>1.3149899999999943</v>
       </c>
       <c r="AE63" s="29">
         <f t="shared" si="19"/>
-        <v>1.1650099999999965</v>
+        <v>1.3150099999999945</v>
       </c>
       <c r="AF63" s="30">
         <f t="shared" si="20"/>
-        <v>9.241051159568775E-2</v>
+        <v>0.11386501053735512</v>
       </c>
       <c r="AG63" s="30">
         <f t="shared" si="21"/>
-        <v>9.2406829985112876E-2</v>
+        <v>0.11385878227442427</v>
       </c>
       <c r="AH63" s="30">
         <f t="shared" si="22"/>
-        <v>9.2414193576835058E-2</v>
+        <v>0.11387123918065836</v>
       </c>
       <c r="AI63" s="31">
         <f t="shared" si="23"/>
-        <v>1.5373911166745718E-3</v>
+        <v>3.1393814495277172E-4</v>
       </c>
       <c r="AJ63" s="31">
         <f t="shared" si="24"/>
-        <v>1.5377648861525511E-3</v>
+        <v>3.1393032418629632E-4</v>
       </c>
       <c r="AK63" s="31">
         <f t="shared" si="25"/>
-        <v>1.5370174842975065E-3</v>
+        <v>3.1394597474689034E-4</v>
       </c>
       <c r="AL63" s="5">
         <f t="shared" si="14"/>
-        <v>1.3710091395502386</v>
+        <v>9.0276432163083328E-2</v>
       </c>
       <c r="AM63" s="3">
         <f t="shared" si="15"/>
-        <v>6.9717934071688329E-3</v>
+        <v>4.5587494751960362E-4</v>
       </c>
     </row>
     <row r="64" spans="1:39" x14ac:dyDescent="0.25">
@@ -12069,51 +12069,51 @@
       </c>
       <c r="Z64" s="7">
         <f t="shared" si="5"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC64" s="29">
         <f t="shared" si="16"/>
-        <v>1.1699999999999964</v>
+        <v>1.3199999999999943</v>
       </c>
       <c r="AD64" s="29">
         <f t="shared" si="6"/>
-        <v>1.1699899999999963</v>
+        <v>1.3199899999999942</v>
       </c>
       <c r="AE64" s="29">
         <f t="shared" si="19"/>
-        <v>1.1700099999999964</v>
+        <v>1.3200099999999944</v>
       </c>
       <c r="AF64" s="30">
         <f t="shared" si="20"/>
-        <v>9.4297527435805231E-2</v>
+        <v>0.11702659601899054</v>
       </c>
       <c r="AG64" s="30">
         <f t="shared" si="21"/>
-        <v>9.4293661756843367E-2</v>
+        <v>0.11702017869205583</v>
       </c>
       <c r="AH64" s="30">
         <f t="shared" si="22"/>
-        <v>9.4301393480471341E-2</v>
+        <v>0.11703301372181048</v>
       </c>
       <c r="AI64" s="31">
         <f t="shared" si="23"/>
-        <v>1.366653057090092E-3</v>
+        <v>3.1896338596181135E-4</v>
       </c>
       <c r="AJ64" s="31">
         <f t="shared" si="24"/>
-        <v>1.3669643211935284E-3</v>
+        <v>3.1895114293068946E-4</v>
       </c>
       <c r="AK64" s="31">
         <f t="shared" si="25"/>
-        <v>1.3663419066038129E-3</v>
+        <v>3.1897563768035729E-4</v>
       </c>
       <c r="AL64" s="5">
         <f t="shared" si="14"/>
-        <v>1.1361715734903297</v>
+        <v>8.6874240440293335E-2</v>
       </c>
       <c r="AM64" s="3">
         <f t="shared" si="15"/>
-        <v>5.7776080822269822E-3</v>
+        <v>4.386946720488506E-4</v>
       </c>
     </row>
     <row r="65" spans="1:39" x14ac:dyDescent="0.25">
@@ -12141,51 +12141,51 @@
       </c>
       <c r="Z65" s="7">
         <f t="shared" si="5"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC65" s="29">
         <f t="shared" si="16"/>
-        <v>1.1749999999999963</v>
+        <v>1.3249999999999942</v>
       </c>
       <c r="AD65" s="29">
         <f t="shared" si="6"/>
-        <v>1.1749899999999962</v>
+        <v>1.3249899999999941</v>
       </c>
       <c r="AE65" s="29">
         <f t="shared" si="19"/>
-        <v>1.1750099999999963</v>
+        <v>1.3250099999999942</v>
       </c>
       <c r="AF65" s="30">
         <f t="shared" si="20"/>
-        <v>9.6275970928443338E-2</v>
+        <v>0.12028215411322575</v>
       </c>
       <c r="AG65" s="30">
         <f t="shared" si="21"/>
-        <v>9.627192359605459E-2</v>
+        <v>0.12027554995015415</v>
       </c>
       <c r="AH65" s="30">
         <f t="shared" si="22"/>
-        <v>9.6280018621744665E-2</v>
+        <v>0.12028875864775826</v>
       </c>
       <c r="AI65" s="31">
         <f t="shared" si="23"/>
-        <v>1.2244048798811316E-3</v>
+        <v>3.261635314992014E-4</v>
       </c>
       <c r="AJ65" s="31">
         <f t="shared" si="24"/>
-        <v>1.2246643259181123E-3</v>
+        <v>3.2614699865378925E-4</v>
       </c>
       <c r="AK65" s="31">
         <f t="shared" si="25"/>
-        <v>1.2241455280885619E-3</v>
+        <v>3.2618007283829152E-4</v>
       </c>
       <c r="AL65" s="5">
         <f t="shared" si="14"/>
-        <v>0.94244410886457064</v>
+        <v>8.4936779831679118E-2</v>
       </c>
       <c r="AM65" s="3">
         <f t="shared" si="15"/>
-        <v>4.7924739779361273E-3</v>
+        <v>4.2891094741429991E-4</v>
       </c>
     </row>
     <row r="66" spans="1:39" x14ac:dyDescent="0.25">
@@ -12194,23 +12194,23 @@
       </c>
       <c r="B66" s="17">
         <f>$F$3</f>
-        <v>1.05</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="C66" s="13">
         <f>E58 + E59*LN(B66/$B$5) + E60*LN(B66/$B$5)^2</f>
-        <v>7.8251485072639529E-2</v>
+        <v>8.622579050245649E-2</v>
       </c>
       <c r="D66" s="18">
         <f>1 / (C66 * SQRT($B$2)) * (LN($B$1/B66) + ($B$3-$B$4 + C66^2/2)*$B$2)</f>
-        <v>0.91465173053641347</v>
+        <v>1.2201302845360589</v>
       </c>
       <c r="E66" s="18">
         <f>1 / (C66 * SQRT($B$2)) * (LN($B$1/B66) + ($B$3-$B$4 - C66^2/2)*$B$2)</f>
-        <v>0.87552598800009362</v>
+        <v>1.1770173892848306</v>
       </c>
       <c r="F66" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(D66,0,1,1) - B66*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(E66, 0, 1, 1)) * $F$2</f>
-        <v>41214.331696617031</v>
+        <v>60526.247840826385</v>
       </c>
       <c r="N66" s="6"/>
       <c r="P66" s="3"/>
@@ -12220,51 +12220,51 @@
       </c>
       <c r="Z66" s="7">
         <f t="shared" si="5"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC66" s="29">
         <f t="shared" si="16"/>
-        <v>1.1799999999999962</v>
+        <v>1.3299999999999941</v>
       </c>
       <c r="AD66" s="29">
         <f t="shared" si="6"/>
-        <v>1.1799899999999961</v>
+        <v>1.329989999999994</v>
       </c>
       <c r="AE66" s="29">
         <f t="shared" si="19"/>
-        <v>1.1800099999999962</v>
+        <v>1.3300099999999941</v>
       </c>
       <c r="AF66" s="30">
         <f t="shared" si="20"/>
-        <v>9.8344644111667809E-2</v>
+        <v>0.12363057870897971</v>
       </c>
       <c r="AG66" s="30">
         <f t="shared" si="21"/>
-        <v>9.8340417502938537E-2</v>
+        <v>0.12362378990650076</v>
       </c>
       <c r="AH66" s="30">
         <f t="shared" si="22"/>
-        <v>9.8348871076592875E-2</v>
+        <v>0.12363736787855695</v>
       </c>
       <c r="AI66" s="31">
         <f t="shared" si="23"/>
-        <v>1.1057896821275379E-3</v>
+        <v>3.354896412784119E-4</v>
       </c>
       <c r="AJ66" s="31">
         <f t="shared" si="24"/>
-        <v>1.1060061089423617E-3</v>
+        <v>3.3546888405417731E-4</v>
       </c>
       <c r="AK66" s="31">
         <f t="shared" si="25"/>
-        <v>1.1055733336383378E-3</v>
+        <v>3.3551040692508978E-4</v>
       </c>
       <c r="AL66" s="5">
         <f t="shared" si="14"/>
-        <v>0.78325623764641239</v>
+        <v>8.4224432983504002E-2</v>
       </c>
       <c r="AM66" s="3">
         <f t="shared" si="15"/>
-        <v>3.9829790453027271E-3</v>
+        <v>4.2531376181173926E-4</v>
       </c>
     </row>
     <row r="67" spans="1:39" x14ac:dyDescent="0.25">
@@ -12273,23 +12273,23 @@
       </c>
       <c r="B67" s="17">
         <f>$F$3 + $F$13</f>
-        <v>1.0501</v>
+        <v>1.1001000000000001</v>
       </c>
       <c r="C67" s="13">
         <f>E58 + E59*LN(B67/$B$5) + E60*LN(B67/$B$5)^2</f>
-        <v>7.8238694643547935E-2</v>
+        <v>8.6181138712864341E-2</v>
       </c>
       <c r="D67" s="18">
         <f>1 / (C67 * SQRT($B$2)) * (LN($B$1/B67) + ($B$3-$B$4 + C67^2/2)*$B$2)</f>
-        <v>0.91236042535030359</v>
+        <v>1.2186304959683001</v>
       </c>
       <c r="E67" s="18">
         <f>1 / (C67 * SQRT($B$2)) * (LN($B$1/B67) + ($B$3-$B$4 - C67^2/2)*$B$2)</f>
-        <v>0.87324107802852968</v>
+        <v>1.1755399266118678</v>
       </c>
       <c r="F67" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(D67,0,1,1) - B67*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(E67, 0, 1, 1)) * $F$2</f>
-        <v>41132.483867325042</v>
+        <v>60434.149188765216</v>
       </c>
       <c r="N67" s="6"/>
       <c r="P67" s="3"/>
@@ -12299,51 +12299,51 @@
       </c>
       <c r="Z67" s="7">
         <f t="shared" si="5"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC67" s="29">
         <f t="shared" si="16"/>
-        <v>1.1849999999999961</v>
+        <v>1.334999999999994</v>
       </c>
       <c r="AD67" s="29">
         <f t="shared" si="6"/>
-        <v>1.184989999999996</v>
+        <v>1.3349899999999939</v>
       </c>
       <c r="AE67" s="29">
         <f t="shared" si="19"/>
-        <v>1.1850099999999961</v>
+        <v>1.335009999999994</v>
       </c>
       <c r="AF67" s="30">
         <f t="shared" si="20"/>
-        <v>0.10050236777676598</v>
+        <v>0.12707077912966708</v>
       </c>
       <c r="AG67" s="30">
         <f t="shared" si="21"/>
-        <v>0.10049796423163911</v>
+        <v>0.12706380785390681</v>
       </c>
       <c r="AH67" s="30">
         <f t="shared" si="22"/>
-        <v>0.10050677167344552</v>
+        <v>0.12707775076822364</v>
       </c>
       <c r="AI67" s="31">
         <f t="shared" si="23"/>
-        <v>1.0068156872240289E-3</v>
+        <v>3.4692351028337357E-4</v>
       </c>
       <c r="AJ67" s="31">
         <f t="shared" si="24"/>
-        <v>1.0069963145079575E-3</v>
+        <v>3.4689853775173897E-4</v>
       </c>
       <c r="AK67" s="31">
         <f t="shared" si="25"/>
-        <v>1.0066351252217901E-3</v>
+        <v>3.4694849126977803E-4</v>
       </c>
       <c r="AL67" s="5">
         <f t="shared" si="14"/>
-        <v>0.65281689776153218</v>
+        <v>8.454769870325228E-2</v>
       </c>
       <c r="AM67" s="3">
         <f t="shared" si="15"/>
-        <v>3.319674838488182E-3</v>
+        <v>4.2694617837378188E-4</v>
       </c>
     </row>
     <row r="68" spans="1:39" x14ac:dyDescent="0.25">
@@ -12352,23 +12352,23 @@
       </c>
       <c r="B68" s="17">
         <f>$F$4</f>
-        <v>1.1000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="C68" s="13">
         <f>E58 + E59*LN(B68/$B$5) + E60*LN(B68/$B$5)^2</f>
-        <v>7.7762771496734398E-2</v>
+        <v>7.0810610119536044E-2</v>
       </c>
       <c r="D68" s="18">
         <f>1 / (C68 * SQRT($B$2)) * (LN($B$1/B68) + ($B$3-$B$4 + C68^2/2)*$B$2)</f>
-        <v>-0.27630492315026506</v>
+        <v>-0.98037909393137179</v>
       </c>
       <c r="E68" s="18">
         <f>1 / (C68 * SQRT($B$2)) * (LN($B$1/B68) + ($B$3-$B$4 - C68^2/2)*$B$2)</f>
-        <v>-0.31518630889863225</v>
+        <v>-1.0157843989911399</v>
       </c>
       <c r="F68" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(D68,0,1,1) - B68*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(E68, 0, 1, 1)) * $F$2</f>
-        <v>11290.130922734175</v>
+        <v>3458.8828285815607</v>
       </c>
       <c r="N68" s="6"/>
       <c r="P68" s="3"/>
@@ -12378,51 +12378,51 @@
       </c>
       <c r="Z68" s="7">
         <f t="shared" si="5"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC68" s="29">
         <f t="shared" si="16"/>
-        <v>1.1899999999999959</v>
+        <v>1.3399999999999939</v>
       </c>
       <c r="AD68" s="29">
         <f t="shared" si="6"/>
-        <v>1.1899899999999959</v>
+        <v>1.3399899999999938</v>
       </c>
       <c r="AE68" s="29">
         <f t="shared" si="19"/>
-        <v>1.190009999999996</v>
+        <v>1.3400099999999939</v>
       </c>
       <c r="AF68" s="30">
         <f t="shared" si="20"/>
-        <v>0.10274798110756456</v>
+        <v>0.13060167986901033</v>
       </c>
       <c r="AG68" s="30">
         <f t="shared" si="21"/>
-        <v>0.10274340292955225</v>
+        <v>0.13059452825601423</v>
       </c>
       <c r="AH68" s="30">
         <f t="shared" si="22"/>
-        <v>0.10275255963255855</v>
+        <v>0.13060883184056041</v>
       </c>
       <c r="AI68" s="31">
         <f t="shared" si="23"/>
-        <v>9.2421150213457121E-4</v>
+        <v>3.6047291881641241E-4</v>
       </c>
       <c r="AJ68" s="31">
         <f t="shared" si="24"/>
-        <v>9.243622399842874E-4</v>
+        <v>3.6044369213390423E-4</v>
       </c>
       <c r="AK68" s="31">
         <f t="shared" si="25"/>
-        <v>9.2406081889823133E-4</v>
+        <v>3.6050215407459896E-4</v>
       </c>
       <c r="AL68" s="5">
         <f t="shared" si="14"/>
-        <v>0.54613376321288587</v>
+        <v>8.5756783618773355E-2</v>
       </c>
       <c r="AM68" s="3">
         <f t="shared" si="15"/>
-        <v>2.7771746080766232E-3</v>
+        <v>4.3305177547374468E-4</v>
       </c>
     </row>
     <row r="69" spans="1:39" x14ac:dyDescent="0.25">
@@ -12431,23 +12431,23 @@
       </c>
       <c r="B69" s="17">
         <f>$F$4+$F$13</f>
-        <v>1.1001000000000001</v>
+        <v>1.2000999999999999</v>
       </c>
       <c r="C69" s="13">
         <f>E58 + E59*LN(B69/$B$5) + E60*LN(B69/$B$5)^2</f>
-        <v>7.7773115697402098E-2</v>
+        <v>7.0822067630880448E-2</v>
       </c>
       <c r="D69" s="18">
         <f>1 / (C69 * SQRT($B$2)) * (LN($B$1/B69) + ($B$3-$B$4 + C69^2/2)*$B$2)</f>
-        <v>-0.2786006977129486</v>
+        <v>-0.98256797846553157</v>
       </c>
       <c r="E69" s="18">
         <f>1 / (C69 * SQRT($B$2)) * (LN($B$1/B69) + ($B$3-$B$4 - C69^2/2)*$B$2)</f>
-        <v>-0.31748725556164958</v>
+        <v>-1.0179790122809718</v>
       </c>
       <c r="F69" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(D69,0,1,1) - B69*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(E69, 0, 1, 1)) * $F$2</f>
-        <v>11255.081427250125</v>
+        <v>3445.1816260736846</v>
       </c>
       <c r="N69" s="6"/>
       <c r="P69" s="3"/>
@@ -12457,51 +12457,51 @@
       </c>
       <c r="Z69" s="7">
         <f t="shared" si="5"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC69" s="29">
         <f t="shared" si="16"/>
-        <v>1.1949999999999958</v>
+        <v>1.3449999999999938</v>
       </c>
       <c r="AD69" s="29">
         <f t="shared" si="6"/>
-        <v>1.1949899999999958</v>
+        <v>1.3449899999999937</v>
       </c>
       <c r="AE69" s="29">
         <f t="shared" si="19"/>
-        <v>1.1950099999999959</v>
+        <v>1.3450099999999938</v>
       </c>
       <c r="AF69" s="30">
         <f t="shared" si="20"/>
-        <v>0.10508034132805902</v>
+        <v>0.1342222203322673</v>
       </c>
       <c r="AG69" s="30">
         <f t="shared" si="21"/>
-        <v>0.10507559078493933</v>
+        <v>0.13421489048851254</v>
       </c>
       <c r="AH69" s="30">
         <f t="shared" si="22"/>
-        <v>0.10508509221366014</v>
+        <v>0.13422955053039243</v>
       </c>
       <c r="AI69" s="31">
         <f t="shared" si="23"/>
-        <v>8.5530125045887168E-4</v>
+        <v>3.7616785131613234E-4</v>
       </c>
       <c r="AJ69" s="31">
         <f t="shared" si="24"/>
-        <v>8.5542692967517653E-4</v>
+        <v>3.7613429047684763E-4</v>
       </c>
       <c r="AK69" s="31">
         <f t="shared" si="25"/>
-        <v>8.5517561714037321E-4</v>
+        <v>3.7620142092857287E-4</v>
       </c>
       <c r="AL69" s="5">
         <f t="shared" si="14"/>
-        <v>0.45897806388861534</v>
+        <v>8.7731558129355833E-2</v>
       </c>
       <c r="AM69" s="3">
         <f t="shared" si="15"/>
-        <v>2.3339744043599123E-3</v>
+        <v>4.4302392661889128E-4</v>
       </c>
     </row>
     <row r="70" spans="1:39" x14ac:dyDescent="0.25">
@@ -12513,51 +12513,51 @@
       </c>
       <c r="Z70" s="7">
         <f t="shared" si="5"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC70" s="29">
         <f t="shared" si="16"/>
-        <v>1.1999999999999957</v>
+        <v>1.3499999999999936</v>
       </c>
       <c r="AD70" s="29">
         <f t="shared" si="6"/>
-        <v>1.1999899999999957</v>
+        <v>1.3499899999999936</v>
       </c>
       <c r="AE70" s="29">
         <f t="shared" si="19"/>
-        <v>1.2000099999999958</v>
+        <v>1.3500099999999937</v>
       </c>
       <c r="AF70" s="30">
         <f t="shared" si="20"/>
-        <v>0.1074983233581316</v>
+        <v>0.1379313545827463</v>
       </c>
       <c r="AG70" s="30">
         <f t="shared" si="21"/>
-        <v>0.10749340268262919</v>
+        <v>0.13792384858564338</v>
       </c>
       <c r="AH70" s="30">
         <f t="shared" si="22"/>
-        <v>0.10750324437168469</v>
+        <v>0.13793886093009355</v>
       </c>
       <c r="AI70" s="31">
         <f t="shared" si="23"/>
-        <v>7.9789871349386643E-4</v>
+        <v>3.9405746212343648E-4</v>
       </c>
       <c r="AJ70" s="31">
         <f t="shared" si="24"/>
-        <v>7.9800327937432775E-4</v>
+        <v>3.9401945140243519E-4</v>
       </c>
       <c r="AK70" s="31">
         <f t="shared" si="25"/>
-        <v>7.9779418639518845E-4</v>
+        <v>3.9409548188173646E-4</v>
       </c>
       <c r="AL70" s="5">
         <f t="shared" si="14"/>
-        <v>0.38781783340269266</v>
+        <v>9.0372986871756197E-2</v>
       </c>
       <c r="AM70" s="3">
         <f t="shared" si="15"/>
-        <v>1.972113632288676E-3</v>
+        <v>4.5636252630062475E-4</v>
       </c>
     </row>
     <row r="71" spans="1:39" x14ac:dyDescent="0.25">
@@ -12566,21 +12566,21 @@
       </c>
       <c r="B71" s="19">
         <f>(F66 - F67) / $F$13</f>
-        <v>818478.2929198991</v>
+        <v>920986.5206116956</v>
       </c>
       <c r="C71" s="12" t="s">
         <v>30</v>
       </c>
       <c r="D71" s="19">
         <f>(F68 - F69) / $F$13</f>
-        <v>350494.95484050567</v>
+        <v>137012.02507876133</v>
       </c>
       <c r="E71" s="12" t="s">
         <v>0</v>
       </c>
       <c r="F71" s="19">
         <f>B71-D71</f>
-        <v>467983.33807939343</v>
+        <v>783974.49553293432</v>
       </c>
       <c r="N71" s="6"/>
       <c r="P71" s="3"/>
@@ -12590,7 +12590,7 @@
       </c>
       <c r="Z71" s="7">
         <f t="shared" si="5"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC71" s="29"/>
     </row>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="Z72" s="7">
         <f t="shared" si="5"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC72" s="11"/>
     </row>
@@ -12641,7 +12641,7 @@
       </c>
       <c r="Z73" s="7">
         <f t="shared" si="5"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC73" s="11"/>
     </row>
@@ -12652,38 +12652,38 @@
       </c>
       <c r="Z74" s="7">
         <f t="shared" si="5"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC74" s="11"/>
     </row>
     <row r="75" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A75" s="35" t="s">
+      <c r="A75" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="B75" s="35"/>
-      <c r="C75" s="35" t="s">
+      <c r="B75" s="33"/>
+      <c r="C75" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="D75" s="35"/>
-      <c r="E75" s="35" t="s">
+      <c r="D75" s="33"/>
+      <c r="E75" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="F75" s="35"/>
-      <c r="G75" s="35"/>
+      <c r="F75" s="33"/>
+      <c r="G75" s="33"/>
       <c r="H75" s="4"/>
-      <c r="J75" s="35" t="s">
+      <c r="J75" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="K75" s="35"/>
-      <c r="L75" s="35" t="s">
+      <c r="K75" s="33"/>
+      <c r="L75" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="M75" s="35"/>
-      <c r="N75" s="35" t="s">
+      <c r="M75" s="33"/>
+      <c r="N75" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="O75" s="35"/>
-      <c r="P75" s="35"/>
+      <c r="O75" s="33"/>
+      <c r="P75" s="33"/>
       <c r="Q75" s="36"/>
       <c r="R75" s="36"/>
       <c r="Y75" s="23">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="Z75" s="7">
         <f t="shared" ref="Z75:Z138" si="27">IF(AND(Y75&gt;=$F$3, Y75&lt;=$F$4), $F$2, 0)</f>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC75" s="11"/>
     </row>
@@ -12745,7 +12745,7 @@
       </c>
       <c r="Z76" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC76" s="11"/>
     </row>
@@ -12755,25 +12755,25 @@
       </c>
       <c r="B77" s="20">
         <f>$B$19</f>
-        <v>7.5499999999999998E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="C77" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D77" s="13">
         <f>B77 + B81 - B79/2</f>
-        <v>8.0499999999999988E-2</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="E77" s="14">
         <v>0.9</v>
       </c>
       <c r="F77" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(E77 * EXP($B$4*$B$2), 0, 1) * D77 * SQRT($B$2) - ($B$3 - $B$4 + D77^2/2)*$B$2)</f>
-        <v>1.0323369799876165</v>
+        <v>1.0949090068168106</v>
       </c>
       <c r="G77" s="16">
         <f t="shared" ref="G77:G79" si="28">EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(1/(D77*SQRT($B$2)) * (LN($B$1 / F77) + ($B$3 - $B$4 + D77^2/2)*$B$2), 0, 1, 1)</f>
-        <v>0.9</v>
+        <v>0.90000000000000024</v>
       </c>
       <c r="H77" s="3"/>
       <c r="J77" s="12" t="s">
@@ -12781,25 +12781,25 @@
       </c>
       <c r="K77" s="20">
         <f>$B$19</f>
-        <v>7.5499999999999998E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="L77" s="12" t="s">
         <v>17</v>
       </c>
       <c r="M77" s="13">
         <f>K77 + K81 - K79/2</f>
-        <v>7.9999999999999988E-2</v>
+        <v>8.6999999999999994E-2</v>
       </c>
       <c r="N77" s="14">
         <v>0.9</v>
       </c>
       <c r="O77" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(N77 * EXP($B$4*$B$2), 0, 1) * M77 * SQRT($B$2) - ($B$3 - $B$4 + M77^2/2)*$B$2)</f>
-        <v>1.0326652065394013</v>
+        <v>1.0952554366665379</v>
       </c>
       <c r="P77" s="16">
         <f t="shared" ref="P77:P79" si="29">EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(1/(M77*SQRT($B$2)) * (LN($B$1 / O77) + ($B$3 - $B$4 + M77^2/2)*$B$2), 0, 1, 1)</f>
-        <v>0.90000000000000058</v>
+        <v>0.9</v>
       </c>
       <c r="Q77" s="3"/>
       <c r="R77" s="3"/>
@@ -12809,7 +12809,7 @@
       </c>
       <c r="Z77" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC77" s="11"/>
     </row>
@@ -12819,21 +12819,21 @@
       </c>
       <c r="B78" s="13">
         <f>$B$20+$F$12</f>
-        <v>4.5000000000000005E-3</v>
+        <v>-7.0000000000000001E-3</v>
       </c>
       <c r="C78" s="12" t="s">
         <v>18</v>
       </c>
       <c r="D78" s="13">
         <f>B77+B80 - B78/2</f>
-        <v>7.5749999999999998E-2</v>
+        <v>7.5500000000000012E-2</v>
       </c>
       <c r="E78" s="14">
         <v>0.75</v>
       </c>
       <c r="F78" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(E78 * EXP($B$4*$B$2), 0, 1) * D78 * SQRT($B$2) - ($B$3 - $B$4 + D78^2/2)*$B$2)</f>
-        <v>1.0602070990284818</v>
+        <v>1.1294872188272151</v>
       </c>
       <c r="G78" s="16">
         <f t="shared" si="28"/>
@@ -12845,25 +12845,25 @@
       </c>
       <c r="K78" s="20">
         <f>$B$20</f>
-        <v>3.5000000000000001E-3</v>
+        <v>-8.0000000000000002E-3</v>
       </c>
       <c r="L78" s="12" t="s">
         <v>18</v>
       </c>
       <c r="M78" s="13">
         <f>K77+K80 - K78/2</f>
-        <v>7.6249999999999998E-2</v>
+        <v>7.6000000000000012E-2</v>
       </c>
       <c r="N78" s="14">
         <v>0.75</v>
       </c>
       <c r="O78" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(N78 * EXP($B$4*$B$2), 0, 1) * M78 * SQRT($B$2) - ($B$3 - $B$4 + M78^2/2)*$B$2)</f>
-        <v>1.0600347861818515</v>
+        <v>1.1293039487620771</v>
       </c>
       <c r="P78" s="16">
         <f t="shared" si="29"/>
-        <v>0.75000000000000078</v>
+        <v>0.75000000000000044</v>
       </c>
       <c r="Q78" s="3"/>
       <c r="R78" s="3"/>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="Z78" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC78" s="11"/>
     </row>
@@ -12883,25 +12883,25 @@
       </c>
       <c r="B79" s="20">
         <f>$B$21</f>
-        <v>7.0000000000000001E-3</v>
+        <v>-1.4999999999999999E-2</v>
       </c>
       <c r="C79" s="12" t="s">
         <v>4</v>
       </c>
       <c r="D79" s="13">
         <f>B77</f>
-        <v>7.5499999999999998E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="E79" s="14">
         <v>0.5</v>
       </c>
       <c r="F79" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(E79 * EXP($B$4*$B$2), 0, 1) * D79 * SQRT($B$2) - ($B$3 - $B$4 + D79^2/2)*$B$2)</f>
-        <v>1.0879017903763666</v>
+        <v>1.1587614138335498</v>
       </c>
       <c r="G79" s="16">
         <f t="shared" si="28"/>
-        <v>0.49999999999999944</v>
+        <v>0.50000000000000022</v>
       </c>
       <c r="H79" s="3"/>
       <c r="J79" s="12" t="s">
@@ -12909,25 +12909,25 @@
       </c>
       <c r="K79" s="13">
         <f>$B$21+$F$12</f>
-        <v>8.0000000000000002E-3</v>
+        <v>-1.3999999999999999E-2</v>
       </c>
       <c r="L79" s="12" t="s">
         <v>4</v>
       </c>
       <c r="M79" s="13">
         <f>K77</f>
-        <v>7.5499999999999998E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="N79" s="14">
         <v>0.5</v>
       </c>
       <c r="O79" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(N79 * EXP($B$4*$B$2), 0, 1) * M79 * SQRT($B$2) - ($B$3 - $B$4 + M79^2/2)*$B$2)</f>
-        <v>1.0879017903763666</v>
+        <v>1.1587614138335498</v>
       </c>
       <c r="P79" s="16">
         <f t="shared" si="29"/>
-        <v>0.49999999999999944</v>
+        <v>0.50000000000000022</v>
       </c>
       <c r="Q79" s="3"/>
       <c r="R79" s="3"/>
@@ -12937,7 +12937,7 @@
       </c>
       <c r="Z79" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC79" s="11"/>
     </row>
@@ -12947,25 +12947,25 @@
       </c>
       <c r="B80" s="20">
         <f>$B$22</f>
-        <v>2.5000000000000001E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="C80" s="12" t="s">
         <v>19</v>
       </c>
       <c r="D80" s="13">
         <f>B77 + B80 + B78/2</f>
-        <v>8.0250000000000002E-2</v>
+        <v>6.8500000000000005E-2</v>
       </c>
       <c r="E80" s="14">
         <v>0.25</v>
       </c>
       <c r="F80" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(E80 * EXP($B$4*$B$2), 0, 1) * D80 * SQRT($B$2) - ($B$3 - $B$4 + D80^2/2)*$B$2)</f>
-        <v>1.1179518812067659</v>
+        <v>1.1859336292735845</v>
       </c>
       <c r="G80" s="16">
         <f>EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(1/(D80*SQRT($B$2)) * (LN($B$1 / F80) + ($B$3 - $B$4 + D80^2/2)*$B$2), 0, 1, 1)</f>
-        <v>0.25</v>
+        <v>0.2500000000000005</v>
       </c>
       <c r="H80" s="3"/>
       <c r="J80" s="12" t="s">
@@ -12973,25 +12973,25 @@
       </c>
       <c r="K80" s="20">
         <f>$B$22</f>
-        <v>2.5000000000000001E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="L80" s="12" t="s">
         <v>19</v>
       </c>
       <c r="M80" s="13">
         <f>K77 + K80 + K78/2</f>
-        <v>7.9750000000000001E-2</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="N80" s="14">
         <v>0.25</v>
       </c>
       <c r="O80" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(N80 * EXP($B$4*$B$2), 0, 1) * M80 * SQRT($B$2) - ($B$3 - $B$4 + M80^2/2)*$B$2)</f>
-        <v>1.1177534735320678</v>
+        <v>1.1857247812154261</v>
       </c>
       <c r="P80" s="16">
         <f>EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(1/(M80*SQRT($B$2)) * (LN($B$1 / O80) + ($B$3 - $B$4 + M80^2/2)*$B$2), 0, 1, 1)</f>
-        <v>0.24999999999999961</v>
+        <v>0.25000000000000094</v>
       </c>
       <c r="Q80" s="3"/>
       <c r="R80" s="3"/>
@@ -13001,7 +13001,7 @@
       </c>
       <c r="Z80" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC80" s="11"/>
     </row>
@@ -13011,25 +13011,25 @@
       </c>
       <c r="B81" s="20">
         <f>$B$23</f>
-        <v>8.5000000000000006E-3</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="C81" s="12" t="s">
         <v>20</v>
       </c>
       <c r="D81" s="13">
         <f>B77 + B81 + B79/2</f>
-        <v>8.7499999999999994E-2</v>
+        <v>7.2500000000000009E-2</v>
       </c>
       <c r="E81" s="14">
         <v>0.1</v>
       </c>
       <c r="F81" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(E81 * EXP($B$4*$B$2), 0, 1) * D81 * SQRT($B$2) - ($B$3 - $B$4 + D81^2/2)*$B$2)</f>
-        <v>1.1510707999322727</v>
+        <v>1.2140828375149078</v>
       </c>
       <c r="G81" s="16">
         <f>EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(1/(D81*SQRT($B$2)) * (LN($B$1 / F81) + ($B$3 - $B$4 + D81^2/2)*$B$2), 0, 1, 1)</f>
-        <v>9.9999999999999784E-2</v>
+        <v>9.9999999999999215E-2</v>
       </c>
       <c r="H81" s="3"/>
       <c r="J81" s="12" t="s">
@@ -13037,25 +13037,25 @@
       </c>
       <c r="K81" s="20">
         <f>$B$23</f>
-        <v>8.5000000000000006E-3</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="L81" s="12" t="s">
         <v>20</v>
       </c>
       <c r="M81" s="13">
         <f>K77 + K81 + K79/2</f>
-        <v>8.7999999999999995E-2</v>
+        <v>7.3000000000000009E-2</v>
       </c>
       <c r="N81" s="14">
         <v>0.1</v>
       </c>
       <c r="O81" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(N81 * EXP($B$4*$B$2), 0, 1) * M81 * SQRT($B$2) - ($B$3 - $B$4 + M81^2/2)*$B$2)</f>
-        <v>1.1514513342034922</v>
+        <v>1.2144820125080726</v>
       </c>
       <c r="P81" s="16">
         <f>EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(1/(M81*SQRT($B$2)) * (LN($B$1 / O81) + ($B$3 - $B$4 + M81^2/2)*$B$2), 0, 1, 1)</f>
-        <v>9.9999999999999686E-2</v>
+        <v>0.10000000000000021</v>
       </c>
       <c r="Q81" s="3"/>
       <c r="R81" s="3"/>
@@ -13065,7 +13065,7 @@
       </c>
       <c r="Z81" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC81" s="11"/>
     </row>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="Z82" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC82" s="11"/>
     </row>
@@ -13113,7 +13113,7 @@
       </c>
       <c r="Z83" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC83" s="11"/>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="Z84" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC84" s="11"/>
     </row>
@@ -13167,25 +13167,25 @@
       </c>
       <c r="Z85" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC85" s="11"/>
     </row>
     <row r="86" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A86" s="35" t="s">
+      <c r="A86" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="B86" s="35"/>
+      <c r="B86" s="33"/>
       <c r="D86" t="s">
         <v>56</v>
       </c>
       <c r="F86" s="6"/>
       <c r="G86" s="3"/>
       <c r="H86" s="5"/>
-      <c r="J86" s="35" t="s">
+      <c r="J86" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="K86" s="35"/>
+      <c r="K86" s="33"/>
       <c r="M86" t="s">
         <v>56</v>
       </c>
@@ -13199,7 +13199,7 @@
       </c>
       <c r="Z86" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC86" s="11"/>
     </row>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="E87" s="16">
         <f>INDEX(LINEST(D77:D81, A88:B92, 1, 0), 3)</f>
-        <v>7.5812269913453079E-2</v>
+        <v>6.946518070165425E-2</v>
       </c>
       <c r="F87" s="6"/>
       <c r="G87" s="3"/>
@@ -13231,7 +13231,7 @@
       </c>
       <c r="N87" s="16">
         <f>INDEX(LINEST(M77:M81, J88:K92, 1, 0), 3)</f>
-        <v>7.5809795633535654E-2</v>
+        <v>6.9474351803922432E-2</v>
       </c>
       <c r="O87" s="6"/>
       <c r="P87" s="3"/>
@@ -13243,43 +13243,43 @@
       </c>
       <c r="Z87" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC87" s="11"/>
     </row>
     <row r="88" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A88" s="16">
         <f>LN(F77 / $B$5)</f>
-        <v>-5.1986035668809515E-2</v>
+        <v>-5.631290706777313E-2</v>
       </c>
       <c r="B88" s="16">
         <f>A88^2</f>
-        <v>2.7025479045587352E-3</v>
+        <v>3.171143502423653E-3</v>
       </c>
       <c r="D88" s="12" t="s">
         <v>26</v>
       </c>
       <c r="E88" s="16">
         <f>INDEX(LINEST(D77:D81, A88:B92, 1, 0), 2)</f>
-        <v>5.6265925927849125E-2</v>
+        <v>-0.11549211454019667</v>
       </c>
       <c r="F88" s="6"/>
       <c r="G88" s="3"/>
       <c r="H88" s="5"/>
       <c r="J88" s="16">
         <f>LN(O77 / $B$5)</f>
-        <v>-5.166814103732649E-2</v>
+        <v>-5.5996556527385777E-2</v>
       </c>
       <c r="K88" s="16">
         <f>J88^2</f>
-        <v>2.6695967982530615E-3</v>
+        <v>3.1356143429247104E-3</v>
       </c>
       <c r="M88" s="12" t="s">
         <v>26</v>
       </c>
       <c r="N88" s="16">
         <f>INDEX(LINEST(M77:M81, J88:K92, 1, 0), 2)</f>
-        <v>5.8822716696682466E-2</v>
+        <v>-0.11304854397681864</v>
       </c>
       <c r="O88" s="6"/>
       <c r="P88" s="3"/>
@@ -13291,43 +13291,43 @@
       </c>
       <c r="Z88" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC88" s="11"/>
     </row>
     <row r="89" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A89" s="16">
         <f>LN(F78 / $B$5)</f>
-        <v>-2.5346914941841457E-2</v>
+        <v>-2.5220427003368632E-2</v>
       </c>
       <c r="B89" s="16">
         <f>A89^2</f>
-        <v>6.4246609706894572E-4</v>
+        <v>6.3606993823224565E-4</v>
       </c>
       <c r="D89" s="12" t="s">
         <v>27</v>
       </c>
       <c r="E89" s="16">
         <f>INDEX(LINEST(D77:D81, A88:B92, 1, 0), 1)</f>
-        <v>2.7230175499928349</v>
+        <v>3.7204916008498397</v>
       </c>
       <c r="F89" s="6"/>
       <c r="G89" s="3"/>
       <c r="H89" s="5"/>
       <c r="J89" s="16">
         <f>LN(O78 / $B$5)</f>
-        <v>-2.5509455686094796E-2</v>
+        <v>-2.5382699698755316E-2</v>
       </c>
       <c r="K89" s="16">
         <f>J89^2</f>
-        <v>6.5073232940083409E-4</v>
+        <v>6.442814439971932E-4</v>
       </c>
       <c r="M89" s="12" t="s">
         <v>27</v>
       </c>
       <c r="N89" s="16">
         <f>INDEX(LINEST(M77:M81, J88:K92, 1, 0), 1)</f>
-        <v>2.7183661576627007</v>
+        <v>3.7253267083323305</v>
       </c>
       <c r="O89" s="6"/>
       <c r="P89" s="3"/>
@@ -13339,29 +13339,29 @@
       </c>
       <c r="Z89" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC89" s="11"/>
     </row>
     <row r="90" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A90" s="16">
         <f>LN(F79 / $B$5)</f>
-        <v>4.3969773703030133E-4</v>
+        <v>3.6751988954891534E-4</v>
       </c>
       <c r="B90" s="16">
         <f>A90^2</f>
-        <v>1.9333409994956802E-7</v>
+        <v>1.3507086921404693E-7</v>
       </c>
       <c r="F90" s="6"/>
       <c r="G90" s="3"/>
       <c r="H90" s="5"/>
       <c r="J90" s="16">
         <f>LN(O79 / $B$5)</f>
-        <v>4.3969773703030133E-4</v>
+        <v>3.6751988954891534E-4</v>
       </c>
       <c r="K90" s="16">
         <f>J90^2</f>
-        <v>1.9333409994956802E-7</v>
+        <v>1.3507086921404693E-7</v>
       </c>
       <c r="O90" s="6"/>
       <c r="P90" s="3"/>
@@ -13373,18 +13373,18 @@
       </c>
       <c r="Z90" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC90" s="11"/>
     </row>
     <row r="91" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A91" s="16">
         <f>LN(F80 / $B$5)</f>
-        <v>2.7687153316862972E-2</v>
+        <v>2.3546169097047414E-2</v>
       </c>
       <c r="B91" s="16">
         <f>A91^2</f>
-        <v>7.6657845879147635E-4</v>
+        <v>5.5442207914675062E-4</v>
       </c>
       <c r="D91" s="3"/>
       <c r="E91" s="10"/>
@@ -13393,11 +13393,11 @@
       <c r="H91" s="5"/>
       <c r="J91" s="16">
         <f>LN(O80 / $B$5)</f>
-        <v>2.7509663313720598E-2</v>
+        <v>2.3370049249623742E-2</v>
       </c>
       <c r="K91" s="16">
         <f>J91^2</f>
-        <v>7.5678157563426496E-4</v>
+        <v>5.4615920192983922E-4</v>
       </c>
       <c r="M91" s="3"/>
       <c r="N91" s="10"/>
@@ -13411,18 +13411,18 @@
       </c>
       <c r="Z91" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC91" s="11"/>
     </row>
     <row r="92" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A92" s="16">
         <f>LN(F81 / $B$5)</f>
-        <v>5.6881459093779917E-2</v>
+        <v>4.7004757408746337E-2</v>
       </c>
       <c r="B92" s="16">
         <f>A92^2</f>
-        <v>3.2355003886373581E-3</v>
+        <v>2.2094472190550937E-3</v>
       </c>
       <c r="D92" s="3"/>
       <c r="E92" s="10"/>
@@ -13431,11 +13431,11 @@
       <c r="H92" s="5"/>
       <c r="J92" s="16">
         <f>LN(O81 / $B$5)</f>
-        <v>5.7211996002887185E-2</v>
+        <v>4.7333490649496254E-2</v>
       </c>
       <c r="K92" s="16">
         <f>J92^2</f>
-        <v>3.2732124866343792E-3</v>
+        <v>2.2404593370659491E-3</v>
       </c>
       <c r="M92" s="3"/>
       <c r="N92" s="10"/>
@@ -13449,7 +13449,7 @@
       </c>
       <c r="Z92" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC92" s="11"/>
     </row>
@@ -13463,7 +13463,7 @@
       </c>
       <c r="Z93" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC93" s="11"/>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="Z94" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC94" s="11"/>
     </row>
@@ -13519,23 +13519,23 @@
       </c>
       <c r="B95" s="17">
         <f>$F$3</f>
-        <v>1.05</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="C95" s="13">
         <f>E87 + E88*LN(B95/$B$5) + E89*LN(B95/$B$5)^2</f>
-        <v>7.7181483642547843E-2</v>
+        <v>8.5367579509653874E-2</v>
       </c>
       <c r="D95" s="18">
         <f>1 / (C95 * SQRT($B$2)) * (LN($B$1/B95) + ($B$3-$B$4 + C95^2/2)*$B$2)</f>
-        <v>0.92679324739747371</v>
+        <v>1.231965145024482</v>
       </c>
       <c r="E95" s="18">
         <f>1 / (C95 * SQRT($B$2)) * (LN($B$1/B95) + ($B$3-$B$4 - C95^2/2)*$B$2)</f>
-        <v>0.88820250557619973</v>
+        <v>1.1892813552696548</v>
       </c>
       <c r="F95" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(D95,0,1,1) - B95*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(E95, 0, 1, 1)) * $F$2</f>
-        <v>41064.044056088875</v>
+        <v>60433.565356773026</v>
       </c>
       <c r="H95" s="5"/>
       <c r="J95" s="12" t="s">
@@ -13543,23 +13543,23 @@
       </c>
       <c r="K95" s="17">
         <f>$F$3</f>
-        <v>1.05</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L95" s="13">
         <f>N87 + N88*LN(K95/$B$5) + N89*LN(K95/$B$5)^2</f>
-        <v>7.7083763151056722E-2</v>
+        <v>8.5263392284413611E-2</v>
       </c>
       <c r="M95" s="18">
         <f>1 / (L95 * SQRT($B$2)) * (LN($B$1/K95) + ($B$3-$B$4 + L95^2/2)*$B$2)</f>
-        <v>0.92791926887286624</v>
+        <v>1.2334184139463502</v>
       </c>
       <c r="N95" s="18">
         <f>1 / (L95 * SQRT($B$2)) * (LN($B$1/K95) + ($B$3-$B$4 - L95^2/2)*$B$2)</f>
-        <v>0.88937738729733784</v>
+        <v>1.1907867178041434</v>
       </c>
       <c r="O95" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(M95,0,1,1) - K95*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(N95, 0, 1, 1)) * $F$2</f>
-        <v>41050.402889909907</v>
+        <v>60422.405491518337</v>
       </c>
       <c r="Q95" s="5"/>
       <c r="R95" s="7"/>
@@ -13569,7 +13569,7 @@
       </c>
       <c r="Z95" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC95" s="11"/>
     </row>
@@ -13579,23 +13579,23 @@
       </c>
       <c r="B96" s="17">
         <f>$F$3 + $F$13</f>
-        <v>1.0501</v>
+        <v>1.1001000000000001</v>
       </c>
       <c r="C96" s="13">
         <f>E87 + E88*LN(B96/$B$5) + E89*LN(B96/$B$5)^2</f>
-        <v>7.7168703257301574E-2</v>
+        <v>8.5322158012220484E-2</v>
       </c>
       <c r="D96" s="18">
         <f>1 / (C96 * SQRT($B$2)) * (LN($B$1/B96) + ($B$3-$B$4 + C96^2/2)*$B$2)</f>
-        <v>0.92447215734199328</v>
+        <v>1.2304674044020067</v>
       </c>
       <c r="E96" s="18">
         <f>1 / (C96 * SQRT($B$2)) * (LN($B$1/B96) + ($B$3-$B$4 - C96^2/2)*$B$2)</f>
-        <v>0.88588780571334258</v>
+        <v>1.1878063253958966</v>
       </c>
       <c r="F96" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(D96,0,1,1) - B96*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(E96, 0, 1, 1)) * $F$2</f>
-        <v>40981.878607949882</v>
+        <v>60341.213066726348</v>
       </c>
       <c r="H96" s="5"/>
       <c r="J96" s="12" t="s">
@@ -13603,23 +13603,23 @@
       </c>
       <c r="K96" s="17">
         <f>$F$3 + $F$13</f>
-        <v>1.0501</v>
+        <v>1.1001000000000001</v>
       </c>
       <c r="L96" s="13">
         <f>N87 + N88*LN(K96/$B$5) + N89*LN(K96/$B$5)^2</f>
-        <v>7.7071257242337765E-2</v>
+        <v>8.5218147534539448E-2</v>
       </c>
       <c r="M96" s="18">
         <f>1 / (L96 * SQRT($B$2)) * (LN($B$1/K96) + ($B$3-$B$4 + L96^2/2)*$B$2)</f>
-        <v>0.92559227155048229</v>
+        <v>1.2319171778530404</v>
       </c>
       <c r="N96" s="18">
         <f>1 / (L96 * SQRT($B$2)) * (LN($B$1/K96) + ($B$3-$B$4 - L96^2/2)*$B$2)</f>
-        <v>0.88705664292931341</v>
+        <v>1.1893081040857707</v>
       </c>
       <c r="O96" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(M96,0,1,1) - K96*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(N96, 0, 1, 1)) * $F$2</f>
-        <v>40968.246445113655</v>
+        <v>60330.051534084552</v>
       </c>
       <c r="Q96" s="5"/>
       <c r="R96" s="7"/>
@@ -13629,7 +13629,7 @@
       </c>
       <c r="Z96" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC96" s="11"/>
     </row>
@@ -13639,23 +13639,23 @@
       </c>
       <c r="B97" s="17">
         <f>$F$4</f>
-        <v>1.1000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="C97" s="13">
         <f>E87 + E88*LN(B97/$B$5) + E89*LN(B97/$B$5)^2</f>
-        <v>7.6819328166295789E-2</v>
+        <v>7.0029884306091278E-2</v>
       </c>
       <c r="D97" s="18">
         <f>1 / (C97 * SQRT($B$2)) * (LN($B$1/B97) + ($B$3-$B$4 + C97^2/2)*$B$2)</f>
-        <v>-0.2801729327611186</v>
+        <v>-0.9917013562176018</v>
       </c>
       <c r="E97" s="18">
         <f>1 / (C97 * SQRT($B$2)) * (LN($B$1/B97) + ($B$3-$B$4 - C97^2/2)*$B$2)</f>
-        <v>-0.31858259684426654</v>
+        <v>-1.0267162983706475</v>
       </c>
       <c r="F97" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(D97,0,1,1) - B97*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(E97, 0, 1, 1)) * $F$2</f>
-        <v>11095.363762145817</v>
+        <v>3348.9351136826717</v>
       </c>
       <c r="H97" s="5"/>
       <c r="J97" s="12" t="s">
@@ -13663,23 +13663,23 @@
       </c>
       <c r="K97" s="17">
         <f>$F$4</f>
-        <v>1.1000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="L97" s="13">
         <f>N87 + N88*LN(K97/$B$5) + N89*LN(K97/$B$5)^2</f>
-        <v>7.6845639382252098E-2</v>
+        <v>7.0131442559991611E-2</v>
       </c>
       <c r="M97" s="18">
         <f>1 / (L97 * SQRT($B$2)) * (LN($B$1/K97) + ($B$3-$B$4 + L97^2/2)*$B$2)</f>
-        <v>-0.28006385085819091</v>
+        <v>-0.99021451822843498</v>
       </c>
       <c r="N97" s="18">
         <f>1 / (L97 * SQRT($B$2)) * (LN($B$1/K97) + ($B$3-$B$4 - L97^2/2)*$B$2)</f>
-        <v>-0.31848667054931695</v>
+        <v>-1.0252802395084306</v>
       </c>
       <c r="O97" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(M97,0,1,1) - K97*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(N97, 0, 1, 1)) * $F$2</f>
-        <v>11100.792668044145</v>
+        <v>3363.1676772711285</v>
       </c>
       <c r="Q97" s="5"/>
       <c r="R97" s="7"/>
@@ -13689,7 +13689,7 @@
       </c>
       <c r="Z97" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC97" s="11"/>
     </row>
@@ -13699,23 +13699,23 @@
       </c>
       <c r="B98" s="17">
         <f>$F$4+$F$13</f>
-        <v>1.1001000000000001</v>
+        <v>1.2000999999999999</v>
       </c>
       <c r="C98" s="13">
         <f>E87 + E88*LN(B98/$B$5) + E89*LN(B98/$B$5)^2</f>
-        <v>7.683015834820088E-2</v>
+        <v>7.0042197362160857E-2</v>
       </c>
       <c r="D98" s="18">
         <f>1 / (C98 * SQRT($B$2)) * (LN($B$1/B98) + ($B$3-$B$4 + C98^2/2)*$B$2)</f>
-        <v>-0.28249441152534482</v>
+        <v>-0.99390028308106693</v>
       </c>
       <c r="E98" s="18">
         <f>1 / (C98 * SQRT($B$2)) * (LN($B$1/B98) + ($B$3-$B$4 - C98^2/2)*$B$2)</f>
-        <v>-0.32090949069944524</v>
+        <v>-1.0289213817621472</v>
       </c>
       <c r="F98" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(D98,0,1,1) - B98*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(E98, 0, 1, 1)) * $F$2</f>
-        <v>11060.540111921424</v>
+        <v>3335.5919826787981</v>
       </c>
       <c r="H98" s="5"/>
       <c r="J98" s="12" t="s">
@@ -13723,23 +13723,23 @@
       </c>
       <c r="K98" s="17">
         <f>$F$4+$F$13</f>
-        <v>1.1001000000000001</v>
+        <v>1.2000999999999999</v>
       </c>
       <c r="L98" s="13">
         <f>N87 + N88*LN(K98/$B$5) + N89*LN(K98/$B$5)^2</f>
-        <v>7.6856692226328974E-2</v>
+        <v>7.014398774752395E-2</v>
       </c>
       <c r="M98" s="18">
         <f>1 / (L98 * SQRT($B$2)) * (LN($B$1/K98) + ($B$3-$B$4 + L98^2/2)*$B$2)</f>
-        <v>-0.28238361896998787</v>
+        <v>-0.99240711313675856</v>
       </c>
       <c r="N98" s="18">
         <f>1 / (L98 * SQRT($B$2)) * (LN($B$1/K98) + ($B$3-$B$4 - L98^2/2)*$B$2)</f>
-        <v>-0.32081196508315235</v>
+        <v>-1.0274791070105205</v>
       </c>
       <c r="O98" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(M98,0,1,1) - K98*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(N98, 0, 1, 1)) * $F$2</f>
-        <v>11066.011388162378</v>
+        <v>3349.8260375691425</v>
       </c>
       <c r="Q98" s="5"/>
       <c r="R98" s="7"/>
@@ -13749,7 +13749,7 @@
       </c>
       <c r="Z98" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC98" s="11"/>
     </row>
@@ -13763,7 +13763,7 @@
       </c>
       <c r="Z99" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC99" s="11"/>
     </row>
@@ -13773,21 +13773,21 @@
       </c>
       <c r="B100" s="19">
         <f>(F95 - F96) / $F$13</f>
-        <v>821654.4813899236</v>
+        <v>923522.90046677808</v>
       </c>
       <c r="C100" s="12" t="s">
         <v>30</v>
       </c>
       <c r="D100" s="19">
         <f>(F97 - F98) / $F$13</f>
-        <v>348236.50224392622</v>
+        <v>133431.31003873624</v>
       </c>
       <c r="E100" s="12" t="s">
         <v>0</v>
       </c>
       <c r="F100" s="19">
         <f>B100-D100</f>
-        <v>473417.97914599738</v>
+        <v>790091.59042804188</v>
       </c>
       <c r="H100" s="5"/>
       <c r="J100" s="12" t="s">
@@ -13795,21 +13795,21 @@
       </c>
       <c r="K100" s="19">
         <f>(O95 - O96) / $F$13</f>
-        <v>821564.4479625189</v>
+        <v>923539.57433784672</v>
       </c>
       <c r="L100" s="12" t="s">
         <v>30</v>
       </c>
       <c r="M100" s="19">
         <f>(O97 - O98) / $F$13</f>
-        <v>347812.79881766747</v>
+        <v>133416.39701985969</v>
       </c>
       <c r="N100" s="12" t="s">
         <v>0</v>
       </c>
       <c r="O100" s="19">
         <f>K100-M100</f>
-        <v>473751.64914485143</v>
+        <v>790123.17731798696</v>
       </c>
       <c r="Q100" s="5"/>
       <c r="R100" s="7"/>
@@ -13819,7 +13819,7 @@
       </c>
       <c r="Z100" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC100" s="11"/>
     </row>
@@ -13831,7 +13831,7 @@
       </c>
       <c r="Z101" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC101" s="11"/>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="Z102" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC102" s="11"/>
     </row>
@@ -13874,37 +13874,37 @@
       </c>
       <c r="Z103" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC103" s="11"/>
     </row>
     <row r="104" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A104" s="35" t="s">
+      <c r="A104" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="B104" s="35"/>
-      <c r="C104" s="35" t="s">
+      <c r="B104" s="33"/>
+      <c r="C104" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="D104" s="35"/>
-      <c r="E104" s="35" t="s">
+      <c r="D104" s="33"/>
+      <c r="E104" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="F104" s="35"/>
-      <c r="G104" s="35"/>
-      <c r="J104" s="35" t="s">
+      <c r="F104" s="33"/>
+      <c r="G104" s="33"/>
+      <c r="J104" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="K104" s="35"/>
-      <c r="L104" s="35" t="s">
+      <c r="K104" s="33"/>
+      <c r="L104" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="M104" s="35"/>
-      <c r="N104" s="35" t="s">
+      <c r="M104" s="33"/>
+      <c r="N104" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="O104" s="35"/>
-      <c r="P104" s="35"/>
+      <c r="O104" s="33"/>
+      <c r="P104" s="33"/>
       <c r="Q104" s="36"/>
       <c r="R104" s="36"/>
       <c r="Y104" s="23">
@@ -13913,7 +13913,7 @@
       </c>
       <c r="Z104" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC104" s="11"/>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="Z105" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC105" s="11"/>
     </row>
@@ -13976,25 +13976,25 @@
       </c>
       <c r="B106" s="20">
         <f>$B$19</f>
-        <v>7.5499999999999998E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="C106" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D106" s="13">
         <f>B106 + B110 - B108/2</f>
-        <v>8.0499999999999988E-2</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="E106" s="14">
         <v>0.9</v>
       </c>
       <c r="F106" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(E106 * EXP($B$4*$B$2), 0, 1) * D106 * SQRT($B$2) - ($B$3 - $B$4 + D106^2/2)*$B$2)</f>
-        <v>1.0323369799876165</v>
+        <v>1.0949090068168106</v>
       </c>
       <c r="G106" s="16">
         <f t="shared" ref="G106:G108" si="30">EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(1/(D106*SQRT($B$2)) * (LN($B$1 / F106) + ($B$3 - $B$4 + D106^2/2)*$B$2), 0, 1, 1)</f>
-        <v>0.9</v>
+        <v>0.90000000000000024</v>
       </c>
       <c r="H106" s="3"/>
       <c r="J106" s="12" t="s">
@@ -14002,25 +14002,25 @@
       </c>
       <c r="K106" s="20">
         <f>$B$19</f>
-        <v>7.5499999999999998E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="L106" s="12" t="s">
         <v>17</v>
       </c>
       <c r="M106" s="13">
         <f>K106 + K110 - K108/2</f>
-        <v>8.1499999999999989E-2</v>
+        <v>8.8499999999999995E-2</v>
       </c>
       <c r="N106" s="14">
         <v>0.9</v>
       </c>
       <c r="O106" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(N106 * EXP($B$4*$B$2), 0, 1) * M106 * SQRT($B$2) - ($B$3 - $B$4 + M106^2/2)*$B$2)</f>
-        <v>1.0316810332656901</v>
+        <v>1.0942166809761167</v>
       </c>
       <c r="P106" s="16">
         <f t="shared" ref="P106:P108" si="31">EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(1/(M106*SQRT($B$2)) * (LN($B$1 / O106) + ($B$3 - $B$4 + M106^2/2)*$B$2), 0, 1, 1)</f>
-        <v>0.90000000000000058</v>
+        <v>0.90000000000000036</v>
       </c>
       <c r="Q106" s="3"/>
       <c r="R106" s="3"/>
@@ -14030,7 +14030,7 @@
       </c>
       <c r="Z106" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC106" s="11"/>
     </row>
@@ -14040,21 +14040,21 @@
       </c>
       <c r="B107" s="20">
         <f>$B$20</f>
-        <v>3.5000000000000001E-3</v>
+        <v>-8.0000000000000002E-3</v>
       </c>
       <c r="C107" s="12" t="s">
         <v>18</v>
       </c>
       <c r="D107" s="13">
         <f>B106+B109 - B107/2</f>
-        <v>7.7249999999999999E-2</v>
+        <v>7.7000000000000013E-2</v>
       </c>
       <c r="E107" s="14">
         <v>0.75</v>
       </c>
       <c r="F107" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(E107 * EXP($B$4*$B$2), 0, 1) * D107 * SQRT($B$2) - ($B$3 - $B$4 + D107^2/2)*$B$2)</f>
-        <v>1.0596904431927263</v>
+        <v>1.1289377095147208</v>
       </c>
       <c r="G107" s="16">
         <f t="shared" si="30"/>
@@ -14066,25 +14066,25 @@
       </c>
       <c r="K107" s="20">
         <f>$B$20</f>
-        <v>3.5000000000000001E-3</v>
+        <v>-8.0000000000000002E-3</v>
       </c>
       <c r="L107" s="12" t="s">
         <v>18</v>
       </c>
       <c r="M107" s="13">
         <f>K106+K109 - K107/2</f>
-        <v>7.6249999999999998E-2</v>
+        <v>7.6000000000000012E-2</v>
       </c>
       <c r="N107" s="14">
         <v>0.75</v>
       </c>
       <c r="O107" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(N107 * EXP($B$4*$B$2), 0, 1) * M107 * SQRT($B$2) - ($B$3 - $B$4 + M107^2/2)*$B$2)</f>
-        <v>1.0600347861818515</v>
+        <v>1.1293039487620771</v>
       </c>
       <c r="P107" s="16">
         <f t="shared" si="31"/>
-        <v>0.75000000000000078</v>
+        <v>0.75000000000000044</v>
       </c>
       <c r="Q107" s="3"/>
       <c r="R107" s="3"/>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="Z107" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC107" s="11"/>
     </row>
@@ -14104,25 +14104,25 @@
       </c>
       <c r="B108" s="20">
         <f>$B$21</f>
-        <v>7.0000000000000001E-3</v>
+        <v>-1.4999999999999999E-2</v>
       </c>
       <c r="C108" s="12" t="s">
         <v>4</v>
       </c>
       <c r="D108" s="13">
         <f>B106</f>
-        <v>7.5499999999999998E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="E108" s="14">
         <v>0.5</v>
       </c>
       <c r="F108" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(E108 * EXP($B$4*$B$2), 0, 1) * D108 * SQRT($B$2) - ($B$3 - $B$4 + D108^2/2)*$B$2)</f>
-        <v>1.0879017903763666</v>
+        <v>1.1587614138335498</v>
       </c>
       <c r="G108" s="16">
         <f t="shared" si="30"/>
-        <v>0.49999999999999944</v>
+        <v>0.50000000000000022</v>
       </c>
       <c r="H108" s="3"/>
       <c r="J108" s="12" t="s">
@@ -14130,25 +14130,25 @@
       </c>
       <c r="K108" s="20">
         <f>$B$21</f>
-        <v>7.0000000000000001E-3</v>
+        <v>-1.4999999999999999E-2</v>
       </c>
       <c r="L108" s="12" t="s">
         <v>4</v>
       </c>
       <c r="M108" s="13">
         <f>K106</f>
-        <v>7.5499999999999998E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="N108" s="14">
         <v>0.5</v>
       </c>
       <c r="O108" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(N108 * EXP($B$4*$B$2), 0, 1) * M108 * SQRT($B$2) - ($B$3 - $B$4 + M108^2/2)*$B$2)</f>
-        <v>1.0879017903763666</v>
+        <v>1.1587614138335498</v>
       </c>
       <c r="P108" s="16">
         <f t="shared" si="31"/>
-        <v>0.49999999999999944</v>
+        <v>0.50000000000000022</v>
       </c>
       <c r="Q108" s="3"/>
       <c r="R108" s="3"/>
@@ -14158,7 +14158,7 @@
       </c>
       <c r="Z108" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC108" s="11"/>
     </row>
@@ -14168,25 +14168,25 @@
       </c>
       <c r="B109" s="13">
         <f>$B$22+$F$12</f>
-        <v>3.5000000000000001E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="C109" s="12" t="s">
         <v>19</v>
       </c>
       <c r="D109" s="13">
         <f>B106 + B109 + B107/2</f>
-        <v>8.0750000000000002E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="E109" s="14">
         <v>0.25</v>
       </c>
       <c r="F109" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(E109 * EXP($B$4*$B$2), 0, 1) * D109 * SQRT($B$2) - ($B$3 - $B$4 + D109^2/2)*$B$2)</f>
-        <v>1.1181503939843658</v>
+        <v>1.1861425882511798</v>
       </c>
       <c r="G109" s="16">
         <f>EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(1/(D109*SQRT($B$2)) * (LN($B$1 / F109) + ($B$3 - $B$4 + D109^2/2)*$B$2), 0, 1, 1)</f>
-        <v>0.25000000000000039</v>
+        <v>0.25000000000000011</v>
       </c>
       <c r="H109" s="3"/>
       <c r="J109" s="12" t="s">
@@ -14194,25 +14194,25 @@
       </c>
       <c r="K109" s="20">
         <f>$B$22</f>
-        <v>2.5000000000000001E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="L109" s="12" t="s">
         <v>19</v>
       </c>
       <c r="M109" s="13">
         <f>K106 + K109 + K107/2</f>
-        <v>7.9750000000000001E-2</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="N109" s="14">
         <v>0.25</v>
       </c>
       <c r="O109" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(N109 * EXP($B$4*$B$2), 0, 1) * M109 * SQRT($B$2) - ($B$3 - $B$4 + M109^2/2)*$B$2)</f>
-        <v>1.1177534735320678</v>
+        <v>1.1857247812154261</v>
       </c>
       <c r="P109" s="16">
         <f>EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(1/(M109*SQRT($B$2)) * (LN($B$1 / O109) + ($B$3 - $B$4 + M109^2/2)*$B$2), 0, 1, 1)</f>
-        <v>0.24999999999999961</v>
+        <v>0.25000000000000094</v>
       </c>
       <c r="Q109" s="3"/>
       <c r="R109" s="3"/>
@@ -14222,7 +14222,7 @@
       </c>
       <c r="Z109" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC109" s="11"/>
     </row>
@@ -14232,25 +14232,25 @@
       </c>
       <c r="B110" s="20">
         <f>$B$23</f>
-        <v>8.5000000000000006E-3</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="C110" s="12" t="s">
         <v>20</v>
       </c>
       <c r="D110" s="13">
         <f>B106 + B110 + B108/2</f>
-        <v>8.7499999999999994E-2</v>
+        <v>7.2500000000000009E-2</v>
       </c>
       <c r="E110" s="14">
         <v>0.1</v>
       </c>
       <c r="F110" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(E110 * EXP($B$4*$B$2), 0, 1) * D110 * SQRT($B$2) - ($B$3 - $B$4 + D110^2/2)*$B$2)</f>
-        <v>1.1510707999322727</v>
+        <v>1.2140828375149078</v>
       </c>
       <c r="G110" s="16">
         <f>EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(1/(D110*SQRT($B$2)) * (LN($B$1 / F110) + ($B$3 - $B$4 + D110^2/2)*$B$2), 0, 1, 1)</f>
-        <v>9.9999999999999784E-2</v>
+        <v>9.9999999999999215E-2</v>
       </c>
       <c r="H110" s="3"/>
       <c r="J110" s="12" t="s">
@@ -14258,25 +14258,25 @@
       </c>
       <c r="K110" s="13">
         <f>$B$23+$F$12</f>
-        <v>9.5000000000000015E-3</v>
+        <v>1.2E-2</v>
       </c>
       <c r="L110" s="12" t="s">
         <v>20</v>
       </c>
       <c r="M110" s="13">
         <f>K106 + K110 + K108/2</f>
-        <v>8.8499999999999995E-2</v>
+        <v>7.350000000000001E-2</v>
       </c>
       <c r="N110" s="14">
         <v>0.1</v>
       </c>
       <c r="O110" s="15">
         <f>$B$1 / EXP(_xlfn.NORM.INV(N110 * EXP($B$4*$B$2), 0, 1) * M110 * SQRT($B$2) - ($B$3 - $B$4 + M110^2/2)*$B$2)</f>
-        <v>1.1518320662656254</v>
+        <v>1.2148813946749826</v>
       </c>
       <c r="P110" s="16">
         <f>EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(1/(M110*SQRT($B$2)) * (LN($B$1 / O110) + ($B$3 - $B$4 + M110^2/2)*$B$2), 0, 1, 1)</f>
-        <v>9.9999999999999936E-2</v>
+        <v>9.9999999999999756E-2</v>
       </c>
       <c r="Q110" s="3"/>
       <c r="R110" s="3"/>
@@ -14286,7 +14286,7 @@
       </c>
       <c r="Z110" s="7">
         <f t="shared" si="27"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="AC110" s="11"/>
     </row>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="Z111" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC111" s="11"/>
     </row>
@@ -14334,7 +14334,7 @@
       </c>
       <c r="Z112" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC112" s="11"/>
     </row>
@@ -14364,7 +14364,7 @@
       </c>
       <c r="Z113" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC113" s="11"/>
     </row>
@@ -14388,25 +14388,25 @@
       </c>
       <c r="Z114" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC114" s="11"/>
     </row>
     <row r="115" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A115" s="35" t="s">
+      <c r="A115" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="B115" s="35"/>
+      <c r="B115" s="33"/>
       <c r="D115" t="s">
         <v>56</v>
       </c>
       <c r="F115" s="6"/>
       <c r="G115" s="3"/>
       <c r="H115" s="5"/>
-      <c r="J115" s="35" t="s">
+      <c r="J115" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="K115" s="35"/>
+      <c r="K115" s="33"/>
       <c r="M115" t="s">
         <v>56</v>
       </c>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="Z115" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC115" s="11"/>
     </row>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="E116" s="16">
         <f>INDEX(LINEST(D106:D110, A117:B121, 1, 0), 3)</f>
-        <v>7.6462335025610437E-2</v>
+        <v>7.0121083605839268E-2</v>
       </c>
       <c r="F116" s="6"/>
       <c r="G116" s="3"/>
@@ -14452,7 +14452,7 @@
       </c>
       <c r="N116" s="16">
         <f>INDEX(LINEST(M106:M110, J117:K121, 1, 0), 3)</f>
-        <v>7.5687952588259125E-2</v>
+        <v>6.93706811977821E-2</v>
       </c>
       <c r="O116" s="6"/>
       <c r="P116" s="3"/>
@@ -14464,43 +14464,43 @@
       </c>
       <c r="Z116" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC116" s="11"/>
     </row>
     <row r="117" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A117" s="16">
         <f>LN(F106 / $B$5)</f>
-        <v>-5.1986035668809515E-2</v>
+        <v>-5.631290706777313E-2</v>
       </c>
       <c r="B117" s="16">
         <f>A117^2</f>
-        <v>2.7025479045587352E-3</v>
+        <v>3.171143502423653E-3</v>
       </c>
       <c r="D117" s="12" t="s">
         <v>26</v>
       </c>
       <c r="E117" s="16">
         <f>INDEX(LINEST(D106:D110, A117:B121, 1, 0), 2)</f>
-        <v>5.3452136103951955E-2</v>
+        <v>-0.120660112263654</v>
       </c>
       <c r="F117" s="6"/>
       <c r="G117" s="3"/>
       <c r="H117" s="5"/>
       <c r="J117" s="16">
         <f>LN(O106 / $B$5)</f>
-        <v>-5.2621637431776239E-2</v>
+        <v>-5.6945420648547525E-2</v>
       </c>
       <c r="K117" s="16">
         <f>J117^2</f>
-        <v>2.7690367260013141E-3</v>
+        <v>3.2427809328400229E-3</v>
       </c>
       <c r="M117" s="12" t="s">
         <v>26</v>
       </c>
       <c r="N117" s="16">
         <f>INDEX(LINEST(M106:M110, J117:K121, 1, 0), 2)</f>
-        <v>5.0767924584503438E-2</v>
+        <v>-0.11517235597603526</v>
       </c>
       <c r="O117" s="6"/>
       <c r="P117" s="3"/>
@@ -14512,43 +14512,43 @@
       </c>
       <c r="Z117" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC117" s="11"/>
     </row>
     <row r="118" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A118" s="16">
         <f>LN(F107 / $B$5)</f>
-        <v>-2.5834349674600837E-2</v>
+        <v>-2.5707057589528355E-2</v>
       </c>
       <c r="B118" s="16">
         <f>A118^2</f>
-        <v>6.6741362310954839E-4</v>
+        <v>6.6085280991132742E-4</v>
       </c>
       <c r="D118" s="12" t="s">
         <v>27</v>
       </c>
       <c r="E118" s="16">
         <f>INDEX(LINEST(D106:D110, A117:B121, 1, 0), 1)</f>
-        <v>2.5459736130021962</v>
+        <v>3.4941219992452259</v>
       </c>
       <c r="F118" s="6"/>
       <c r="G118" s="3"/>
       <c r="H118" s="5"/>
       <c r="J118" s="16">
         <f>LN(O107 / $B$5)</f>
-        <v>-2.5509455686094796E-2</v>
+        <v>-2.5382699698755316E-2</v>
       </c>
       <c r="K118" s="16">
         <f>J118^2</f>
-        <v>6.5073232940083409E-4</v>
+        <v>6.442814439971932E-4</v>
       </c>
       <c r="M118" s="12" t="s">
         <v>27</v>
       </c>
       <c r="N118" s="16">
         <f>INDEX(LINEST(M106:M110, J117:K121, 1, 0), 1)</f>
-        <v>3.0297625127150156</v>
+        <v>4.0101057007776255</v>
       </c>
       <c r="O118" s="6"/>
       <c r="P118" s="3"/>
@@ -14560,29 +14560,29 @@
       </c>
       <c r="Z118" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC118" s="11"/>
     </row>
     <row r="119" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A119" s="16">
         <f>LN(F108 / $B$5)</f>
-        <v>4.3969773703030133E-4</v>
+        <v>3.6751988954891534E-4</v>
       </c>
       <c r="B119" s="16">
         <f>A119^2</f>
-        <v>1.9333409994956802E-7</v>
+        <v>1.3507086921404693E-7</v>
       </c>
       <c r="F119" s="6"/>
       <c r="G119" s="3"/>
       <c r="H119" s="5"/>
       <c r="J119" s="16">
         <f>LN(O108 / $B$5)</f>
-        <v>4.3969773703030133E-4</v>
+        <v>3.6751988954891534E-4</v>
       </c>
       <c r="K119" s="16">
         <f>J119^2</f>
-        <v>1.9333409994956802E-7</v>
+        <v>1.3507086921404693E-7</v>
       </c>
       <c r="O119" s="6"/>
       <c r="P119" s="3"/>
@@ -14594,18 +14594,18 @@
       </c>
       <c r="Z119" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC119" s="11"/>
     </row>
     <row r="120" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A120" s="16">
         <f>LN(F109 / $B$5)</f>
-        <v>2.7864705820005477E-2</v>
+        <v>2.3722351444471133E-2</v>
       </c>
       <c r="B120" s="16">
         <f>A120^2</f>
-        <v>7.7644183043544708E-4</v>
+        <v>5.6274995805500163E-4</v>
       </c>
       <c r="D120" s="3"/>
       <c r="E120" s="10"/>
@@ -14614,11 +14614,11 @@
       <c r="H120" s="5"/>
       <c r="J120" s="16">
         <f>LN(O109 / $B$5)</f>
-        <v>2.7509663313720598E-2</v>
+        <v>2.3370049249623742E-2</v>
       </c>
       <c r="K120" s="16">
         <f>J120^2</f>
-        <v>7.5678157563426496E-4</v>
+        <v>5.4615920192983922E-4</v>
       </c>
       <c r="M120" s="3"/>
       <c r="N120" s="10"/>
@@ -14632,18 +14632,18 @@
       </c>
       <c r="Z120" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC120" s="11"/>
     </row>
     <row r="121" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A121" s="16">
         <f>LN(F110 / $B$5)</f>
-        <v>5.6881459093779917E-2</v>
+        <v>4.7004757408746337E-2</v>
       </c>
       <c r="B121" s="16">
         <f>A121^2</f>
-        <v>3.2355003886373581E-3</v>
+        <v>2.2094472190550937E-3</v>
       </c>
       <c r="D121" s="3"/>
       <c r="E121" s="10"/>
@@ -14652,11 +14652,11 @@
       <c r="H121" s="5"/>
       <c r="J121" s="16">
         <f>LN(O110 / $B$5)</f>
-        <v>5.7542595411994329E-2</v>
+        <v>4.7662286390246132E-2</v>
       </c>
       <c r="K121" s="16">
         <f>J121^2</f>
-        <v>3.311150286748471E-3</v>
+        <v>2.2716935439458415E-3</v>
       </c>
       <c r="M121" s="3"/>
       <c r="N121" s="10"/>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="Z121" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC121" s="11"/>
     </row>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="Z122" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC122" s="11"/>
     </row>
@@ -14730,7 +14730,7 @@
       </c>
       <c r="Z123" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC123" s="11"/>
     </row>
@@ -14740,23 +14740,23 @@
       </c>
       <c r="B124" s="17">
         <f>$F$3</f>
-        <v>1.05</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="C124" s="13">
         <f>E116 + E117*LN(B124/$B$5) + E118*LN(B124/$B$5)^2</f>
-        <v>7.7712951176819769E-2</v>
+        <v>8.5686081116368745E-2</v>
       </c>
       <c r="D124" s="18">
         <f>1 / (C124 * SQRT($B$2)) * (LN($B$1/B124) + ($B$3-$B$4 + C124^2/2)*$B$2)</f>
-        <v>0.92071986871360612</v>
+        <v>1.2275447927719771</v>
       </c>
       <c r="E124" s="18">
         <f>1 / (C124 * SQRT($B$2)) * (LN($B$1/B124) + ($B$3-$B$4 - C124^2/2)*$B$2)</f>
-        <v>0.88186339312519624</v>
+        <v>1.1847017522137928</v>
       </c>
       <c r="F124" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(D124,0,1,1) - B124*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(E124, 0, 1, 1)) * $F$2</f>
-        <v>41138.481628631096</v>
+        <v>60467.804899078772</v>
       </c>
       <c r="H124" s="5"/>
       <c r="J124" s="12" t="s">
@@ -14764,23 +14764,23 @@
       </c>
       <c r="K124" s="17">
         <f>$F$3</f>
-        <v>1.05</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L124" s="13">
         <f>N116 + N117*LN(K124/$B$5) + N118*LN(K124/$B$5)^2</f>
-        <v>7.7625925890709033E-2</v>
+        <v>8.6029884683528832E-2</v>
       </c>
       <c r="M124" s="18">
         <f>1 / (L124 * SQRT($B$2)) * (LN($B$1/K124) + ($B$3-$B$4 + L124^2/2)*$B$2)</f>
-        <v>0.92170853721020418</v>
+        <v>1.2228106804375607</v>
       </c>
       <c r="N124" s="18">
         <f>1 / (L124 * SQRT($B$2)) * (LN($B$1/K124) + ($B$3-$B$4 - L124^2/2)*$B$2)</f>
-        <v>0.88289557426484977</v>
+        <v>1.1797957380957962</v>
       </c>
       <c r="O124" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(M124,0,1,1) - K124*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(N124, 0, 1, 1)) * $F$2</f>
-        <v>41126.264284993886</v>
+        <v>60504.972710000104</v>
       </c>
       <c r="Q124" s="5"/>
       <c r="R124" s="7"/>
@@ -14790,7 +14790,7 @@
       </c>
       <c r="Z124" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC124" s="11"/>
     </row>
@@ -14800,23 +14800,23 @@
       </c>
       <c r="B125" s="17">
         <f>$F$3 + $F$13</f>
-        <v>1.0501</v>
+        <v>1.1001000000000001</v>
       </c>
       <c r="C125" s="13">
         <f>E116 + E117*LN(B125/$B$5) + E118*LN(B125/$B$5)^2</f>
-        <v>7.7701082164065224E-2</v>
+        <v>8.5642314658656377E-2</v>
       </c>
       <c r="D125" s="18">
         <f>1 / (C125 * SQRT($B$2)) * (LN($B$1/B125) + ($B$3-$B$4 + C125^2/2)*$B$2)</f>
-        <v>0.91840329560207401</v>
+        <v>1.2260273274820856</v>
       </c>
       <c r="E125" s="18">
         <f>1 / (C125 * SQRT($B$2)) * (LN($B$1/B125) + ($B$3-$B$4 - C125^2/2)*$B$2)</f>
-        <v>0.87955275452004134</v>
+        <v>1.1832061701527574</v>
       </c>
       <c r="F125" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(D125,0,1,1) - B125*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(E125, 0, 1, 1)) * $F$2</f>
-        <v>41056.603518264899</v>
+        <v>60375.694359474321</v>
       </c>
       <c r="H125" s="5"/>
       <c r="J125" s="12" t="s">
@@ -14824,23 +14824,23 @@
       </c>
       <c r="K125" s="17">
         <f>$F$3 + $F$13</f>
-        <v>1.0501</v>
+        <v>1.1001000000000001</v>
       </c>
       <c r="L125" s="13">
         <f>N116 + N117*LN(K125/$B$5) + N118*LN(K125/$B$5)^2</f>
-        <v>7.761057859630606E-2</v>
+        <v>8.5981773767858982E-2</v>
       </c>
       <c r="M125" s="18">
         <f>1 / (L125 * SQRT($B$2)) * (LN($B$1/K125) + ($B$3-$B$4 + L125^2/2)*$B$2)</f>
-        <v>0.91942898966956033</v>
+        <v>1.2213563223748205</v>
       </c>
       <c r="N125" s="18">
         <f>1 / (L125 * SQRT($B$2)) * (LN($B$1/K125) + ($B$3-$B$4 - L125^2/2)*$B$2)</f>
-        <v>0.88062370037140725</v>
+        <v>1.178365435490891</v>
       </c>
       <c r="O125" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(M125,0,1,1) - K125*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(N125, 0, 1, 1)) * $F$2</f>
-        <v>41043.870971138487</v>
+        <v>60412.459326099954</v>
       </c>
       <c r="Q125" s="5"/>
       <c r="R125" s="7"/>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="Z125" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC125" s="11"/>
     </row>
@@ -14860,23 +14860,23 @@
       </c>
       <c r="B126" s="17">
         <f>$F$4</f>
-        <v>1.1000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="C126" s="13">
         <f>E116 + E117*LN(B126/$B$5) + E118*LN(B126/$B$5)^2</f>
-        <v>7.7413627524703391E-2</v>
+        <v>7.0220488917684787E-2</v>
       </c>
       <c r="D126" s="18">
         <f>1 / (C126 * SQRT($B$2)) * (LN($B$1/B126) + ($B$3-$B$4 + C126^2/2)*$B$2)</f>
-        <v>-0.27772605438979076</v>
+        <v>-0.98891433569391163</v>
       </c>
       <c r="E126" s="18">
         <f>1 / (C126 * SQRT($B$2)) * (LN($B$1/B126) + ($B$3-$B$4 - C126^2/2)*$B$2)</f>
-        <v>-0.31643286815214244</v>
+        <v>-1.0240245801527541</v>
       </c>
       <c r="F126" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(D126,0,1,1) - B126*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(E126, 0, 1, 1)) * $F$2</f>
-        <v>11218.028240872036</v>
+        <v>3375.6640316219</v>
       </c>
       <c r="H126" s="5"/>
       <c r="J126" s="12" t="s">
@@ -14884,23 +14884,23 @@
       </c>
       <c r="K126" s="17">
         <f>$F$4</f>
-        <v>1.1000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="L126" s="13">
         <f>N116 + N117*LN(K126/$B$5) + N118*LN(K126/$B$5)^2</f>
-        <v>7.6672349289182332E-2</v>
+        <v>7.0308334351298893E-2</v>
       </c>
       <c r="M126" s="18">
         <f>1 / (L126 * SQRT($B$2)) * (LN($B$1/K126) + ($B$3-$B$4 + L126^2/2)*$B$2)</f>
-        <v>-0.28078357678192323</v>
+        <v>-0.98763485989193078</v>
       </c>
       <c r="N126" s="18">
         <f>1 / (L126 * SQRT($B$2)) * (LN($B$1/K126) + ($B$3-$B$4 - L126^2/2)*$B$2)</f>
-        <v>-0.31911975142651433</v>
+        <v>-1.0227890270675801</v>
       </c>
       <c r="O126" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(M126,0,1,1) - K126*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(N126, 0, 1, 1)) * $F$2</f>
-        <v>11065.04003860298</v>
+        <v>3388.0075883597206</v>
       </c>
       <c r="Q126" s="5"/>
       <c r="R126" s="7"/>
@@ -14910,7 +14910,7 @@
       </c>
       <c r="Z126" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC126" s="11"/>
     </row>
@@ -14920,23 +14920,23 @@
       </c>
       <c r="B127" s="17">
         <f>$F$4+$F$13</f>
-        <v>1.1001000000000001</v>
+        <v>1.2000999999999999</v>
       </c>
       <c r="C127" s="13">
         <f>E116 + E117*LN(B127/$B$5) + E118*LN(B127/$B$5)^2</f>
-        <v>7.74238303223765E-2</v>
+        <v>7.0231036590454474E-2</v>
       </c>
       <c r="D127" s="18">
         <f>1 / (C127 * SQRT($B$2)) * (LN($B$1/B127) + ($B$3-$B$4 + C127^2/2)*$B$2)</f>
-        <v>-0.28003259735669894</v>
+        <v>-0.991133562778996</v>
       </c>
       <c r="E127" s="18">
         <f>1 / (C127 * SQRT($B$2)) * (LN($B$1/B127) + ($B$3-$B$4 - C127^2/2)*$B$2)</f>
-        <v>-0.3187445125178871</v>
+        <v>-1.0262490810742233</v>
       </c>
       <c r="F127" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(D127,0,1,1) - B127*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(E127, 0, 1, 1)) * $F$2</f>
-        <v>11182.99570076392</v>
+        <v>3362.0154029602168</v>
       </c>
       <c r="H127" s="5"/>
       <c r="J127" s="12" t="s">
@@ -14944,23 +14944,23 @@
       </c>
       <c r="K127" s="17">
         <f>$F$4+$F$13</f>
-        <v>1.1001000000000001</v>
+        <v>1.2000999999999999</v>
       </c>
       <c r="L127" s="13">
         <f>N116 + N117*LN(K127/$B$5) + N118*LN(K127/$B$5)^2</f>
-        <v>7.6683323501228612E-2</v>
+        <v>7.0322381693783853E-2</v>
       </c>
       <c r="M127" s="18">
         <f>1 / (L127 * SQRT($B$2)) * (LN($B$1/K127) + ($B$3-$B$4 + L127^2/2)*$B$2)</f>
-        <v>-0.28310882550337191</v>
+        <v>-0.98980048912482721</v>
       </c>
       <c r="N127" s="18">
         <f>1 / (L127 * SQRT($B$2)) * (LN($B$1/K127) + ($B$3-$B$4 - L127^2/2)*$B$2)</f>
-        <v>-0.32145048725398623</v>
+        <v>-1.0249616799717189</v>
       </c>
       <c r="O127" s="19">
         <f>($B$1*EXP(-$B$4*$B$2)*_xlfn.NORM.DIST(M127,0,1,1) - K127*EXP(-$B$3*$B$2)*_xlfn.NORM.DIST(N127, 0, 1, 1)) * $F$2</f>
-        <v>11030.265920182746</v>
+        <v>3374.8229030940156</v>
       </c>
       <c r="Q127" s="5"/>
       <c r="R127" s="7"/>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="Z127" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC127" s="11"/>
     </row>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="Z128" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC128" s="11"/>
     </row>
@@ -14994,21 +14994,21 @@
       </c>
       <c r="B129" s="19">
         <f>(F124 - F125) / $F$13</f>
-        <v>818781.10366196779</v>
+        <v>921105.39604451333</v>
       </c>
       <c r="C129" s="12" t="s">
         <v>30</v>
       </c>
       <c r="D129" s="19">
         <f>(F126 - F127) / $F$13</f>
-        <v>350325.40108115424</v>
+        <v>136486.28661683234</v>
       </c>
       <c r="E129" s="12" t="s">
         <v>0</v>
       </c>
       <c r="F129" s="19">
         <f>B129-D129</f>
-        <v>468455.70258081355</v>
+        <v>784619.10942768096</v>
       </c>
       <c r="H129" s="5"/>
       <c r="J129" s="12" t="s">
@@ -15016,21 +15016,21 @@
       </c>
       <c r="K129" s="19">
         <f>(O124 - O125) / $F$13</f>
-        <v>823933.13855398446</v>
+        <v>925133.83900150075</v>
       </c>
       <c r="L129" s="12" t="s">
         <v>30</v>
       </c>
       <c r="M129" s="19">
         <f>(O126 - O127) / $F$13</f>
-        <v>347741.18420233205</v>
+        <v>131846.85265704957</v>
       </c>
       <c r="N129" s="12" t="s">
         <v>0</v>
       </c>
       <c r="O129" s="19">
         <f>K129-M129</f>
-        <v>476191.95435165241</v>
+        <v>793286.9863444512</v>
       </c>
       <c r="Q129" s="5"/>
       <c r="R129" s="7"/>
@@ -15040,7 +15040,7 @@
       </c>
       <c r="Z129" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC129" s="11"/>
     </row>
@@ -15052,7 +15052,7 @@
       </c>
       <c r="Z130" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC130" s="11"/>
     </row>
@@ -15064,7 +15064,7 @@
       </c>
       <c r="Z131" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC131" s="11"/>
     </row>
@@ -15076,7 +15076,7 @@
       </c>
       <c r="Z132" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC132" s="11"/>
     </row>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="Z133" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC133" s="11"/>
     </row>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="Z134" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC134" s="11"/>
     </row>
@@ -15112,7 +15112,7 @@
       </c>
       <c r="Z135" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC135" s="11"/>
     </row>
@@ -15124,7 +15124,7 @@
       </c>
       <c r="Z136" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC136" s="11"/>
     </row>
@@ -15136,7 +15136,7 @@
       </c>
       <c r="Z137" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC137" s="11"/>
     </row>
@@ -15148,7 +15148,7 @@
       </c>
       <c r="Z138" s="7">
         <f t="shared" si="27"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC138" s="11"/>
     </row>
@@ -15160,7 +15160,7 @@
       </c>
       <c r="Z139" s="7">
         <f t="shared" ref="Z139:Z202" si="33">IF(AND(Y139&gt;=$F$3, Y139&lt;=$F$4), $F$2, 0)</f>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC139" s="11"/>
     </row>
@@ -15172,7 +15172,7 @@
       </c>
       <c r="Z140" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC140" s="11"/>
     </row>
@@ -15184,7 +15184,7 @@
       </c>
       <c r="Z141" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC141" s="11"/>
     </row>
@@ -15196,7 +15196,7 @@
       </c>
       <c r="Z142" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC142" s="11"/>
     </row>
@@ -15208,7 +15208,7 @@
       </c>
       <c r="Z143" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC143" s="11"/>
     </row>
@@ -15220,7 +15220,7 @@
       </c>
       <c r="Z144" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC144" s="11"/>
     </row>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="Z145" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC145" s="11"/>
     </row>
@@ -15242,7 +15242,7 @@
       </c>
       <c r="Z146" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC146" s="11"/>
     </row>
@@ -15253,7 +15253,7 @@
       </c>
       <c r="Z147" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC147" s="11"/>
     </row>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="Z148" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC148" s="11"/>
     </row>
@@ -15275,7 +15275,7 @@
       </c>
       <c r="Z149" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC149" s="11"/>
     </row>
@@ -15286,7 +15286,7 @@
       </c>
       <c r="Z150" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC150" s="11"/>
     </row>
@@ -15297,7 +15297,7 @@
       </c>
       <c r="Z151" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC151" s="11"/>
     </row>
@@ -15308,7 +15308,7 @@
       </c>
       <c r="Z152" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC152" s="11"/>
     </row>
@@ -15319,7 +15319,7 @@
       </c>
       <c r="Z153" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC153" s="11"/>
     </row>
@@ -15330,7 +15330,7 @@
       </c>
       <c r="Z154" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC154" s="11"/>
     </row>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="Z155" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC155" s="11"/>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="Z156" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC156" s="11"/>
     </row>
@@ -15363,7 +15363,7 @@
       </c>
       <c r="Z157" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC157" s="11"/>
     </row>
@@ -15374,7 +15374,7 @@
       </c>
       <c r="Z158" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC158" s="11"/>
     </row>
@@ -15385,7 +15385,7 @@
       </c>
       <c r="Z159" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC159" s="11"/>
     </row>
@@ -15396,7 +15396,7 @@
       </c>
       <c r="Z160" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC160" s="11"/>
     </row>
@@ -15407,7 +15407,7 @@
       </c>
       <c r="Z161" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC161" s="11"/>
     </row>
@@ -15418,7 +15418,7 @@
       </c>
       <c r="Z162" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC162" s="11"/>
     </row>
@@ -15429,7 +15429,7 @@
       </c>
       <c r="Z163" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC163" s="11"/>
     </row>
@@ -15440,7 +15440,7 @@
       </c>
       <c r="Z164" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC164" s="11"/>
     </row>
@@ -15451,7 +15451,7 @@
       </c>
       <c r="Z165" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC165" s="11"/>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="Z166" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC166" s="11"/>
     </row>
@@ -15473,7 +15473,7 @@
       </c>
       <c r="Z167" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC167" s="11"/>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="Z168" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC168" s="11"/>
     </row>
@@ -15495,7 +15495,7 @@
       </c>
       <c r="Z169" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC169" s="11"/>
     </row>
@@ -15506,7 +15506,7 @@
       </c>
       <c r="Z170" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC170" s="11"/>
     </row>
@@ -15517,7 +15517,7 @@
       </c>
       <c r="Z171" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC171" s="11"/>
     </row>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="Z172" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC172" s="11"/>
     </row>
@@ -15539,7 +15539,7 @@
       </c>
       <c r="Z173" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC173" s="11"/>
     </row>
@@ -15550,7 +15550,7 @@
       </c>
       <c r="Z174" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC174" s="11"/>
     </row>
@@ -15561,7 +15561,7 @@
       </c>
       <c r="Z175" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC175" s="11"/>
     </row>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="Z176" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC176" s="11"/>
     </row>
@@ -15583,7 +15583,7 @@
       </c>
       <c r="Z177" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC177" s="11"/>
     </row>
@@ -15594,7 +15594,7 @@
       </c>
       <c r="Z178" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC178" s="11"/>
     </row>
@@ -15605,7 +15605,7 @@
       </c>
       <c r="Z179" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC179" s="11"/>
     </row>
@@ -15616,7 +15616,7 @@
       </c>
       <c r="Z180" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC180" s="11"/>
     </row>
@@ -15627,7 +15627,7 @@
       </c>
       <c r="Z181" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="AC181" s="11"/>
     </row>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="Z182" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="183" spans="25:29" x14ac:dyDescent="0.25">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="Z183" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="184" spans="25:29" x14ac:dyDescent="0.25">
@@ -15658,7 +15658,7 @@
       </c>
       <c r="Z184" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="185" spans="25:29" x14ac:dyDescent="0.25">
@@ -15668,7 +15668,7 @@
       </c>
       <c r="Z185" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="186" spans="25:29" x14ac:dyDescent="0.25">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="Z186" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="187" spans="25:29" x14ac:dyDescent="0.25">
@@ -15688,7 +15688,7 @@
       </c>
       <c r="Z187" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="188" spans="25:29" x14ac:dyDescent="0.25">
@@ -15698,7 +15698,7 @@
       </c>
       <c r="Z188" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="189" spans="25:29" x14ac:dyDescent="0.25">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="Z189" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="190" spans="25:29" x14ac:dyDescent="0.25">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="Z190" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="191" spans="25:29" x14ac:dyDescent="0.25">
@@ -15728,7 +15728,7 @@
       </c>
       <c r="Z191" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="192" spans="25:29" x14ac:dyDescent="0.25">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="Z192" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="193" spans="25:26" x14ac:dyDescent="0.25">
@@ -15748,7 +15748,7 @@
       </c>
       <c r="Z193" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="194" spans="25:26" x14ac:dyDescent="0.25">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="Z194" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="195" spans="25:26" x14ac:dyDescent="0.25">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="Z195" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="196" spans="25:26" x14ac:dyDescent="0.25">
@@ -15778,7 +15778,7 @@
       </c>
       <c r="Z196" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="197" spans="25:26" x14ac:dyDescent="0.25">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="Z197" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="198" spans="25:26" x14ac:dyDescent="0.25">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="Z198" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="199" spans="25:26" x14ac:dyDescent="0.25">
@@ -15808,7 +15808,7 @@
       </c>
       <c r="Z199" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="200" spans="25:26" x14ac:dyDescent="0.25">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="Z200" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="201" spans="25:26" x14ac:dyDescent="0.25">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="Z201" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="202" spans="25:26" x14ac:dyDescent="0.25">
@@ -15838,7 +15838,7 @@
       </c>
       <c r="Z202" s="7">
         <f t="shared" si="33"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="203" spans="25:26" x14ac:dyDescent="0.25">
@@ -15848,7 +15848,7 @@
       </c>
       <c r="Z203" s="7">
         <f t="shared" ref="Z203:Z250" si="35">IF(AND(Y203&gt;=$F$3, Y203&lt;=$F$4), $F$2, 0)</f>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="204" spans="25:26" x14ac:dyDescent="0.25">
@@ -15858,7 +15858,7 @@
       </c>
       <c r="Z204" s="7">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="205" spans="25:26" x14ac:dyDescent="0.25">
@@ -15868,7 +15868,7 @@
       </c>
       <c r="Z205" s="7">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="206" spans="25:26" x14ac:dyDescent="0.25">
@@ -15878,7 +15878,7 @@
       </c>
       <c r="Z206" s="7">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="207" spans="25:26" x14ac:dyDescent="0.25">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="Z207" s="7">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="208" spans="25:26" x14ac:dyDescent="0.25">
@@ -15898,7 +15898,7 @@
       </c>
       <c r="Z208" s="7">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="209" spans="25:26" x14ac:dyDescent="0.25">
@@ -15908,7 +15908,7 @@
       </c>
       <c r="Z209" s="7">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="210" spans="25:26" x14ac:dyDescent="0.25">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="Z210" s="7">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="211" spans="25:26" x14ac:dyDescent="0.25">
@@ -17025,13 +17025,14 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="E46:G46"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="J104:K104"/>
+    <mergeCell ref="L104:M104"/>
+    <mergeCell ref="N104:P104"/>
+    <mergeCell ref="Q104:R104"/>
+    <mergeCell ref="L75:M75"/>
+    <mergeCell ref="N75:P75"/>
+    <mergeCell ref="Q75:R75"/>
     <mergeCell ref="A57:B57"/>
     <mergeCell ref="A86:B86"/>
     <mergeCell ref="A115:B115"/>
@@ -17044,14 +17045,13 @@
     <mergeCell ref="C75:D75"/>
     <mergeCell ref="E75:G75"/>
     <mergeCell ref="J115:K115"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="J104:K104"/>
-    <mergeCell ref="L104:M104"/>
-    <mergeCell ref="N104:P104"/>
-    <mergeCell ref="Q104:R104"/>
-    <mergeCell ref="L75:M75"/>
-    <mergeCell ref="N75:P75"/>
-    <mergeCell ref="Q75:R75"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E46:G46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
